--- a/artfynd/A 15629-2024 artfynd.xlsx
+++ b/artfynd/A 15629-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -790,6 +790,4977 @@
       <c r="AY2" t="inlineStr">
         <is>
           <t>Artskyddsutredning vid Lärbro 2021 (JAG0090)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>126075195</v>
+      </c>
+      <c r="B3" t="n">
+        <v>103781</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>224416</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Ljus solvända</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Hemhagen, Nors, Gtl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>723294</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6412905</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Lärbro</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>FNT0020 Lärbro Nors NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>126075055</v>
+      </c>
+      <c r="B4" t="n">
+        <v>109151</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Hemhagen, Nors, Gtl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>723291</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6413160</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Lärbro</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-05-15</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-05-15</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>FNT0020 Lärbro Nors NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>126075032</v>
+      </c>
+      <c r="B5" t="n">
+        <v>109151</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Hemhagen, Nors, Gtl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>723222</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6412868</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Lärbro</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>FNT0020 Lärbro Nors NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>126075167</v>
+      </c>
+      <c r="B6" t="n">
+        <v>98360</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>219862</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Nästrot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Neottia nidus-avis</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Hemhagen, Nors, Gtl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>723327</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6413202</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Lärbro</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>FNT0020 Lärbro Nors NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>126075089</v>
+      </c>
+      <c r="B7" t="n">
+        <v>98366</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>219864</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Sankt pers nycklar</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Orchis mascula</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Hemhagen, Nors, Gtl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>723237</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6413005</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Lärbro</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>FNT0020 Lärbro Nors NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>126075088</v>
+      </c>
+      <c r="B8" t="n">
+        <v>98366</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>219864</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Sankt pers nycklar</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Orchis mascula</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Hemhagen, Nors, Gtl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>723278</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6413037</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Lärbro</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>FNT0020 Lärbro Nors NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>126075038</v>
+      </c>
+      <c r="B9" t="n">
+        <v>109151</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Hemhagen, Nors, Gtl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>723299</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6413005</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Lärbro</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>FNT0020 Lärbro Nors NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>126075294</v>
+      </c>
+      <c r="B10" t="n">
+        <v>105274</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Hemhagen, Nors, Gtl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>723318</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6412902</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Lärbro</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>FNT0020 Lärbro Nors NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>126075295</v>
+      </c>
+      <c r="B11" t="n">
+        <v>105274</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Hemhagen, Nors, Gtl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>723293</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6412916</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Lärbro</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>FNT0020 Lärbro Nors NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>126075351</v>
+      </c>
+      <c r="B12" t="n">
+        <v>106620</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Hemhagen, Nors, Gtl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>723310</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6412729</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Lärbro</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>FNT0020 Lärbro Nors NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>126075422</v>
+      </c>
+      <c r="B13" t="n">
+        <v>106166</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>221903</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Axveronika</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Veronica spicata</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Hemhagen, Nors, Gtl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>723297</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6412905</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Lärbro</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>FNT0020 Lärbro Nors NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>126075247</v>
+      </c>
+      <c r="B14" t="n">
+        <v>96398</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>588</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Kalkkoppmossa</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Entosthodon muhlenbergii</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Turner) Fife</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Hemhagen, Nors, Gtl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>723305</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6412901</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Lärbro</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>FNT0020 Lärbro Nors NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>126075046</v>
+      </c>
+      <c r="B15" t="n">
+        <v>109151</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Hemhagen, Nors, Gtl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>723345</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6413172</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Lärbro</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>FNT0020 Lärbro Nors NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>126075072</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57648</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Hemhagen, Nors, Gtl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>723335</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6413183</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Lärbro</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Lockläte i lämplig biotop, senvuxna tallar med spår av spår av spillkråka, enstaka äldre potentiella boträd i skogen.</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>FNT0020 Lärbro Nors NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>126075228</v>
+      </c>
+      <c r="B17" t="n">
+        <v>75006</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Hemhagen, Nors, Gtl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>723347</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6413067</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Lärbro</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>FNT0020 Lärbro Nors NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>126075192</v>
+      </c>
+      <c r="B18" t="n">
+        <v>103781</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>224416</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Ljus solvända</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Hemhagen, Nors, Gtl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>723305</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6412896</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Lärbro</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>FNT0020 Lärbro Nors NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>126075420</v>
+      </c>
+      <c r="B19" t="n">
+        <v>106166</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>221903</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Axveronika</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Veronica spicata</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Hemhagen, Nors, Gtl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>723302</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6412899</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Lärbro</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>FNT0020 Lärbro Nors NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>126075041</v>
+      </c>
+      <c r="B20" t="n">
+        <v>109151</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Hemhagen, Nors, Gtl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>723339</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6413055</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Lärbro</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>FNT0020 Lärbro Nors NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>126075050</v>
+      </c>
+      <c r="B21" t="n">
+        <v>109151</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Hemhagen, Nors, Gtl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>723315</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6413206</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Lärbro</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>FNT0020 Lärbro Nors NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>126075043</v>
+      </c>
+      <c r="B22" t="n">
+        <v>109151</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Hemhagen, Nors, Gtl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>723368</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6413087</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Lärbro</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>FNT0020 Lärbro Nors NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>126075053</v>
+      </c>
+      <c r="B23" t="n">
+        <v>109151</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Hemhagen, Nors, Gtl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>723356</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6413200</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Lärbro</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>FNT0020 Lärbro Nors NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>126075040</v>
+      </c>
+      <c r="B24" t="n">
+        <v>109151</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Hemhagen, Nors, Gtl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>723311</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6413017</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Lärbro</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>FNT0020 Lärbro Nors NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>126075330</v>
+      </c>
+      <c r="B25" t="n">
+        <v>95941</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Hemhagen, Nors, Gtl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>723341</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6413230</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Lärbro</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>FNT0020 Lärbro Nors NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>126075095</v>
+      </c>
+      <c r="B26" t="n">
+        <v>98366</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>219864</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Sankt pers nycklar</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Orchis mascula</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Hemhagen, Nors, Gtl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>723328</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6412904</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Lärbro</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>FNT0020 Lärbro Nors NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>126075193</v>
+      </c>
+      <c r="B27" t="n">
+        <v>103781</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>224416</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Ljus solvända</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Hemhagen, Nors, Gtl</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>723321</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6412898</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Lärbro</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>FNT0020 Lärbro Nors NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>126075052</v>
+      </c>
+      <c r="B28" t="n">
+        <v>109151</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Hemhagen, Nors, Gtl</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>723338</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6413224</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Lärbro</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>FNT0020 Lärbro Nors NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>126075357</v>
+      </c>
+      <c r="B29" t="n">
+        <v>106620</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Hemhagen, Nors, Gtl</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>723324</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6412899</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Lärbro</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>FNT0020 Lärbro Nors NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>126075049</v>
+      </c>
+      <c r="B30" t="n">
+        <v>109151</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Hemhagen, Nors, Gtl</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>723331</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6413195</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Lärbro</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>FNT0020 Lärbro Nors NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>126075185</v>
+      </c>
+      <c r="B31" t="n">
+        <v>103781</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>224416</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Ljus solvända</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Hemhagen, Nors, Gtl</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>723250</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6413023</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Lärbro</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>FNT0020 Lärbro Nors NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>126075189</v>
+      </c>
+      <c r="B32" t="n">
+        <v>103781</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>224416</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Ljus solvända</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Hemhagen, Nors, Gtl</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>723328</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6412741</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Lärbro</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>FNT0020 Lärbro Nors NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>126075054</v>
+      </c>
+      <c r="B33" t="n">
+        <v>109151</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Hemhagen, Nors, Gtl</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>723389</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6413195</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Lärbro</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>FNT0020 Lärbro Nors NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>126075188</v>
+      </c>
+      <c r="B34" t="n">
+        <v>103781</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>224416</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Ljus solvända</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Hemhagen, Nors, Gtl</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>723322</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6412738</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Lärbro</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>FNT0020 Lärbro Nors NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>126075328</v>
+      </c>
+      <c r="B35" t="n">
+        <v>100520</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Hemhagen, Nors, Gtl</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>723335</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6413175</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Lärbro</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>FNT0020 Lärbro Nors NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>126075031</v>
+      </c>
+      <c r="B36" t="n">
+        <v>109151</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Hemhagen, Nors, Gtl</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>723216</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6412876</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Lärbro</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>FNT0020 Lärbro Nors NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>126075421</v>
+      </c>
+      <c r="B37" t="n">
+        <v>106166</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>221903</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Axveronika</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Veronica spicata</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Hemhagen, Nors, Gtl</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>723321</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6412897</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Lärbro</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>FNT0020 Lärbro Nors NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>126075165</v>
+      </c>
+      <c r="B38" t="n">
+        <v>19793</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>241122</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Orellia scorzonerae</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Robineau-Desvoidy, 1830)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Hemhagen, Nors, Gtl</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>723375</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6413131</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Lärbro</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>På knoppar av värdväxten svinrot.</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>svinrot</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t>FNT0020 Lärbro Nors NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>126075028</v>
+      </c>
+      <c r="B39" t="n">
+        <v>109151</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Hemhagen, Nors, Gtl</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>723208</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6412969</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Lärbro</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>FNT0020 Lärbro Nors NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>126075039</v>
+      </c>
+      <c r="B40" t="n">
+        <v>109151</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Hemhagen, Nors, Gtl</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>723331</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6413009</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Lärbro</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t>FNT0020 Lärbro Nors NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>126075042</v>
+      </c>
+      <c r="B41" t="n">
+        <v>109151</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Hemhagen, Nors, Gtl</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>723354</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6413071</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Lärbro</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t>FNT0020 Lärbro Nors NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>126075030</v>
+      </c>
+      <c r="B42" t="n">
+        <v>109151</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Hemhagen, Nors, Gtl</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>723211</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6412911</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Lärbro</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t>FNT0020 Lärbro Nors NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>126075044</v>
+      </c>
+      <c r="B43" t="n">
+        <v>109151</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Hemhagen, Nors, Gtl</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>723367</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6413134</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Lärbro</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t>FNT0020 Lärbro Nors NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>126075184</v>
+      </c>
+      <c r="B44" t="n">
+        <v>103781</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>224416</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Ljus solvända</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Hemhagen, Nors, Gtl</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>723240</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6413005</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Lärbro</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t>FNT0020 Lärbro Nors NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>126075269</v>
+      </c>
+      <c r="B45" t="n">
+        <v>107209</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>220079</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Jordtistel</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Cirsium acaule</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Hemhagen, Nors, Gtl</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>723282</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6413048</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Lärbro</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr">
+        <is>
+          <t>FNT0020 Lärbro Nors NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>126075182</v>
+      </c>
+      <c r="B46" t="n">
+        <v>103781</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>224416</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Ljus solvända</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Hemhagen, Nors, Gtl</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>723272</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6413033</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Lärbro</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>FNT0020 Lärbro Nors NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>126075412</v>
+      </c>
+      <c r="B47" t="n">
+        <v>106166</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>221903</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Axveronika</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Veronica spicata</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Hemhagen, Nors, Gtl</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>723243</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6413018</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Lärbro</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t>FNT0020 Lärbro Nors NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>126075045</v>
+      </c>
+      <c r="B48" t="n">
+        <v>109151</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Hemhagen, Nors, Gtl</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>723352</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6413153</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Lärbro</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr">
+        <is>
+          <t>FNT0020 Lärbro Nors NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>126075096</v>
+      </c>
+      <c r="B49" t="n">
+        <v>98366</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>219864</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Sankt pers nycklar</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Orchis mascula</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Hemhagen, Nors, Gtl</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>723293</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6412906</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Lärbro</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr">
+        <is>
+          <t>FNT0020 Lärbro Nors NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>126075047</v>
+      </c>
+      <c r="B50" t="n">
+        <v>109151</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Hemhagen, Nors, Gtl</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>723335</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6413175</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Lärbro</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr">
+        <is>
+          <t>FNT0020 Lärbro Nors NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>126075029</v>
+      </c>
+      <c r="B51" t="n">
+        <v>109151</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Hemhagen, Nors, Gtl</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>723216</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6412940</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Lärbro</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr">
+        <is>
+          <t>FNT0020 Lärbro Nors NVI 2024</t>
         </is>
       </c>
     </row>

--- a/artfynd/A 15629-2024 artfynd.xlsx
+++ b/artfynd/A 15629-2024 artfynd.xlsx
@@ -892,27 +892,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126075055</v>
+        <v>126075089</v>
       </c>
       <c r="B4" t="n">
-        <v>109151</v>
+        <v>98366</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220299</v>
+        <v>219864</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -921,16 +921,21 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Hemhagen, Nors, Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>723291</v>
+        <v>723237</v>
       </c>
       <c r="R4" t="n">
-        <v>6413160</v>
+        <v>6413005</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -957,12 +962,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1094,32 +1099,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126075167</v>
+        <v>126075055</v>
       </c>
       <c r="B6" t="n">
-        <v>98360</v>
+        <v>109151</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219862</v>
+        <v>220299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1129,10 +1134,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>723327</v>
+        <v>723291</v>
       </c>
       <c r="R6" t="n">
-        <v>6413202</v>
+        <v>6413160</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1159,12 +1164,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1195,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126075089</v>
+        <v>126075167</v>
       </c>
       <c r="B7" t="n">
-        <v>98366</v>
+        <v>98360</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1206,39 +1211,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219864</v>
+        <v>219862</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hemhagen, Nors, Gtl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>723237</v>
+        <v>723327</v>
       </c>
       <c r="R7" t="n">
-        <v>6413005</v>
+        <v>6413202</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1301,27 +1301,27 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126075088</v>
+        <v>126075038</v>
       </c>
       <c r="B8" t="n">
-        <v>98366</v>
+        <v>109151</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219864</v>
+        <v>220299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1330,21 +1330,16 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hemhagen, Nors, Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>723278</v>
+        <v>723299</v>
       </c>
       <c r="R8" t="n">
-        <v>6413037</v>
+        <v>6413005</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1407,27 +1402,27 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126075038</v>
+        <v>126075088</v>
       </c>
       <c r="B9" t="n">
-        <v>109151</v>
+        <v>98366</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220299</v>
+        <v>219864</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1436,16 +1431,21 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hemhagen, Nors, Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>723299</v>
+        <v>723278</v>
       </c>
       <c r="R9" t="n">
-        <v>6413005</v>
+        <v>6413037</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1609,27 +1609,27 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126075295</v>
+        <v>126075351</v>
       </c>
       <c r="B11" t="n">
-        <v>105274</v>
+        <v>106620</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221141</v>
+        <v>221849</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1644,10 +1644,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>723293</v>
+        <v>723310</v>
       </c>
       <c r="R11" t="n">
-        <v>6412916</v>
+        <v>6412729</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1710,27 +1710,27 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126075351</v>
+        <v>126075295</v>
       </c>
       <c r="B12" t="n">
-        <v>106620</v>
+        <v>105274</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221849</v>
+        <v>221141</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1745,10 +1745,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>723310</v>
+        <v>723293</v>
       </c>
       <c r="R12" t="n">
-        <v>6412729</v>
+        <v>6412916</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1811,10 +1811,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126075422</v>
+        <v>126075046</v>
       </c>
       <c r="B13" t="n">
-        <v>106166</v>
+        <v>109151</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1822,16 +1822,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221903</v>
+        <v>220299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>723297</v>
+        <v>723345</v>
       </c>
       <c r="R13" t="n">
-        <v>6412905</v>
+        <v>6413172</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2013,10 +2013,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126075046</v>
+        <v>126075422</v>
       </c>
       <c r="B15" t="n">
-        <v>109151</v>
+        <v>106166</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2024,16 +2024,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220299</v>
+        <v>221903</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2048,10 +2048,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>723345</v>
+        <v>723297</v>
       </c>
       <c r="R15" t="n">
-        <v>6413172</v>
+        <v>6412905</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2432,10 +2432,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126075420</v>
+        <v>126075041</v>
       </c>
       <c r="B19" t="n">
-        <v>106166</v>
+        <v>109151</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2443,16 +2443,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221903</v>
+        <v>220299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2467,10 +2467,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>723302</v>
+        <v>723339</v>
       </c>
       <c r="R19" t="n">
-        <v>6412899</v>
+        <v>6413055</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2533,10 +2533,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126075041</v>
+        <v>126075420</v>
       </c>
       <c r="B20" t="n">
-        <v>109151</v>
+        <v>106166</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2544,16 +2544,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220299</v>
+        <v>221903</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2568,10 +2568,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>723339</v>
+        <v>723302</v>
       </c>
       <c r="R20" t="n">
-        <v>6413055</v>
+        <v>6412899</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3038,10 +3038,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126075330</v>
+        <v>126075095</v>
       </c>
       <c r="B25" t="n">
-        <v>95941</v>
+        <v>98366</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3049,34 +3049,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2180</v>
+        <v>219864</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Hemhagen, Nors, Gtl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>723341</v>
+        <v>723328</v>
       </c>
       <c r="R25" t="n">
-        <v>6413230</v>
+        <v>6412904</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3139,27 +3144,27 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126075095</v>
+        <v>126075052</v>
       </c>
       <c r="B26" t="n">
-        <v>98366</v>
+        <v>109151</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>219864</v>
+        <v>220299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3168,21 +3173,16 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Hemhagen, Nors, Gtl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>723328</v>
+        <v>723338</v>
       </c>
       <c r="R26" t="n">
-        <v>6412904</v>
+        <v>6413224</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3245,10 +3245,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126075193</v>
+        <v>126075049</v>
       </c>
       <c r="B27" t="n">
-        <v>103781</v>
+        <v>109151</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3256,19 +3256,23 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>224416</v>
+        <v>220299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ljus solvända</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. nummularium</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr"/>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3276,10 +3280,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>723321</v>
+        <v>723331</v>
       </c>
       <c r="R27" t="n">
-        <v>6412898</v>
+        <v>6413195</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3342,10 +3346,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126075052</v>
+        <v>126075193</v>
       </c>
       <c r="B28" t="n">
-        <v>109151</v>
+        <v>103781</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3353,23 +3357,19 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220299</v>
+        <v>224416</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Ljus solvända</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3377,10 +3377,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>723338</v>
+        <v>723321</v>
       </c>
       <c r="R28" t="n">
-        <v>6413224</v>
+        <v>6412898</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3544,32 +3544,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126075049</v>
+        <v>126075330</v>
       </c>
       <c r="B30" t="n">
-        <v>109151</v>
+        <v>95941</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220299</v>
+        <v>2180</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3579,10 +3579,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>723331</v>
+        <v>723341</v>
       </c>
       <c r="R30" t="n">
-        <v>6413195</v>
+        <v>6413230</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3645,7 +3645,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126075185</v>
+        <v>126075188</v>
       </c>
       <c r="B31" t="n">
         <v>103781</v>
@@ -3676,10 +3676,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>723250</v>
+        <v>723322</v>
       </c>
       <c r="R31" t="n">
-        <v>6413023</v>
+        <v>6412738</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3839,10 +3839,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126075054</v>
+        <v>126075185</v>
       </c>
       <c r="B33" t="n">
-        <v>109151</v>
+        <v>103781</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3850,23 +3850,19 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220299</v>
+        <v>224416</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Ljus solvända</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -3874,10 +3870,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>723389</v>
+        <v>723250</v>
       </c>
       <c r="R33" t="n">
-        <v>6413195</v>
+        <v>6413023</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3940,10 +3936,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126075188</v>
+        <v>126075054</v>
       </c>
       <c r="B34" t="n">
-        <v>103781</v>
+        <v>109151</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3951,19 +3947,23 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>224416</v>
+        <v>220299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ljus solvända</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. nummularium</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr"/>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -3971,10 +3971,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>723322</v>
+        <v>723389</v>
       </c>
       <c r="R34" t="n">
-        <v>6412738</v>
+        <v>6413195</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4860,10 +4860,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126075044</v>
+        <v>126075269</v>
       </c>
       <c r="B43" t="n">
-        <v>109151</v>
+        <v>107209</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4871,21 +4871,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220299</v>
+        <v>220079</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4895,10 +4895,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>723367</v>
+        <v>723282</v>
       </c>
       <c r="R43" t="n">
-        <v>6413134</v>
+        <v>6413048</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4961,10 +4961,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126075184</v>
+        <v>126075044</v>
       </c>
       <c r="B44" t="n">
-        <v>103781</v>
+        <v>109151</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4972,19 +4972,23 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>224416</v>
+        <v>220299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ljus solvända</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. nummularium</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr"/>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -4992,10 +4996,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>723240</v>
+        <v>723367</v>
       </c>
       <c r="R44" t="n">
-        <v>6413005</v>
+        <v>6413134</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5058,10 +5062,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126075269</v>
+        <v>126075184</v>
       </c>
       <c r="B45" t="n">
-        <v>107209</v>
+        <v>103781</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5069,23 +5073,19 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220079</v>
+        <v>224416</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Ljus solvända</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5093,10 +5093,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>723282</v>
+        <v>723240</v>
       </c>
       <c r="R45" t="n">
-        <v>6413048</v>
+        <v>6413005</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5159,10 +5159,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126075182</v>
+        <v>126075412</v>
       </c>
       <c r="B46" t="n">
-        <v>103781</v>
+        <v>106166</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5170,19 +5170,23 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>224416</v>
+        <v>221903</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ljus solvända</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. nummularium</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr"/>
+          <t>Veronica spicata</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5190,10 +5194,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>723272</v>
+        <v>723243</v>
       </c>
       <c r="R46" t="n">
-        <v>6413033</v>
+        <v>6413018</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5256,10 +5260,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126075412</v>
+        <v>126075182</v>
       </c>
       <c r="B47" t="n">
-        <v>106166</v>
+        <v>103781</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5267,23 +5271,19 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221903</v>
+        <v>224416</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Ljus solvända</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5291,10 +5291,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>723243</v>
+        <v>723272</v>
       </c>
       <c r="R47" t="n">
-        <v>6413018</v>
+        <v>6413033</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5458,27 +5458,27 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126075096</v>
+        <v>126075047</v>
       </c>
       <c r="B49" t="n">
-        <v>98366</v>
+        <v>109151</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>219864</v>
+        <v>220299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -5487,21 +5487,16 @@
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Hemhagen, Nors, Gtl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>723293</v>
+        <v>723335</v>
       </c>
       <c r="R49" t="n">
-        <v>6412906</v>
+        <v>6413175</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5564,27 +5559,27 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126075047</v>
+        <v>126075096</v>
       </c>
       <c r="B50" t="n">
-        <v>109151</v>
+        <v>98366</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220299</v>
+        <v>219864</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -5593,16 +5588,21 @@
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Hemhagen, Nors, Gtl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>723335</v>
+        <v>723293</v>
       </c>
       <c r="R50" t="n">
-        <v>6413175</v>
+        <v>6412906</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>

--- a/artfynd/A 15629-2024 artfynd.xlsx
+++ b/artfynd/A 15629-2024 artfynd.xlsx
@@ -1609,27 +1609,27 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126075351</v>
+        <v>126075295</v>
       </c>
       <c r="B11" t="n">
-        <v>106620</v>
+        <v>105274</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221849</v>
+        <v>221141</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1644,10 +1644,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>723310</v>
+        <v>723293</v>
       </c>
       <c r="R11" t="n">
-        <v>6412729</v>
+        <v>6412916</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1710,27 +1710,27 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126075295</v>
+        <v>126075351</v>
       </c>
       <c r="B12" t="n">
-        <v>105274</v>
+        <v>106620</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221141</v>
+        <v>221849</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1745,10 +1745,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>723293</v>
+        <v>723310</v>
       </c>
       <c r="R12" t="n">
-        <v>6412916</v>
+        <v>6412729</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1811,10 +1811,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126075046</v>
+        <v>126075422</v>
       </c>
       <c r="B13" t="n">
-        <v>109151</v>
+        <v>106166</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1822,16 +1822,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220299</v>
+        <v>221903</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>723345</v>
+        <v>723297</v>
       </c>
       <c r="R13" t="n">
-        <v>6413172</v>
+        <v>6412905</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1912,10 +1912,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126075247</v>
+        <v>126075046</v>
       </c>
       <c r="B14" t="n">
-        <v>96398</v>
+        <v>109151</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1923,21 +1923,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>588</v>
+        <v>220299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kalkkoppmossa</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Entosthodon muhlenbergii</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Turner) Fife</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1947,10 +1947,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>723305</v>
+        <v>723345</v>
       </c>
       <c r="R14" t="n">
-        <v>6412901</v>
+        <v>6413172</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2013,10 +2013,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126075422</v>
+        <v>126075247</v>
       </c>
       <c r="B15" t="n">
-        <v>106166</v>
+        <v>96398</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2024,21 +2024,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221903</v>
+        <v>588</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Kalkkoppmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Entosthodon muhlenbergii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Turner) Fife</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2048,10 +2048,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>723297</v>
+        <v>723305</v>
       </c>
       <c r="R15" t="n">
-        <v>6412905</v>
+        <v>6412901</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -4037,32 +4037,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126075328</v>
+        <v>126075031</v>
       </c>
       <c r="B35" t="n">
-        <v>100520</v>
+        <v>109151</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>222498</v>
+        <v>220299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4072,10 +4072,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>723335</v>
+        <v>723216</v>
       </c>
       <c r="R35" t="n">
-        <v>6413175</v>
+        <v>6412876</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4138,32 +4138,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126075031</v>
+        <v>126075328</v>
       </c>
       <c r="B36" t="n">
-        <v>109151</v>
+        <v>100520</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220299</v>
+        <v>222498</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4173,10 +4173,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>723216</v>
+        <v>723335</v>
       </c>
       <c r="R36" t="n">
-        <v>6412876</v>
+        <v>6413175</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>

--- a/artfynd/A 15629-2024 artfynd.xlsx
+++ b/artfynd/A 15629-2024 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>126075195</v>
       </c>
       <c r="B3" t="n">
-        <v>103781</v>
+        <v>103782</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126075089</v>
+        <v>126075167</v>
       </c>
       <c r="B4" t="n">
-        <v>98366</v>
+        <v>98361</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -903,39 +903,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219864</v>
+        <v>219862</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Hemhagen, Nors, Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>723237</v>
+        <v>723327</v>
       </c>
       <c r="R4" t="n">
-        <v>6413005</v>
+        <v>6413202</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -998,27 +993,27 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126075032</v>
+        <v>126075089</v>
       </c>
       <c r="B5" t="n">
-        <v>109151</v>
+        <v>98367</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220299</v>
+        <v>219864</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1027,16 +1022,21 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hemhagen, Nors, Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>723222</v>
+        <v>723237</v>
       </c>
       <c r="R5" t="n">
-        <v>6412868</v>
+        <v>6413005</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126075055</v>
+        <v>126075032</v>
       </c>
       <c r="B6" t="n">
-        <v>109151</v>
+        <v>109152</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>723291</v>
+        <v>723222</v>
       </c>
       <c r="R6" t="n">
-        <v>6413160</v>
+        <v>6412868</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1164,12 +1164,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,32 +1200,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126075167</v>
+        <v>126075055</v>
       </c>
       <c r="B7" t="n">
-        <v>98360</v>
+        <v>109152</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219862</v>
+        <v>220299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>723327</v>
+        <v>723291</v>
       </c>
       <c r="R7" t="n">
-        <v>6413202</v>
+        <v>6413160</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1265,12 +1265,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1301,27 +1301,27 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126075038</v>
+        <v>126075088</v>
       </c>
       <c r="B8" t="n">
-        <v>109151</v>
+        <v>98367</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220299</v>
+        <v>219864</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1330,16 +1330,21 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hemhagen, Nors, Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>723299</v>
+        <v>723278</v>
       </c>
       <c r="R8" t="n">
-        <v>6413005</v>
+        <v>6413037</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1402,10 +1407,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126075088</v>
+        <v>126075294</v>
       </c>
       <c r="B9" t="n">
-        <v>98366</v>
+        <v>105275</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1413,16 +1418,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219864</v>
+        <v>221141</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1431,21 +1436,16 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hemhagen, Nors, Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>723278</v>
+        <v>723318</v>
       </c>
       <c r="R9" t="n">
-        <v>6413037</v>
+        <v>6412902</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1508,27 +1508,27 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126075294</v>
+        <v>126075038</v>
       </c>
       <c r="B10" t="n">
-        <v>105274</v>
+        <v>109152</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221141</v>
+        <v>220299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1543,10 +1543,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>723318</v>
+        <v>723299</v>
       </c>
       <c r="R10" t="n">
-        <v>6412902</v>
+        <v>6413005</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1612,7 +1612,7 @@
         <v>126075295</v>
       </c>
       <c r="B11" t="n">
-        <v>105274</v>
+        <v>105275</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
         <v>126075351</v>
       </c>
       <c r="B12" t="n">
-        <v>106620</v>
+        <v>106621</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1811,10 +1811,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126075422</v>
+        <v>126075247</v>
       </c>
       <c r="B13" t="n">
-        <v>106166</v>
+        <v>96399</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1822,21 +1822,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221903</v>
+        <v>588</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Kalkkoppmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Entosthodon muhlenbergii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Turner) Fife</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>723297</v>
+        <v>723305</v>
       </c>
       <c r="R13" t="n">
-        <v>6412905</v>
+        <v>6412901</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1912,10 +1912,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126075046</v>
+        <v>126075422</v>
       </c>
       <c r="B14" t="n">
-        <v>109151</v>
+        <v>106167</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1923,16 +1923,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220299</v>
+        <v>221903</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1947,10 +1947,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>723345</v>
+        <v>723297</v>
       </c>
       <c r="R14" t="n">
-        <v>6413172</v>
+        <v>6412905</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2013,10 +2013,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126075247</v>
+        <v>126075046</v>
       </c>
       <c r="B15" t="n">
-        <v>96398</v>
+        <v>109152</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2024,21 +2024,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>588</v>
+        <v>220299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kalkkoppmossa</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Entosthodon muhlenbergii</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Turner) Fife</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2048,10 +2048,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>723305</v>
+        <v>723345</v>
       </c>
       <c r="R15" t="n">
-        <v>6412901</v>
+        <v>6413172</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2114,59 +2114,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126075072</v>
+        <v>126075228</v>
       </c>
       <c r="B16" t="n">
-        <v>57648</v>
+        <v>75006</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>6426</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Hemhagen, Nors, Gtl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>723335</v>
+        <v>723347</v>
       </c>
       <c r="R16" t="n">
-        <v>6413183</v>
+        <v>6413067</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2199,11 +2185,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-05-16</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Lockläte i lämplig biotop, senvuxna tallar med spår av spår av spillkråka, enstaka äldre potentiella boträd i skogen.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2234,45 +2215,59 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126075228</v>
+        <v>126075072</v>
       </c>
       <c r="B17" t="n">
-        <v>75006</v>
+        <v>57648</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6426</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Hemhagen, Nors, Gtl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>723347</v>
+        <v>723335</v>
       </c>
       <c r="R17" t="n">
-        <v>6413067</v>
+        <v>6413183</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2305,6 +2300,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Lockläte i lämplig biotop, senvuxna tallar med spår av spår av spillkråka, enstaka äldre potentiella boträd i skogen.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2335,10 +2335,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126075192</v>
+        <v>126075420</v>
       </c>
       <c r="B18" t="n">
-        <v>103781</v>
+        <v>106167</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2346,19 +2346,23 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>224416</v>
+        <v>221903</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ljus solvända</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. nummularium</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
+          <t>Veronica spicata</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2366,10 +2370,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>723305</v>
+        <v>723302</v>
       </c>
       <c r="R18" t="n">
-        <v>6412896</v>
+        <v>6412899</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2435,7 +2439,7 @@
         <v>126075041</v>
       </c>
       <c r="B19" t="n">
-        <v>109151</v>
+        <v>109152</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2533,10 +2537,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126075420</v>
+        <v>126075192</v>
       </c>
       <c r="B20" t="n">
-        <v>106166</v>
+        <v>103782</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2544,23 +2548,19 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221903</v>
+        <v>224416</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Ljus solvända</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2568,10 +2568,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>723302</v>
+        <v>723305</v>
       </c>
       <c r="R20" t="n">
-        <v>6412899</v>
+        <v>6412896</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2637,7 +2637,7 @@
         <v>126075050</v>
       </c>
       <c r="B21" t="n">
-        <v>109151</v>
+        <v>109152</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         <v>126075043</v>
       </c>
       <c r="B22" t="n">
-        <v>109151</v>
+        <v>109152</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2839,7 +2839,7 @@
         <v>126075053</v>
       </c>
       <c r="B23" t="n">
-        <v>109151</v>
+        <v>109152</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2940,7 +2940,7 @@
         <v>126075040</v>
       </c>
       <c r="B24" t="n">
-        <v>109151</v>
+        <v>109152</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3038,10 +3038,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126075095</v>
+        <v>126075330</v>
       </c>
       <c r="B25" t="n">
-        <v>98366</v>
+        <v>95942</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3049,39 +3049,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>219864</v>
+        <v>2180</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Hemhagen, Nors, Gtl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>723328</v>
+        <v>723341</v>
       </c>
       <c r="R25" t="n">
-        <v>6412904</v>
+        <v>6413230</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3144,27 +3139,27 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126075052</v>
+        <v>126075095</v>
       </c>
       <c r="B26" t="n">
-        <v>109151</v>
+        <v>98367</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220299</v>
+        <v>219864</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3173,16 +3168,21 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Hemhagen, Nors, Gtl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>723338</v>
+        <v>723328</v>
       </c>
       <c r="R26" t="n">
-        <v>6413224</v>
+        <v>6412904</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3245,10 +3245,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126075049</v>
+        <v>126075052</v>
       </c>
       <c r="B27" t="n">
-        <v>109151</v>
+        <v>109152</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3280,10 +3280,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>723331</v>
+        <v>723338</v>
       </c>
       <c r="R27" t="n">
-        <v>6413195</v>
+        <v>6413224</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3346,10 +3346,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126075193</v>
+        <v>126075049</v>
       </c>
       <c r="B28" t="n">
-        <v>103781</v>
+        <v>109152</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3357,19 +3357,23 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>224416</v>
+        <v>220299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ljus solvända</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. nummularium</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr"/>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3377,10 +3381,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>723321</v>
+        <v>723331</v>
       </c>
       <c r="R28" t="n">
-        <v>6412898</v>
+        <v>6413195</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3443,10 +3447,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126075357</v>
+        <v>126075193</v>
       </c>
       <c r="B29" t="n">
-        <v>106620</v>
+        <v>103782</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3454,23 +3458,19 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221849</v>
+        <v>224416</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Ljus solvända</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3478,10 +3478,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>723324</v>
+        <v>723321</v>
       </c>
       <c r="R29" t="n">
-        <v>6412899</v>
+        <v>6412898</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3544,32 +3544,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126075330</v>
+        <v>126075357</v>
       </c>
       <c r="B30" t="n">
-        <v>95941</v>
+        <v>106621</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2180</v>
+        <v>221849</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3579,10 +3579,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>723341</v>
+        <v>723324</v>
       </c>
       <c r="R30" t="n">
-        <v>6413230</v>
+        <v>6412899</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3648,7 +3648,7 @@
         <v>126075188</v>
       </c>
       <c r="B31" t="n">
-        <v>103781</v>
+        <v>103782</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3745,7 +3745,7 @@
         <v>126075189</v>
       </c>
       <c r="B32" t="n">
-        <v>103781</v>
+        <v>103782</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3842,7 +3842,7 @@
         <v>126075185</v>
       </c>
       <c r="B33" t="n">
-        <v>103781</v>
+        <v>103782</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3939,7 +3939,7 @@
         <v>126075054</v>
       </c>
       <c r="B34" t="n">
-        <v>109151</v>
+        <v>109152</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4040,7 +4040,7 @@
         <v>126075031</v>
       </c>
       <c r="B35" t="n">
-        <v>109151</v>
+        <v>109152</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4141,7 +4141,7 @@
         <v>126075328</v>
       </c>
       <c r="B36" t="n">
-        <v>100520</v>
+        <v>100521</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4242,7 +4242,7 @@
         <v>126075421</v>
       </c>
       <c r="B37" t="n">
-        <v>106166</v>
+        <v>106167</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4459,7 +4459,7 @@
         <v>126075028</v>
       </c>
       <c r="B39" t="n">
-        <v>109151</v>
+        <v>109152</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4560,7 +4560,7 @@
         <v>126075039</v>
       </c>
       <c r="B40" t="n">
-        <v>109151</v>
+        <v>109152</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4661,7 +4661,7 @@
         <v>126075042</v>
       </c>
       <c r="B41" t="n">
-        <v>109151</v>
+        <v>109152</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4762,7 +4762,7 @@
         <v>126075030</v>
       </c>
       <c r="B42" t="n">
-        <v>109151</v>
+        <v>109152</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4863,7 +4863,7 @@
         <v>126075269</v>
       </c>
       <c r="B43" t="n">
-        <v>107209</v>
+        <v>107210</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4961,10 +4961,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126075044</v>
+        <v>126075184</v>
       </c>
       <c r="B44" t="n">
-        <v>109151</v>
+        <v>103782</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4972,23 +4972,19 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220299</v>
+        <v>224416</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Ljus solvända</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -4996,10 +4992,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>723367</v>
+        <v>723240</v>
       </c>
       <c r="R44" t="n">
-        <v>6413134</v>
+        <v>6413005</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5062,10 +5058,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126075184</v>
+        <v>126075044</v>
       </c>
       <c r="B45" t="n">
-        <v>103781</v>
+        <v>109152</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5073,19 +5069,23 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>224416</v>
+        <v>220299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ljus solvända</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. nummularium</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr"/>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5093,10 +5093,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>723240</v>
+        <v>723367</v>
       </c>
       <c r="R45" t="n">
-        <v>6413005</v>
+        <v>6413134</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5159,10 +5159,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126075412</v>
+        <v>126075182</v>
       </c>
       <c r="B46" t="n">
-        <v>106166</v>
+        <v>103782</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5170,23 +5170,19 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>221903</v>
+        <v>224416</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Ljus solvända</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5194,10 +5190,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>723243</v>
+        <v>723272</v>
       </c>
       <c r="R46" t="n">
-        <v>6413018</v>
+        <v>6413033</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5260,10 +5256,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126075182</v>
+        <v>126075412</v>
       </c>
       <c r="B47" t="n">
-        <v>103781</v>
+        <v>106167</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5271,19 +5267,23 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>224416</v>
+        <v>221903</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ljus solvända</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. nummularium</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr"/>
+          <t>Veronica spicata</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5291,10 +5291,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>723272</v>
+        <v>723243</v>
       </c>
       <c r="R47" t="n">
-        <v>6413033</v>
+        <v>6413018</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5360,7 +5360,7 @@
         <v>126075045</v>
       </c>
       <c r="B48" t="n">
-        <v>109151</v>
+        <v>109152</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5458,27 +5458,27 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126075047</v>
+        <v>126075096</v>
       </c>
       <c r="B49" t="n">
-        <v>109151</v>
+        <v>98367</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220299</v>
+        <v>219864</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -5487,16 +5487,21 @@
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Hemhagen, Nors, Gtl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>723335</v>
+        <v>723293</v>
       </c>
       <c r="R49" t="n">
-        <v>6413175</v>
+        <v>6412906</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5559,27 +5564,27 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126075096</v>
+        <v>126075047</v>
       </c>
       <c r="B50" t="n">
-        <v>98366</v>
+        <v>109152</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>219864</v>
+        <v>220299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -5588,21 +5593,16 @@
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Hemhagen, Nors, Gtl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>723293</v>
+        <v>723335</v>
       </c>
       <c r="R50" t="n">
-        <v>6412906</v>
+        <v>6413175</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5668,7 +5668,7 @@
         <v>126075029</v>
       </c>
       <c r="B51" t="n">
-        <v>109151</v>
+        <v>109152</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>

--- a/artfynd/A 15629-2024 artfynd.xlsx
+++ b/artfynd/A 15629-2024 artfynd.xlsx
@@ -1301,10 +1301,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126075088</v>
+        <v>126075294</v>
       </c>
       <c r="B8" t="n">
-        <v>98367</v>
+        <v>105275</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1312,16 +1312,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219864</v>
+        <v>221141</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1330,21 +1330,16 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hemhagen, Nors, Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>723278</v>
+        <v>723318</v>
       </c>
       <c r="R8" t="n">
-        <v>6413037</v>
+        <v>6412902</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1407,27 +1402,27 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126075294</v>
+        <v>126075038</v>
       </c>
       <c r="B9" t="n">
-        <v>105275</v>
+        <v>109152</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221141</v>
+        <v>220299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1442,10 +1437,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>723318</v>
+        <v>723299</v>
       </c>
       <c r="R9" t="n">
-        <v>6412902</v>
+        <v>6413005</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1508,27 +1503,27 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126075038</v>
+        <v>126075088</v>
       </c>
       <c r="B10" t="n">
-        <v>109152</v>
+        <v>98367</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220299</v>
+        <v>219864</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1537,16 +1532,21 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hemhagen, Nors, Gtl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>723299</v>
+        <v>723278</v>
       </c>
       <c r="R10" t="n">
-        <v>6413005</v>
+        <v>6413037</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -3038,10 +3038,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126075330</v>
+        <v>126075095</v>
       </c>
       <c r="B25" t="n">
-        <v>95942</v>
+        <v>98367</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3049,34 +3049,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2180</v>
+        <v>219864</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Hemhagen, Nors, Gtl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>723341</v>
+        <v>723328</v>
       </c>
       <c r="R25" t="n">
-        <v>6413230</v>
+        <v>6412904</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3139,10 +3144,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126075095</v>
+        <v>126075330</v>
       </c>
       <c r="B26" t="n">
-        <v>98367</v>
+        <v>95942</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3150,39 +3155,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>219864</v>
+        <v>2180</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Hemhagen, Nors, Gtl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>723328</v>
+        <v>723341</v>
       </c>
       <c r="R26" t="n">
-        <v>6412904</v>
+        <v>6413230</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3245,10 +3245,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126075052</v>
+        <v>126075193</v>
       </c>
       <c r="B27" t="n">
-        <v>109152</v>
+        <v>103782</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3256,23 +3256,19 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220299</v>
+        <v>224416</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Ljus solvända</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3280,10 +3276,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>723338</v>
+        <v>723321</v>
       </c>
       <c r="R27" t="n">
-        <v>6413224</v>
+        <v>6412898</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3346,10 +3342,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126075049</v>
+        <v>126075357</v>
       </c>
       <c r="B28" t="n">
-        <v>109152</v>
+        <v>106621</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3357,16 +3353,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220299</v>
+        <v>221849</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3381,10 +3377,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>723331</v>
+        <v>723324</v>
       </c>
       <c r="R28" t="n">
-        <v>6413195</v>
+        <v>6412899</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3447,10 +3443,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126075193</v>
+        <v>126075052</v>
       </c>
       <c r="B29" t="n">
-        <v>103782</v>
+        <v>109152</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3458,19 +3454,23 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>224416</v>
+        <v>220299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ljus solvända</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. nummularium</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3478,10 +3478,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>723321</v>
+        <v>723338</v>
       </c>
       <c r="R29" t="n">
-        <v>6412898</v>
+        <v>6413224</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3544,10 +3544,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126075357</v>
+        <v>126075049</v>
       </c>
       <c r="B30" t="n">
-        <v>106621</v>
+        <v>109152</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3555,16 +3555,16 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221849</v>
+        <v>220299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3579,10 +3579,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>723324</v>
+        <v>723331</v>
       </c>
       <c r="R30" t="n">
-        <v>6412899</v>
+        <v>6413195</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>

--- a/artfynd/A 15629-2024 artfynd.xlsx
+++ b/artfynd/A 15629-2024 artfynd.xlsx
@@ -1301,10 +1301,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126075294</v>
+        <v>126075088</v>
       </c>
       <c r="B8" t="n">
-        <v>105275</v>
+        <v>98367</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1312,16 +1312,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221141</v>
+        <v>219864</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1330,16 +1330,21 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hemhagen, Nors, Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>723318</v>
+        <v>723278</v>
       </c>
       <c r="R8" t="n">
-        <v>6412902</v>
+        <v>6413037</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1402,27 +1407,27 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126075038</v>
+        <v>126075294</v>
       </c>
       <c r="B9" t="n">
-        <v>109152</v>
+        <v>105275</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220299</v>
+        <v>221141</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1437,10 +1442,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>723299</v>
+        <v>723318</v>
       </c>
       <c r="R9" t="n">
-        <v>6413005</v>
+        <v>6412902</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1503,27 +1508,27 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126075088</v>
+        <v>126075038</v>
       </c>
       <c r="B10" t="n">
-        <v>98367</v>
+        <v>109152</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219864</v>
+        <v>220299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1532,21 +1537,16 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hemhagen, Nors, Gtl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>723278</v>
+        <v>723299</v>
       </c>
       <c r="R10" t="n">
-        <v>6413037</v>
+        <v>6413005</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -2335,10 +2335,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126075420</v>
+        <v>126075192</v>
       </c>
       <c r="B18" t="n">
-        <v>106167</v>
+        <v>103782</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2346,23 +2346,19 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221903</v>
+        <v>224416</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Ljus solvända</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2370,10 +2366,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>723302</v>
+        <v>723305</v>
       </c>
       <c r="R18" t="n">
-        <v>6412899</v>
+        <v>6412896</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2436,10 +2432,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126075041</v>
+        <v>126075420</v>
       </c>
       <c r="B19" t="n">
-        <v>109152</v>
+        <v>106167</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2447,16 +2443,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220299</v>
+        <v>221903</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2471,10 +2467,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>723339</v>
+        <v>723302</v>
       </c>
       <c r="R19" t="n">
-        <v>6413055</v>
+        <v>6412899</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2537,10 +2533,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126075192</v>
+        <v>126075041</v>
       </c>
       <c r="B20" t="n">
-        <v>103782</v>
+        <v>109152</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2548,19 +2544,23 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>224416</v>
+        <v>220299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ljus solvända</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. nummularium</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr"/>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2568,10 +2568,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>723305</v>
+        <v>723339</v>
       </c>
       <c r="R20" t="n">
-        <v>6412896</v>
+        <v>6413055</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3038,10 +3038,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126075095</v>
+        <v>126075330</v>
       </c>
       <c r="B25" t="n">
-        <v>98367</v>
+        <v>95942</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3049,39 +3049,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>219864</v>
+        <v>2180</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Hemhagen, Nors, Gtl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>723328</v>
+        <v>723341</v>
       </c>
       <c r="R25" t="n">
-        <v>6412904</v>
+        <v>6413230</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3144,10 +3139,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126075330</v>
+        <v>126075095</v>
       </c>
       <c r="B26" t="n">
-        <v>95942</v>
+        <v>98367</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3155,34 +3150,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2180</v>
+        <v>219864</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Hemhagen, Nors, Gtl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>723341</v>
+        <v>723328</v>
       </c>
       <c r="R26" t="n">
-        <v>6413230</v>
+        <v>6412904</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3245,10 +3245,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126075193</v>
+        <v>126075052</v>
       </c>
       <c r="B27" t="n">
-        <v>103782</v>
+        <v>109152</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3256,19 +3256,23 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>224416</v>
+        <v>220299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ljus solvända</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. nummularium</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr"/>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3276,10 +3280,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>723321</v>
+        <v>723338</v>
       </c>
       <c r="R27" t="n">
-        <v>6412898</v>
+        <v>6413224</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3342,10 +3346,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126075357</v>
+        <v>126075049</v>
       </c>
       <c r="B28" t="n">
-        <v>106621</v>
+        <v>109152</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3353,16 +3357,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221849</v>
+        <v>220299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3377,10 +3381,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>723324</v>
+        <v>723331</v>
       </c>
       <c r="R28" t="n">
-        <v>6412899</v>
+        <v>6413195</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3443,10 +3447,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126075052</v>
+        <v>126075193</v>
       </c>
       <c r="B29" t="n">
-        <v>109152</v>
+        <v>103782</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3454,23 +3458,19 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220299</v>
+        <v>224416</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Ljus solvända</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3478,10 +3478,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>723338</v>
+        <v>723321</v>
       </c>
       <c r="R29" t="n">
-        <v>6413224</v>
+        <v>6412898</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3544,10 +3544,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126075049</v>
+        <v>126075357</v>
       </c>
       <c r="B30" t="n">
-        <v>109152</v>
+        <v>106621</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3555,16 +3555,16 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220299</v>
+        <v>221849</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3579,10 +3579,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>723331</v>
+        <v>723324</v>
       </c>
       <c r="R30" t="n">
-        <v>6413195</v>
+        <v>6412899</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>

--- a/artfynd/A 15629-2024 artfynd.xlsx
+++ b/artfynd/A 15629-2024 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>126075195</v>
       </c>
       <c r="B3" t="n">
-        <v>103782</v>
+        <v>103784</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126075167</v>
+        <v>126075089</v>
       </c>
       <c r="B4" t="n">
-        <v>98361</v>
+        <v>98369</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -903,34 +903,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219862</v>
+        <v>219864</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Hemhagen, Nors, Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>723327</v>
+        <v>723237</v>
       </c>
       <c r="R4" t="n">
-        <v>6413202</v>
+        <v>6413005</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +998,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126075089</v>
+        <v>126075167</v>
       </c>
       <c r="B5" t="n">
-        <v>98367</v>
+        <v>98363</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1004,39 +1009,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219864</v>
+        <v>219862</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hemhagen, Nors, Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>723237</v>
+        <v>723327</v>
       </c>
       <c r="R5" t="n">
-        <v>6413005</v>
+        <v>6413202</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126075032</v>
+        <v>126075055</v>
       </c>
       <c r="B6" t="n">
-        <v>109152</v>
+        <v>109154</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>723222</v>
+        <v>723291</v>
       </c>
       <c r="R6" t="n">
-        <v>6412868</v>
+        <v>6413160</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1164,12 +1164,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126075055</v>
+        <v>126075032</v>
       </c>
       <c r="B7" t="n">
-        <v>109152</v>
+        <v>109154</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1235,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>723291</v>
+        <v>723222</v>
       </c>
       <c r="R7" t="n">
-        <v>6413160</v>
+        <v>6412868</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1265,12 +1265,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1304,7 +1304,7 @@
         <v>126075088</v>
       </c>
       <c r="B8" t="n">
-        <v>98367</v>
+        <v>98369</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1407,27 +1407,27 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126075294</v>
+        <v>126075038</v>
       </c>
       <c r="B9" t="n">
-        <v>105275</v>
+        <v>109154</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221141</v>
+        <v>220299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1442,10 +1442,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>723318</v>
+        <v>723299</v>
       </c>
       <c r="R9" t="n">
-        <v>6412902</v>
+        <v>6413005</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1508,27 +1508,27 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126075038</v>
+        <v>126075294</v>
       </c>
       <c r="B10" t="n">
-        <v>109152</v>
+        <v>105277</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220299</v>
+        <v>221141</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1543,10 +1543,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>723299</v>
+        <v>723318</v>
       </c>
       <c r="R10" t="n">
-        <v>6413005</v>
+        <v>6412902</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1612,7 +1612,7 @@
         <v>126075295</v>
       </c>
       <c r="B11" t="n">
-        <v>105275</v>
+        <v>105277</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
         <v>126075351</v>
       </c>
       <c r="B12" t="n">
-        <v>106621</v>
+        <v>106623</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         <v>126075247</v>
       </c>
       <c r="B13" t="n">
-        <v>96399</v>
+        <v>96401</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>126075422</v>
       </c>
       <c r="B14" t="n">
-        <v>106167</v>
+        <v>106169</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
         <v>126075046</v>
       </c>
       <c r="B15" t="n">
-        <v>109152</v>
+        <v>109154</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2114,45 +2114,59 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126075228</v>
+        <v>126075072</v>
       </c>
       <c r="B16" t="n">
-        <v>75006</v>
+        <v>57649</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6426</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Hemhagen, Nors, Gtl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>723347</v>
+        <v>723335</v>
       </c>
       <c r="R16" t="n">
-        <v>6413067</v>
+        <v>6413183</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2185,6 +2199,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Lockläte i lämplig biotop, senvuxna tallar med spår av spår av spillkråka, enstaka äldre potentiella boträd i skogen.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2215,59 +2234,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126075072</v>
+        <v>126075228</v>
       </c>
       <c r="B17" t="n">
-        <v>57648</v>
+        <v>75007</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>6426</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Hemhagen, Nors, Gtl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>723335</v>
+        <v>723347</v>
       </c>
       <c r="R17" t="n">
-        <v>6413183</v>
+        <v>6413067</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2300,11 +2305,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-05-16</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Lockläte i lämplig biotop, senvuxna tallar med spår av spår av spillkråka, enstaka äldre potentiella boträd i skogen.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2335,10 +2335,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126075192</v>
+        <v>126075041</v>
       </c>
       <c r="B18" t="n">
-        <v>103782</v>
+        <v>109154</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2346,19 +2346,23 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>224416</v>
+        <v>220299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ljus solvända</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. nummularium</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2366,10 +2370,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>723305</v>
+        <v>723339</v>
       </c>
       <c r="R18" t="n">
-        <v>6412896</v>
+        <v>6413055</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2435,7 +2439,7 @@
         <v>126075420</v>
       </c>
       <c r="B19" t="n">
-        <v>106167</v>
+        <v>106169</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2533,10 +2537,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126075041</v>
+        <v>126075192</v>
       </c>
       <c r="B20" t="n">
-        <v>109152</v>
+        <v>103784</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2544,23 +2548,19 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220299</v>
+        <v>224416</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Ljus solvända</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2568,10 +2568,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>723339</v>
+        <v>723305</v>
       </c>
       <c r="R20" t="n">
-        <v>6413055</v>
+        <v>6412896</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2637,7 +2637,7 @@
         <v>126075050</v>
       </c>
       <c r="B21" t="n">
-        <v>109152</v>
+        <v>109154</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         <v>126075043</v>
       </c>
       <c r="B22" t="n">
-        <v>109152</v>
+        <v>109154</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2839,7 +2839,7 @@
         <v>126075053</v>
       </c>
       <c r="B23" t="n">
-        <v>109152</v>
+        <v>109154</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2940,7 +2940,7 @@
         <v>126075040</v>
       </c>
       <c r="B24" t="n">
-        <v>109152</v>
+        <v>109154</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3038,10 +3038,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126075330</v>
+        <v>126075095</v>
       </c>
       <c r="B25" t="n">
-        <v>95942</v>
+        <v>98369</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3049,34 +3049,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2180</v>
+        <v>219864</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Hemhagen, Nors, Gtl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>723341</v>
+        <v>723328</v>
       </c>
       <c r="R25" t="n">
-        <v>6413230</v>
+        <v>6412904</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3139,10 +3144,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126075095</v>
+        <v>126075330</v>
       </c>
       <c r="B26" t="n">
-        <v>98367</v>
+        <v>95944</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3150,39 +3155,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>219864</v>
+        <v>2180</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Hemhagen, Nors, Gtl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>723328</v>
+        <v>723341</v>
       </c>
       <c r="R26" t="n">
-        <v>6412904</v>
+        <v>6413230</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3248,7 +3248,7 @@
         <v>126075052</v>
       </c>
       <c r="B27" t="n">
-        <v>109152</v>
+        <v>109154</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3349,7 +3349,7 @@
         <v>126075049</v>
       </c>
       <c r="B28" t="n">
-        <v>109152</v>
+        <v>109154</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3447,10 +3447,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126075193</v>
+        <v>126075357</v>
       </c>
       <c r="B29" t="n">
-        <v>103782</v>
+        <v>106623</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3458,19 +3458,23 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>224416</v>
+        <v>221849</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ljus solvända</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. nummularium</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3478,10 +3482,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>723321</v>
+        <v>723324</v>
       </c>
       <c r="R29" t="n">
-        <v>6412898</v>
+        <v>6412899</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3544,10 +3548,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126075357</v>
+        <v>126075193</v>
       </c>
       <c r="B30" t="n">
-        <v>106621</v>
+        <v>103784</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3555,23 +3559,19 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221849</v>
+        <v>224416</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Ljus solvända</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3579,10 +3579,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>723324</v>
+        <v>723321</v>
       </c>
       <c r="R30" t="n">
-        <v>6412899</v>
+        <v>6412898</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3648,7 +3648,7 @@
         <v>126075188</v>
       </c>
       <c r="B31" t="n">
-        <v>103782</v>
+        <v>103784</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3745,7 +3745,7 @@
         <v>126075189</v>
       </c>
       <c r="B32" t="n">
-        <v>103782</v>
+        <v>103784</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3842,7 +3842,7 @@
         <v>126075185</v>
       </c>
       <c r="B33" t="n">
-        <v>103782</v>
+        <v>103784</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3939,7 +3939,7 @@
         <v>126075054</v>
       </c>
       <c r="B34" t="n">
-        <v>109152</v>
+        <v>109154</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4037,32 +4037,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126075031</v>
+        <v>126075328</v>
       </c>
       <c r="B35" t="n">
-        <v>109152</v>
+        <v>100523</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220299</v>
+        <v>222498</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4072,10 +4072,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>723216</v>
+        <v>723335</v>
       </c>
       <c r="R35" t="n">
-        <v>6412876</v>
+        <v>6413175</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4138,32 +4138,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126075328</v>
+        <v>126075031</v>
       </c>
       <c r="B36" t="n">
-        <v>100521</v>
+        <v>109154</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>222498</v>
+        <v>220299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4173,10 +4173,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>723335</v>
+        <v>723216</v>
       </c>
       <c r="R36" t="n">
-        <v>6413175</v>
+        <v>6412876</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4242,7 +4242,7 @@
         <v>126075421</v>
       </c>
       <c r="B37" t="n">
-        <v>106167</v>
+        <v>106169</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4459,7 +4459,7 @@
         <v>126075028</v>
       </c>
       <c r="B39" t="n">
-        <v>109152</v>
+        <v>109154</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4560,7 +4560,7 @@
         <v>126075039</v>
       </c>
       <c r="B40" t="n">
-        <v>109152</v>
+        <v>109154</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4661,7 +4661,7 @@
         <v>126075042</v>
       </c>
       <c r="B41" t="n">
-        <v>109152</v>
+        <v>109154</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4762,7 +4762,7 @@
         <v>126075030</v>
       </c>
       <c r="B42" t="n">
-        <v>109152</v>
+        <v>109154</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4860,10 +4860,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126075269</v>
+        <v>126075184</v>
       </c>
       <c r="B43" t="n">
-        <v>107210</v>
+        <v>103784</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4871,23 +4871,19 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220079</v>
+        <v>224416</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Ljus solvända</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -4895,10 +4891,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>723282</v>
+        <v>723240</v>
       </c>
       <c r="R43" t="n">
-        <v>6413048</v>
+        <v>6413005</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4961,10 +4957,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126075184</v>
+        <v>126075269</v>
       </c>
       <c r="B44" t="n">
-        <v>103782</v>
+        <v>107212</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4972,19 +4968,23 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>224416</v>
+        <v>220079</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ljus solvända</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. nummularium</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr"/>
+          <t>Cirsium acaule</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -4992,10 +4992,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>723240</v>
+        <v>723282</v>
       </c>
       <c r="R44" t="n">
-        <v>6413005</v>
+        <v>6413048</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5061,7 +5061,7 @@
         <v>126075044</v>
       </c>
       <c r="B45" t="n">
-        <v>109152</v>
+        <v>109154</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5162,7 +5162,7 @@
         <v>126075182</v>
       </c>
       <c r="B46" t="n">
-        <v>103782</v>
+        <v>103784</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5256,10 +5256,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126075412</v>
+        <v>126075045</v>
       </c>
       <c r="B47" t="n">
-        <v>106167</v>
+        <v>109154</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5267,16 +5267,16 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221903</v>
+        <v>220299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -5291,10 +5291,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>723243</v>
+        <v>723352</v>
       </c>
       <c r="R47" t="n">
-        <v>6413018</v>
+        <v>6413153</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5357,10 +5357,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126075045</v>
+        <v>126075412</v>
       </c>
       <c r="B48" t="n">
-        <v>109152</v>
+        <v>106169</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5368,16 +5368,16 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220299</v>
+        <v>221903</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -5392,10 +5392,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>723352</v>
+        <v>723243</v>
       </c>
       <c r="R48" t="n">
-        <v>6413153</v>
+        <v>6413018</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5461,7 +5461,7 @@
         <v>126075096</v>
       </c>
       <c r="B49" t="n">
-        <v>98367</v>
+        <v>98369</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5567,7 +5567,7 @@
         <v>126075047</v>
       </c>
       <c r="B50" t="n">
-        <v>109152</v>
+        <v>109154</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5668,7 +5668,7 @@
         <v>126075029</v>
       </c>
       <c r="B51" t="n">
-        <v>109152</v>
+        <v>109154</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>

--- a/artfynd/A 15629-2024 artfynd.xlsx
+++ b/artfynd/A 15629-2024 artfynd.xlsx
@@ -1811,10 +1811,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126075247</v>
+        <v>126075046</v>
       </c>
       <c r="B13" t="n">
-        <v>96401</v>
+        <v>109154</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1822,21 +1822,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>588</v>
+        <v>220299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kalkkoppmossa</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Entosthodon muhlenbergii</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Turner) Fife</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>723305</v>
+        <v>723345</v>
       </c>
       <c r="R13" t="n">
-        <v>6412901</v>
+        <v>6413172</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1912,10 +1912,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126075422</v>
+        <v>126075247</v>
       </c>
       <c r="B14" t="n">
-        <v>106169</v>
+        <v>96401</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1923,21 +1923,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221903</v>
+        <v>588</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Kalkkoppmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Entosthodon muhlenbergii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Turner) Fife</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1947,10 +1947,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>723297</v>
+        <v>723305</v>
       </c>
       <c r="R14" t="n">
-        <v>6412905</v>
+        <v>6412901</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2013,10 +2013,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126075046</v>
+        <v>126075422</v>
       </c>
       <c r="B15" t="n">
-        <v>109154</v>
+        <v>106169</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2024,16 +2024,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220299</v>
+        <v>221903</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2048,10 +2048,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>723345</v>
+        <v>723297</v>
       </c>
       <c r="R15" t="n">
-        <v>6413172</v>
+        <v>6412905</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -3038,27 +3038,27 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126075095</v>
+        <v>126075052</v>
       </c>
       <c r="B25" t="n">
-        <v>98369</v>
+        <v>109154</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>219864</v>
+        <v>220299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3067,21 +3067,16 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Hemhagen, Nors, Gtl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>723328</v>
+        <v>723338</v>
       </c>
       <c r="R25" t="n">
-        <v>6412904</v>
+        <v>6413224</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3144,32 +3139,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126075330</v>
+        <v>126075049</v>
       </c>
       <c r="B26" t="n">
-        <v>95944</v>
+        <v>109154</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2180</v>
+        <v>220299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3179,10 +3174,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>723341</v>
+        <v>723331</v>
       </c>
       <c r="R26" t="n">
-        <v>6413230</v>
+        <v>6413195</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3245,10 +3240,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126075052</v>
+        <v>126075193</v>
       </c>
       <c r="B27" t="n">
-        <v>109154</v>
+        <v>103784</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3256,23 +3251,19 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220299</v>
+        <v>224416</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Ljus solvända</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3280,10 +3271,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>723338</v>
+        <v>723321</v>
       </c>
       <c r="R27" t="n">
-        <v>6413224</v>
+        <v>6412898</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3346,32 +3337,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126075049</v>
+        <v>126075330</v>
       </c>
       <c r="B28" t="n">
-        <v>109154</v>
+        <v>95944</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220299</v>
+        <v>2180</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3381,10 +3372,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>723331</v>
+        <v>723341</v>
       </c>
       <c r="R28" t="n">
-        <v>6413195</v>
+        <v>6413230</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3447,27 +3438,27 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126075357</v>
+        <v>126075095</v>
       </c>
       <c r="B29" t="n">
-        <v>106623</v>
+        <v>98369</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221849</v>
+        <v>219864</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3476,16 +3467,21 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Hemhagen, Nors, Gtl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>723324</v>
+        <v>723328</v>
       </c>
       <c r="R29" t="n">
-        <v>6412899</v>
+        <v>6412904</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3548,10 +3544,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126075193</v>
+        <v>126075357</v>
       </c>
       <c r="B30" t="n">
-        <v>103784</v>
+        <v>106623</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3559,19 +3555,23 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>224416</v>
+        <v>221849</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ljus solvända</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. nummularium</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr"/>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3579,10 +3579,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>723321</v>
+        <v>723324</v>
       </c>
       <c r="R30" t="n">
-        <v>6412898</v>
+        <v>6412899</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4037,32 +4037,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126075328</v>
+        <v>126075031</v>
       </c>
       <c r="B35" t="n">
-        <v>100523</v>
+        <v>109154</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>222498</v>
+        <v>220299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4072,10 +4072,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>723335</v>
+        <v>723216</v>
       </c>
       <c r="R35" t="n">
-        <v>6413175</v>
+        <v>6412876</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4138,32 +4138,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126075031</v>
+        <v>126075328</v>
       </c>
       <c r="B36" t="n">
-        <v>109154</v>
+        <v>100523</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220299</v>
+        <v>222498</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4173,10 +4173,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>723216</v>
+        <v>723335</v>
       </c>
       <c r="R36" t="n">
-        <v>6412876</v>
+        <v>6413175</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>

--- a/artfynd/A 15629-2024 artfynd.xlsx
+++ b/artfynd/A 15629-2024 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>126075195</v>
       </c>
       <c r="B3" t="n">
-        <v>103784</v>
+        <v>103786</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126075089</v>
+        <v>126075167</v>
       </c>
       <c r="B4" t="n">
-        <v>98369</v>
+        <v>98365</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -903,39 +903,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219864</v>
+        <v>219862</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Hemhagen, Nors, Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>723237</v>
+        <v>723327</v>
       </c>
       <c r="R4" t="n">
-        <v>6413005</v>
+        <v>6413202</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -998,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126075167</v>
+        <v>126075089</v>
       </c>
       <c r="B5" t="n">
-        <v>98363</v>
+        <v>98371</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1009,34 +1004,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219862</v>
+        <v>219864</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hemhagen, Nors, Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>723327</v>
+        <v>723237</v>
       </c>
       <c r="R5" t="n">
-        <v>6413202</v>
+        <v>6413005</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126075055</v>
+        <v>126075032</v>
       </c>
       <c r="B6" t="n">
-        <v>109154</v>
+        <v>109156</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>723291</v>
+        <v>723222</v>
       </c>
       <c r="R6" t="n">
-        <v>6413160</v>
+        <v>6412868</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1164,12 +1164,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126075032</v>
+        <v>126075055</v>
       </c>
       <c r="B7" t="n">
-        <v>109154</v>
+        <v>109156</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1235,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>723222</v>
+        <v>723291</v>
       </c>
       <c r="R7" t="n">
-        <v>6412868</v>
+        <v>6413160</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1265,12 +1265,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1304,7 +1304,7 @@
         <v>126075088</v>
       </c>
       <c r="B8" t="n">
-        <v>98369</v>
+        <v>98371</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1407,27 +1407,27 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126075038</v>
+        <v>126075294</v>
       </c>
       <c r="B9" t="n">
-        <v>109154</v>
+        <v>105279</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220299</v>
+        <v>221141</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1442,10 +1442,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>723299</v>
+        <v>723318</v>
       </c>
       <c r="R9" t="n">
-        <v>6413005</v>
+        <v>6412902</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1508,27 +1508,27 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126075294</v>
+        <v>126075038</v>
       </c>
       <c r="B10" t="n">
-        <v>105277</v>
+        <v>109156</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221141</v>
+        <v>220299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1543,10 +1543,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>723318</v>
+        <v>723299</v>
       </c>
       <c r="R10" t="n">
-        <v>6412902</v>
+        <v>6413005</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1612,7 +1612,7 @@
         <v>126075295</v>
       </c>
       <c r="B11" t="n">
-        <v>105277</v>
+        <v>105279</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
         <v>126075351</v>
       </c>
       <c r="B12" t="n">
-        <v>106623</v>
+        <v>106625</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1811,10 +1811,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126075046</v>
+        <v>126075247</v>
       </c>
       <c r="B13" t="n">
-        <v>109154</v>
+        <v>96403</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1822,21 +1822,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220299</v>
+        <v>588</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Kalkkoppmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Entosthodon muhlenbergii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Turner) Fife</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>723345</v>
+        <v>723305</v>
       </c>
       <c r="R13" t="n">
-        <v>6413172</v>
+        <v>6412901</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1912,10 +1912,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126075247</v>
+        <v>126075046</v>
       </c>
       <c r="B14" t="n">
-        <v>96401</v>
+        <v>109156</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1923,21 +1923,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>588</v>
+        <v>220299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kalkkoppmossa</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Entosthodon muhlenbergii</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Turner) Fife</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1947,10 +1947,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>723305</v>
+        <v>723345</v>
       </c>
       <c r="R14" t="n">
-        <v>6412901</v>
+        <v>6413172</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2016,7 +2016,7 @@
         <v>126075422</v>
       </c>
       <c r="B15" t="n">
-        <v>106169</v>
+        <v>106171</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2114,59 +2114,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126075072</v>
+        <v>126075228</v>
       </c>
       <c r="B16" t="n">
-        <v>57649</v>
+        <v>75007</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>6426</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Hemhagen, Nors, Gtl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>723335</v>
+        <v>723347</v>
       </c>
       <c r="R16" t="n">
-        <v>6413183</v>
+        <v>6413067</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2199,11 +2185,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-05-16</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Lockläte i lämplig biotop, senvuxna tallar med spår av spår av spillkråka, enstaka äldre potentiella boträd i skogen.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2234,45 +2215,59 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126075228</v>
+        <v>126075072</v>
       </c>
       <c r="B17" t="n">
-        <v>75007</v>
+        <v>57649</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6426</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Hemhagen, Nors, Gtl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>723347</v>
+        <v>723335</v>
       </c>
       <c r="R17" t="n">
-        <v>6413067</v>
+        <v>6413183</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2305,6 +2300,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Lockläte i lämplig biotop, senvuxna tallar med spår av spår av spillkråka, enstaka äldre potentiella boträd i skogen.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2338,7 +2338,7 @@
         <v>126075041</v>
       </c>
       <c r="B18" t="n">
-        <v>109154</v>
+        <v>109156</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2439,7 +2439,7 @@
         <v>126075420</v>
       </c>
       <c r="B19" t="n">
-        <v>106169</v>
+        <v>106171</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2540,7 +2540,7 @@
         <v>126075192</v>
       </c>
       <c r="B20" t="n">
-        <v>103784</v>
+        <v>103786</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2637,7 +2637,7 @@
         <v>126075050</v>
       </c>
       <c r="B21" t="n">
-        <v>109154</v>
+        <v>109156</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         <v>126075043</v>
       </c>
       <c r="B22" t="n">
-        <v>109154</v>
+        <v>109156</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2839,7 +2839,7 @@
         <v>126075053</v>
       </c>
       <c r="B23" t="n">
-        <v>109154</v>
+        <v>109156</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2940,7 +2940,7 @@
         <v>126075040</v>
       </c>
       <c r="B24" t="n">
-        <v>109154</v>
+        <v>109156</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3038,32 +3038,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126075052</v>
+        <v>126075330</v>
       </c>
       <c r="B25" t="n">
-        <v>109154</v>
+        <v>95946</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220299</v>
+        <v>2180</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3073,10 +3073,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>723338</v>
+        <v>723341</v>
       </c>
       <c r="R25" t="n">
-        <v>6413224</v>
+        <v>6413230</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3139,27 +3139,27 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126075049</v>
+        <v>126075095</v>
       </c>
       <c r="B26" t="n">
-        <v>109154</v>
+        <v>98371</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220299</v>
+        <v>219864</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3168,16 +3168,21 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Hemhagen, Nors, Gtl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>723331</v>
+        <v>723328</v>
       </c>
       <c r="R26" t="n">
-        <v>6413195</v>
+        <v>6412904</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3240,10 +3245,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126075193</v>
+        <v>126075052</v>
       </c>
       <c r="B27" t="n">
-        <v>103784</v>
+        <v>109156</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3251,19 +3256,23 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>224416</v>
+        <v>220299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ljus solvända</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. nummularium</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr"/>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3271,10 +3280,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>723321</v>
+        <v>723338</v>
       </c>
       <c r="R27" t="n">
-        <v>6412898</v>
+        <v>6413224</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3337,32 +3346,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126075330</v>
+        <v>126075049</v>
       </c>
       <c r="B28" t="n">
-        <v>95944</v>
+        <v>109156</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2180</v>
+        <v>220299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3372,10 +3381,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>723341</v>
+        <v>723331</v>
       </c>
       <c r="R28" t="n">
-        <v>6413230</v>
+        <v>6413195</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3438,27 +3447,27 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126075095</v>
+        <v>126075357</v>
       </c>
       <c r="B29" t="n">
-        <v>98369</v>
+        <v>106625</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>219864</v>
+        <v>221849</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3467,21 +3476,16 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Hemhagen, Nors, Gtl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>723328</v>
+        <v>723324</v>
       </c>
       <c r="R29" t="n">
-        <v>6412904</v>
+        <v>6412899</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3544,10 +3548,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126075357</v>
+        <v>126075193</v>
       </c>
       <c r="B30" t="n">
-        <v>106623</v>
+        <v>103786</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3555,23 +3559,19 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221849</v>
+        <v>224416</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Ljus solvända</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3579,10 +3579,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>723324</v>
+        <v>723321</v>
       </c>
       <c r="R30" t="n">
-        <v>6412899</v>
+        <v>6412898</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3645,10 +3645,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126075188</v>
+        <v>126075054</v>
       </c>
       <c r="B31" t="n">
-        <v>103784</v>
+        <v>109156</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3656,19 +3656,23 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>224416</v>
+        <v>220299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ljus solvända</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. nummularium</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr"/>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3676,10 +3680,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>723322</v>
+        <v>723389</v>
       </c>
       <c r="R31" t="n">
-        <v>6412738</v>
+        <v>6413195</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3742,10 +3746,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126075189</v>
+        <v>126075188</v>
       </c>
       <c r="B32" t="n">
-        <v>103784</v>
+        <v>103786</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3773,10 +3777,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>723328</v>
+        <v>723322</v>
       </c>
       <c r="R32" t="n">
-        <v>6412741</v>
+        <v>6412738</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3839,10 +3843,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126075185</v>
+        <v>126075189</v>
       </c>
       <c r="B33" t="n">
-        <v>103784</v>
+        <v>103786</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3870,10 +3874,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>723250</v>
+        <v>723328</v>
       </c>
       <c r="R33" t="n">
-        <v>6413023</v>
+        <v>6412741</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3936,10 +3940,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126075054</v>
+        <v>126075185</v>
       </c>
       <c r="B34" t="n">
-        <v>109154</v>
+        <v>103786</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3947,23 +3951,19 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220299</v>
+        <v>224416</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Ljus solvända</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -3971,10 +3971,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>723389</v>
+        <v>723250</v>
       </c>
       <c r="R34" t="n">
-        <v>6413195</v>
+        <v>6413023</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4040,7 +4040,7 @@
         <v>126075031</v>
       </c>
       <c r="B35" t="n">
-        <v>109154</v>
+        <v>109156</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4141,7 +4141,7 @@
         <v>126075328</v>
       </c>
       <c r="B36" t="n">
-        <v>100523</v>
+        <v>100525</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4242,7 +4242,7 @@
         <v>126075421</v>
       </c>
       <c r="B37" t="n">
-        <v>106169</v>
+        <v>106171</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4459,7 +4459,7 @@
         <v>126075028</v>
       </c>
       <c r="B39" t="n">
-        <v>109154</v>
+        <v>109156</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4560,7 +4560,7 @@
         <v>126075039</v>
       </c>
       <c r="B40" t="n">
-        <v>109154</v>
+        <v>109156</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4661,7 +4661,7 @@
         <v>126075042</v>
       </c>
       <c r="B41" t="n">
-        <v>109154</v>
+        <v>109156</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4762,7 +4762,7 @@
         <v>126075030</v>
       </c>
       <c r="B42" t="n">
-        <v>109154</v>
+        <v>109156</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4860,10 +4860,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126075184</v>
+        <v>126075269</v>
       </c>
       <c r="B43" t="n">
-        <v>103784</v>
+        <v>107214</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4871,19 +4871,23 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>224416</v>
+        <v>220079</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ljus solvända</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. nummularium</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr"/>
+          <t>Cirsium acaule</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -4891,10 +4895,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>723240</v>
+        <v>723282</v>
       </c>
       <c r="R43" t="n">
-        <v>6413005</v>
+        <v>6413048</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4957,10 +4961,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126075269</v>
+        <v>126075044</v>
       </c>
       <c r="B44" t="n">
-        <v>107212</v>
+        <v>109156</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4968,21 +4972,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220079</v>
+        <v>220299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4992,10 +4996,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>723282</v>
+        <v>723367</v>
       </c>
       <c r="R44" t="n">
-        <v>6413048</v>
+        <v>6413134</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5058,10 +5062,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126075044</v>
+        <v>126075184</v>
       </c>
       <c r="B45" t="n">
-        <v>109154</v>
+        <v>103786</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5069,23 +5073,19 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220299</v>
+        <v>224416</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Ljus solvända</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5093,10 +5093,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>723367</v>
+        <v>723240</v>
       </c>
       <c r="R45" t="n">
-        <v>6413134</v>
+        <v>6413005</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5159,10 +5159,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126075182</v>
+        <v>126075045</v>
       </c>
       <c r="B46" t="n">
-        <v>103784</v>
+        <v>109156</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5170,19 +5170,23 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>224416</v>
+        <v>220299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ljus solvända</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. nummularium</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr"/>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5190,10 +5194,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>723272</v>
+        <v>723352</v>
       </c>
       <c r="R46" t="n">
-        <v>6413033</v>
+        <v>6413153</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5256,10 +5260,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126075045</v>
+        <v>126075412</v>
       </c>
       <c r="B47" t="n">
-        <v>109154</v>
+        <v>106171</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5267,16 +5271,16 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220299</v>
+        <v>221903</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -5291,10 +5295,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>723352</v>
+        <v>723243</v>
       </c>
       <c r="R47" t="n">
-        <v>6413153</v>
+        <v>6413018</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5357,10 +5361,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126075412</v>
+        <v>126075182</v>
       </c>
       <c r="B48" t="n">
-        <v>106169</v>
+        <v>103786</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5368,23 +5372,19 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221903</v>
+        <v>224416</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Ljus solvända</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -5392,10 +5392,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>723243</v>
+        <v>723272</v>
       </c>
       <c r="R48" t="n">
-        <v>6413018</v>
+        <v>6413033</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5458,27 +5458,27 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126075096</v>
+        <v>126075047</v>
       </c>
       <c r="B49" t="n">
-        <v>98369</v>
+        <v>109156</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>219864</v>
+        <v>220299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -5487,21 +5487,16 @@
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Hemhagen, Nors, Gtl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>723293</v>
+        <v>723335</v>
       </c>
       <c r="R49" t="n">
-        <v>6412906</v>
+        <v>6413175</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5564,10 +5559,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126075047</v>
+        <v>126075029</v>
       </c>
       <c r="B50" t="n">
-        <v>109154</v>
+        <v>109156</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5599,10 +5594,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>723335</v>
+        <v>723216</v>
       </c>
       <c r="R50" t="n">
-        <v>6413175</v>
+        <v>6412940</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5665,27 +5660,27 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126075029</v>
+        <v>126075096</v>
       </c>
       <c r="B51" t="n">
-        <v>109154</v>
+        <v>98371</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220299</v>
+        <v>219864</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -5694,16 +5689,21 @@
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Hemhagen, Nors, Gtl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>723216</v>
+        <v>723293</v>
       </c>
       <c r="R51" t="n">
-        <v>6412940</v>
+        <v>6412906</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>

--- a/artfynd/A 15629-2024 artfynd.xlsx
+++ b/artfynd/A 15629-2024 artfynd.xlsx
@@ -1609,27 +1609,27 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126075295</v>
+        <v>126075351</v>
       </c>
       <c r="B11" t="n">
-        <v>105279</v>
+        <v>106625</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221141</v>
+        <v>221849</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1644,10 +1644,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>723293</v>
+        <v>723310</v>
       </c>
       <c r="R11" t="n">
-        <v>6412916</v>
+        <v>6412729</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1710,27 +1710,27 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126075351</v>
+        <v>126075295</v>
       </c>
       <c r="B12" t="n">
-        <v>106625</v>
+        <v>105279</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221849</v>
+        <v>221141</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1745,10 +1745,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>723310</v>
+        <v>723293</v>
       </c>
       <c r="R12" t="n">
-        <v>6412729</v>
+        <v>6412916</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -5458,27 +5458,27 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126075047</v>
+        <v>126075096</v>
       </c>
       <c r="B49" t="n">
-        <v>109156</v>
+        <v>98371</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220299</v>
+        <v>219864</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -5487,16 +5487,21 @@
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Hemhagen, Nors, Gtl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>723335</v>
+        <v>723293</v>
       </c>
       <c r="R49" t="n">
-        <v>6413175</v>
+        <v>6412906</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5559,7 +5564,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126075029</v>
+        <v>126075047</v>
       </c>
       <c r="B50" t="n">
         <v>109156</v>
@@ -5594,10 +5599,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>723216</v>
+        <v>723335</v>
       </c>
       <c r="R50" t="n">
-        <v>6412940</v>
+        <v>6413175</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5660,27 +5665,27 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126075096</v>
+        <v>126075029</v>
       </c>
       <c r="B51" t="n">
-        <v>98371</v>
+        <v>109156</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>219864</v>
+        <v>220299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -5689,21 +5694,16 @@
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Hemhagen, Nors, Gtl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>723293</v>
+        <v>723216</v>
       </c>
       <c r="R51" t="n">
-        <v>6412906</v>
+        <v>6412940</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>

--- a/artfynd/A 15629-2024 artfynd.xlsx
+++ b/artfynd/A 15629-2024 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>126075195</v>
       </c>
       <c r="B3" t="n">
-        <v>103786</v>
+        <v>103790</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126075167</v>
+        <v>126075089</v>
       </c>
       <c r="B4" t="n">
-        <v>98365</v>
+        <v>98373</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -903,34 +903,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219862</v>
+        <v>219864</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Hemhagen, Nors, Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>723327</v>
+        <v>723237</v>
       </c>
       <c r="R4" t="n">
-        <v>6413202</v>
+        <v>6413005</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +998,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126075089</v>
+        <v>126075167</v>
       </c>
       <c r="B5" t="n">
-        <v>98371</v>
+        <v>98367</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1004,39 +1009,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219864</v>
+        <v>219862</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hemhagen, Nors, Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>723237</v>
+        <v>723327</v>
       </c>
       <c r="R5" t="n">
-        <v>6413005</v>
+        <v>6413202</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126075032</v>
+        <v>126075055</v>
       </c>
       <c r="B6" t="n">
-        <v>109156</v>
+        <v>109160</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>723222</v>
+        <v>723291</v>
       </c>
       <c r="R6" t="n">
-        <v>6412868</v>
+        <v>6413160</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1164,12 +1164,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126075055</v>
+        <v>126075032</v>
       </c>
       <c r="B7" t="n">
-        <v>109156</v>
+        <v>109160</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1235,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>723291</v>
+        <v>723222</v>
       </c>
       <c r="R7" t="n">
-        <v>6413160</v>
+        <v>6412868</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1265,12 +1265,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1304,7 +1304,7 @@
         <v>126075088</v>
       </c>
       <c r="B8" t="n">
-        <v>98371</v>
+        <v>98373</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1407,27 +1407,27 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126075294</v>
+        <v>126075038</v>
       </c>
       <c r="B9" t="n">
-        <v>105279</v>
+        <v>109160</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221141</v>
+        <v>220299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1442,10 +1442,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>723318</v>
+        <v>723299</v>
       </c>
       <c r="R9" t="n">
-        <v>6412902</v>
+        <v>6413005</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1508,27 +1508,27 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126075038</v>
+        <v>126075294</v>
       </c>
       <c r="B10" t="n">
-        <v>109156</v>
+        <v>105283</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220299</v>
+        <v>221141</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1543,10 +1543,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>723299</v>
+        <v>723318</v>
       </c>
       <c r="R10" t="n">
-        <v>6413005</v>
+        <v>6412902</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1609,27 +1609,27 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126075351</v>
+        <v>126075295</v>
       </c>
       <c r="B11" t="n">
-        <v>106625</v>
+        <v>105283</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221849</v>
+        <v>221141</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1644,10 +1644,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>723310</v>
+        <v>723293</v>
       </c>
       <c r="R11" t="n">
-        <v>6412729</v>
+        <v>6412916</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1710,27 +1710,27 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126075295</v>
+        <v>126075351</v>
       </c>
       <c r="B12" t="n">
-        <v>105279</v>
+        <v>106629</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221141</v>
+        <v>221849</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1745,10 +1745,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>723293</v>
+        <v>723310</v>
       </c>
       <c r="R12" t="n">
-        <v>6412916</v>
+        <v>6412729</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1814,7 +1814,7 @@
         <v>126075247</v>
       </c>
       <c r="B13" t="n">
-        <v>96403</v>
+        <v>96405</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1912,10 +1912,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126075046</v>
+        <v>126075422</v>
       </c>
       <c r="B14" t="n">
-        <v>109156</v>
+        <v>106175</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1923,16 +1923,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220299</v>
+        <v>221903</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1947,10 +1947,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>723345</v>
+        <v>723297</v>
       </c>
       <c r="R14" t="n">
-        <v>6413172</v>
+        <v>6412905</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2013,10 +2013,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126075422</v>
+        <v>126075046</v>
       </c>
       <c r="B15" t="n">
-        <v>106171</v>
+        <v>109160</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2024,16 +2024,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221903</v>
+        <v>220299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2048,10 +2048,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>723297</v>
+        <v>723345</v>
       </c>
       <c r="R15" t="n">
-        <v>6412905</v>
+        <v>6413172</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2338,7 +2338,7 @@
         <v>126075041</v>
       </c>
       <c r="B18" t="n">
-        <v>109156</v>
+        <v>109160</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2439,7 +2439,7 @@
         <v>126075420</v>
       </c>
       <c r="B19" t="n">
-        <v>106171</v>
+        <v>106175</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2540,7 +2540,7 @@
         <v>126075192</v>
       </c>
       <c r="B20" t="n">
-        <v>103786</v>
+        <v>103790</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2637,7 +2637,7 @@
         <v>126075050</v>
       </c>
       <c r="B21" t="n">
-        <v>109156</v>
+        <v>109160</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         <v>126075043</v>
       </c>
       <c r="B22" t="n">
-        <v>109156</v>
+        <v>109160</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2839,7 +2839,7 @@
         <v>126075053</v>
       </c>
       <c r="B23" t="n">
-        <v>109156</v>
+        <v>109160</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2940,7 +2940,7 @@
         <v>126075040</v>
       </c>
       <c r="B24" t="n">
-        <v>109156</v>
+        <v>109160</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3041,7 +3041,7 @@
         <v>126075330</v>
       </c>
       <c r="B25" t="n">
-        <v>95946</v>
+        <v>95948</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3142,7 +3142,7 @@
         <v>126075095</v>
       </c>
       <c r="B26" t="n">
-        <v>98371</v>
+        <v>98373</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3248,7 +3248,7 @@
         <v>126075052</v>
       </c>
       <c r="B27" t="n">
-        <v>109156</v>
+        <v>109160</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3349,7 +3349,7 @@
         <v>126075049</v>
       </c>
       <c r="B28" t="n">
-        <v>109156</v>
+        <v>109160</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         <v>126075357</v>
       </c>
       <c r="B29" t="n">
-        <v>106625</v>
+        <v>106629</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3551,7 +3551,7 @@
         <v>126075193</v>
       </c>
       <c r="B30" t="n">
-        <v>103786</v>
+        <v>103790</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3648,7 +3648,7 @@
         <v>126075054</v>
       </c>
       <c r="B31" t="n">
-        <v>109156</v>
+        <v>109160</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3749,7 +3749,7 @@
         <v>126075188</v>
       </c>
       <c r="B32" t="n">
-        <v>103786</v>
+        <v>103790</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3846,7 +3846,7 @@
         <v>126075189</v>
       </c>
       <c r="B33" t="n">
-        <v>103786</v>
+        <v>103790</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3943,7 +3943,7 @@
         <v>126075185</v>
       </c>
       <c r="B34" t="n">
-        <v>103786</v>
+        <v>103790</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4037,32 +4037,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126075031</v>
+        <v>126075328</v>
       </c>
       <c r="B35" t="n">
-        <v>109156</v>
+        <v>100527</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220299</v>
+        <v>222498</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4072,10 +4072,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>723216</v>
+        <v>723335</v>
       </c>
       <c r="R35" t="n">
-        <v>6412876</v>
+        <v>6413175</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4138,32 +4138,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126075328</v>
+        <v>126075031</v>
       </c>
       <c r="B36" t="n">
-        <v>100525</v>
+        <v>109160</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>222498</v>
+        <v>220299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4173,10 +4173,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>723335</v>
+        <v>723216</v>
       </c>
       <c r="R36" t="n">
-        <v>6413175</v>
+        <v>6412876</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4242,7 +4242,7 @@
         <v>126075421</v>
       </c>
       <c r="B37" t="n">
-        <v>106171</v>
+        <v>106175</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4459,7 +4459,7 @@
         <v>126075028</v>
       </c>
       <c r="B39" t="n">
-        <v>109156</v>
+        <v>109160</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4560,7 +4560,7 @@
         <v>126075039</v>
       </c>
       <c r="B40" t="n">
-        <v>109156</v>
+        <v>109160</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4661,7 +4661,7 @@
         <v>126075042</v>
       </c>
       <c r="B41" t="n">
-        <v>109156</v>
+        <v>109160</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4762,7 +4762,7 @@
         <v>126075030</v>
       </c>
       <c r="B42" t="n">
-        <v>109156</v>
+        <v>109160</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4863,7 +4863,7 @@
         <v>126075269</v>
       </c>
       <c r="B43" t="n">
-        <v>107214</v>
+        <v>107218</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4964,7 +4964,7 @@
         <v>126075044</v>
       </c>
       <c r="B44" t="n">
-        <v>109156</v>
+        <v>109160</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5065,7 +5065,7 @@
         <v>126075184</v>
       </c>
       <c r="B45" t="n">
-        <v>103786</v>
+        <v>103790</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5162,7 +5162,7 @@
         <v>126075045</v>
       </c>
       <c r="B46" t="n">
-        <v>109156</v>
+        <v>109160</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5263,7 +5263,7 @@
         <v>126075412</v>
       </c>
       <c r="B47" t="n">
-        <v>106171</v>
+        <v>106175</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5364,7 +5364,7 @@
         <v>126075182</v>
       </c>
       <c r="B48" t="n">
-        <v>103786</v>
+        <v>103790</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5461,7 +5461,7 @@
         <v>126075096</v>
       </c>
       <c r="B49" t="n">
-        <v>98371</v>
+        <v>98373</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5567,7 +5567,7 @@
         <v>126075047</v>
       </c>
       <c r="B50" t="n">
-        <v>109156</v>
+        <v>109160</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5668,7 +5668,7 @@
         <v>126075029</v>
       </c>
       <c r="B51" t="n">
-        <v>109156</v>
+        <v>109160</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>

--- a/artfynd/A 15629-2024 artfynd.xlsx
+++ b/artfynd/A 15629-2024 artfynd.xlsx
@@ -1301,27 +1301,27 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126075088</v>
+        <v>126075038</v>
       </c>
       <c r="B8" t="n">
-        <v>98373</v>
+        <v>109160</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219864</v>
+        <v>220299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1330,21 +1330,16 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hemhagen, Nors, Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>723278</v>
+        <v>723299</v>
       </c>
       <c r="R8" t="n">
-        <v>6413037</v>
+        <v>6413005</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1407,27 +1402,27 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126075038</v>
+        <v>126075088</v>
       </c>
       <c r="B9" t="n">
-        <v>109160</v>
+        <v>98373</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220299</v>
+        <v>219864</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1436,16 +1431,21 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hemhagen, Nors, Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>723299</v>
+        <v>723278</v>
       </c>
       <c r="R9" t="n">
-        <v>6413005</v>
+        <v>6413037</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -3038,10 +3038,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126075330</v>
+        <v>126075095</v>
       </c>
       <c r="B25" t="n">
-        <v>95948</v>
+        <v>98373</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3049,34 +3049,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2180</v>
+        <v>219864</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Hemhagen, Nors, Gtl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>723341</v>
+        <v>723328</v>
       </c>
       <c r="R25" t="n">
-        <v>6413230</v>
+        <v>6412904</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3139,27 +3144,27 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126075095</v>
+        <v>126075052</v>
       </c>
       <c r="B26" t="n">
-        <v>98373</v>
+        <v>109160</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>219864</v>
+        <v>220299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3168,21 +3173,16 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Hemhagen, Nors, Gtl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>723328</v>
+        <v>723338</v>
       </c>
       <c r="R26" t="n">
-        <v>6412904</v>
+        <v>6413224</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3245,7 +3245,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126075052</v>
+        <v>126075049</v>
       </c>
       <c r="B27" t="n">
         <v>109160</v>
@@ -3280,10 +3280,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>723338</v>
+        <v>723331</v>
       </c>
       <c r="R27" t="n">
-        <v>6413224</v>
+        <v>6413195</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3346,32 +3346,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126075049</v>
+        <v>126075330</v>
       </c>
       <c r="B28" t="n">
-        <v>109160</v>
+        <v>95948</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220299</v>
+        <v>2180</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3381,10 +3381,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>723331</v>
+        <v>723341</v>
       </c>
       <c r="R28" t="n">
-        <v>6413195</v>
+        <v>6413230</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4037,32 +4037,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126075328</v>
+        <v>126075031</v>
       </c>
       <c r="B35" t="n">
-        <v>100527</v>
+        <v>109160</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>222498</v>
+        <v>220299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4072,10 +4072,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>723335</v>
+        <v>723216</v>
       </c>
       <c r="R35" t="n">
-        <v>6413175</v>
+        <v>6412876</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4138,32 +4138,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126075031</v>
+        <v>126075328</v>
       </c>
       <c r="B36" t="n">
-        <v>109160</v>
+        <v>100527</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220299</v>
+        <v>222498</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4173,10 +4173,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>723216</v>
+        <v>723335</v>
       </c>
       <c r="R36" t="n">
-        <v>6412876</v>
+        <v>6413175</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4239,10 +4239,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126075421</v>
+        <v>126075165</v>
       </c>
       <c r="B37" t="n">
-        <v>106175</v>
+        <v>19793</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4250,21 +4250,16 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221903</v>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Axveronika</t>
-        </is>
+        <v>241122</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Orellia scorzonerae</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Robineau-Desvoidy, 1830)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4274,10 +4269,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>723321</v>
+        <v>723375</v>
       </c>
       <c r="R37" t="n">
-        <v>6412897</v>
+        <v>6413131</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4312,6 +4307,11 @@
           <t>2024-05-16</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>På knoppar av värdväxten svinrot.</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -4320,6 +4320,21 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>svinrot</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -4340,10 +4355,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126075165</v>
+        <v>126075421</v>
       </c>
       <c r="B38" t="n">
-        <v>19793</v>
+        <v>106175</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4351,16 +4366,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>241122</v>
+        <v>221903</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Axveronika</t>
+        </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Orellia scorzonerae</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Robineau-Desvoidy, 1830)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4370,10 +4390,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>723375</v>
+        <v>723321</v>
       </c>
       <c r="R38" t="n">
-        <v>6413131</v>
+        <v>6412897</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4408,11 +4428,6 @@
           <t>2024-05-16</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>På knoppar av värdväxten svinrot.</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -4421,21 +4436,6 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>svinrot</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Scorzonera humilis</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Scorzonera humilis</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -5159,10 +5159,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126075045</v>
+        <v>126075412</v>
       </c>
       <c r="B46" t="n">
-        <v>109160</v>
+        <v>106175</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5170,16 +5170,16 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220299</v>
+        <v>221903</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -5194,10 +5194,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>723352</v>
+        <v>723243</v>
       </c>
       <c r="R46" t="n">
-        <v>6413153</v>
+        <v>6413018</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5260,10 +5260,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126075412</v>
+        <v>126075182</v>
       </c>
       <c r="B47" t="n">
-        <v>106175</v>
+        <v>103790</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5271,23 +5271,19 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221903</v>
+        <v>224416</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Ljus solvända</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5295,10 +5291,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>723243</v>
+        <v>723272</v>
       </c>
       <c r="R47" t="n">
-        <v>6413018</v>
+        <v>6413033</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5361,10 +5357,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126075182</v>
+        <v>126075045</v>
       </c>
       <c r="B48" t="n">
-        <v>103790</v>
+        <v>109160</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5372,19 +5368,23 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>224416</v>
+        <v>220299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ljus solvända</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. nummularium</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr"/>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -5392,10 +5392,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>723272</v>
+        <v>723352</v>
       </c>
       <c r="R48" t="n">
-        <v>6413033</v>
+        <v>6413153</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>

--- a/artfynd/A 15629-2024 artfynd.xlsx
+++ b/artfynd/A 15629-2024 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>126075195</v>
       </c>
       <c r="B3" t="n">
-        <v>103790</v>
+        <v>103803</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,27 +892,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126075089</v>
+        <v>126075032</v>
       </c>
       <c r="B4" t="n">
-        <v>98373</v>
+        <v>109173</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219864</v>
+        <v>220299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -921,21 +921,16 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Hemhagen, Nors, Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>723237</v>
+        <v>723222</v>
       </c>
       <c r="R4" t="n">
-        <v>6413005</v>
+        <v>6412868</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -998,32 +993,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126075167</v>
+        <v>126075055</v>
       </c>
       <c r="B5" t="n">
-        <v>98367</v>
+        <v>109173</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219862</v>
+        <v>220299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1028,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>723327</v>
+        <v>723291</v>
       </c>
       <c r="R5" t="n">
-        <v>6413202</v>
+        <v>6413160</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,12 +1058,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1099,27 +1094,27 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126075055</v>
+        <v>126075089</v>
       </c>
       <c r="B6" t="n">
-        <v>109160</v>
+        <v>98377</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220299</v>
+        <v>219864</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1128,16 +1123,21 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hemhagen, Nors, Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>723291</v>
+        <v>723237</v>
       </c>
       <c r="R6" t="n">
-        <v>6413160</v>
+        <v>6413005</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1164,12 +1164,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,32 +1200,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126075032</v>
+        <v>126075167</v>
       </c>
       <c r="B7" t="n">
-        <v>109160</v>
+        <v>98371</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220299</v>
+        <v>219862</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>723222</v>
+        <v>723327</v>
       </c>
       <c r="R7" t="n">
-        <v>6412868</v>
+        <v>6413202</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1304,7 +1304,7 @@
         <v>126075038</v>
       </c>
       <c r="B8" t="n">
-        <v>109160</v>
+        <v>109173</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1402,10 +1402,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126075088</v>
+        <v>126075294</v>
       </c>
       <c r="B9" t="n">
-        <v>98373</v>
+        <v>105296</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1413,16 +1413,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219864</v>
+        <v>221141</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1431,21 +1431,16 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hemhagen, Nors, Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>723278</v>
+        <v>723318</v>
       </c>
       <c r="R9" t="n">
-        <v>6413037</v>
+        <v>6412902</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1508,10 +1503,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126075294</v>
+        <v>126075088</v>
       </c>
       <c r="B10" t="n">
-        <v>105283</v>
+        <v>98377</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1519,16 +1514,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221141</v>
+        <v>219864</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1537,16 +1532,21 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hemhagen, Nors, Gtl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>723318</v>
+        <v>723278</v>
       </c>
       <c r="R10" t="n">
-        <v>6412902</v>
+        <v>6413037</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1609,27 +1609,27 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126075295</v>
+        <v>126075351</v>
       </c>
       <c r="B11" t="n">
-        <v>105283</v>
+        <v>106642</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221141</v>
+        <v>221849</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1644,10 +1644,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>723293</v>
+        <v>723310</v>
       </c>
       <c r="R11" t="n">
-        <v>6412916</v>
+        <v>6412729</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1710,27 +1710,27 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126075351</v>
+        <v>126075295</v>
       </c>
       <c r="B12" t="n">
-        <v>106629</v>
+        <v>105296</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221849</v>
+        <v>221141</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1745,10 +1745,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>723310</v>
+        <v>723293</v>
       </c>
       <c r="R12" t="n">
-        <v>6412729</v>
+        <v>6412916</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1814,7 +1814,7 @@
         <v>126075247</v>
       </c>
       <c r="B13" t="n">
-        <v>96405</v>
+        <v>96409</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1912,10 +1912,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126075422</v>
+        <v>126075046</v>
       </c>
       <c r="B14" t="n">
-        <v>106175</v>
+        <v>109173</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1923,16 +1923,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221903</v>
+        <v>220299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1947,10 +1947,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>723297</v>
+        <v>723345</v>
       </c>
       <c r="R14" t="n">
-        <v>6412905</v>
+        <v>6413172</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2013,10 +2013,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126075046</v>
+        <v>126075422</v>
       </c>
       <c r="B15" t="n">
-        <v>109160</v>
+        <v>106188</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2024,16 +2024,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220299</v>
+        <v>221903</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2048,10 +2048,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>723345</v>
+        <v>723297</v>
       </c>
       <c r="R15" t="n">
-        <v>6413172</v>
+        <v>6412905</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2114,45 +2114,59 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126075228</v>
+        <v>126075072</v>
       </c>
       <c r="B16" t="n">
-        <v>75007</v>
+        <v>57653</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6426</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Hemhagen, Nors, Gtl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>723347</v>
+        <v>723335</v>
       </c>
       <c r="R16" t="n">
-        <v>6413067</v>
+        <v>6413183</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2185,6 +2199,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Lockläte i lämplig biotop, senvuxna tallar med spår av spår av spillkråka, enstaka äldre potentiella boträd i skogen.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2215,59 +2234,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126075072</v>
+        <v>126075228</v>
       </c>
       <c r="B17" t="n">
-        <v>57649</v>
+        <v>75011</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>6426</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Hemhagen, Nors, Gtl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>723335</v>
+        <v>723347</v>
       </c>
       <c r="R17" t="n">
-        <v>6413183</v>
+        <v>6413067</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2300,11 +2305,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-05-16</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Lockläte i lämplig biotop, senvuxna tallar med spår av spår av spillkråka, enstaka äldre potentiella boträd i skogen.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2335,10 +2335,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126075041</v>
+        <v>126075192</v>
       </c>
       <c r="B18" t="n">
-        <v>109160</v>
+        <v>103803</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2346,23 +2346,19 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220299</v>
+        <v>224416</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Ljus solvända</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2370,10 +2366,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>723339</v>
+        <v>723305</v>
       </c>
       <c r="R18" t="n">
-        <v>6413055</v>
+        <v>6412896</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2436,10 +2432,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126075420</v>
+        <v>126075041</v>
       </c>
       <c r="B19" t="n">
-        <v>106175</v>
+        <v>109173</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2447,16 +2443,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221903</v>
+        <v>220299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2471,10 +2467,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>723302</v>
+        <v>723339</v>
       </c>
       <c r="R19" t="n">
-        <v>6412899</v>
+        <v>6413055</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2537,10 +2533,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126075192</v>
+        <v>126075420</v>
       </c>
       <c r="B20" t="n">
-        <v>103790</v>
+        <v>106188</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2548,19 +2544,23 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>224416</v>
+        <v>221903</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ljus solvända</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. nummularium</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr"/>
+          <t>Veronica spicata</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2568,10 +2568,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>723305</v>
+        <v>723302</v>
       </c>
       <c r="R20" t="n">
-        <v>6412896</v>
+        <v>6412899</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2637,7 +2637,7 @@
         <v>126075050</v>
       </c>
       <c r="B21" t="n">
-        <v>109160</v>
+        <v>109173</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         <v>126075043</v>
       </c>
       <c r="B22" t="n">
-        <v>109160</v>
+        <v>109173</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2839,7 +2839,7 @@
         <v>126075053</v>
       </c>
       <c r="B23" t="n">
-        <v>109160</v>
+        <v>109173</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2940,7 +2940,7 @@
         <v>126075040</v>
       </c>
       <c r="B24" t="n">
-        <v>109160</v>
+        <v>109173</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3038,10 +3038,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126075095</v>
+        <v>126075330</v>
       </c>
       <c r="B25" t="n">
-        <v>98373</v>
+        <v>95952</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3049,39 +3049,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>219864</v>
+        <v>2180</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Hemhagen, Nors, Gtl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>723328</v>
+        <v>723341</v>
       </c>
       <c r="R25" t="n">
-        <v>6412904</v>
+        <v>6413230</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3144,10 +3139,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126075052</v>
+        <v>126075357</v>
       </c>
       <c r="B26" t="n">
-        <v>109160</v>
+        <v>106642</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3155,16 +3150,16 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220299</v>
+        <v>221849</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3179,10 +3174,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>723338</v>
+        <v>723324</v>
       </c>
       <c r="R26" t="n">
-        <v>6413224</v>
+        <v>6412899</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3245,10 +3240,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126075049</v>
+        <v>126075052</v>
       </c>
       <c r="B27" t="n">
-        <v>109160</v>
+        <v>109173</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3280,10 +3275,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>723331</v>
+        <v>723338</v>
       </c>
       <c r="R27" t="n">
-        <v>6413195</v>
+        <v>6413224</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3346,32 +3341,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126075330</v>
+        <v>126075049</v>
       </c>
       <c r="B28" t="n">
-        <v>95948</v>
+        <v>109173</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2180</v>
+        <v>220299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3381,10 +3376,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>723341</v>
+        <v>723331</v>
       </c>
       <c r="R28" t="n">
-        <v>6413230</v>
+        <v>6413195</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3447,10 +3442,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126075357</v>
+        <v>126075193</v>
       </c>
       <c r="B29" t="n">
-        <v>106629</v>
+        <v>103803</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3458,23 +3453,19 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221849</v>
+        <v>224416</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Ljus solvända</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3482,10 +3473,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>723324</v>
+        <v>723321</v>
       </c>
       <c r="R29" t="n">
-        <v>6412899</v>
+        <v>6412898</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3548,41 +3539,50 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126075193</v>
+        <v>126075095</v>
       </c>
       <c r="B30" t="n">
-        <v>103790</v>
+        <v>98377</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>224416</v>
+        <v>219864</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ljus solvända</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. nummularium</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr"/>
+          <t>Orchis mascula</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Hemhagen, Nors, Gtl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>723321</v>
+        <v>723328</v>
       </c>
       <c r="R30" t="n">
-        <v>6412898</v>
+        <v>6412904</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3648,7 +3648,7 @@
         <v>126075054</v>
       </c>
       <c r="B31" t="n">
-        <v>109160</v>
+        <v>109173</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3749,7 +3749,7 @@
         <v>126075188</v>
       </c>
       <c r="B32" t="n">
-        <v>103790</v>
+        <v>103803</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3846,7 +3846,7 @@
         <v>126075189</v>
       </c>
       <c r="B33" t="n">
-        <v>103790</v>
+        <v>103803</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3943,7 +3943,7 @@
         <v>126075185</v>
       </c>
       <c r="B34" t="n">
-        <v>103790</v>
+        <v>103803</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4040,7 +4040,7 @@
         <v>126075031</v>
       </c>
       <c r="B35" t="n">
-        <v>109160</v>
+        <v>109173</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4141,7 +4141,7 @@
         <v>126075328</v>
       </c>
       <c r="B36" t="n">
-        <v>100527</v>
+        <v>100531</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4239,10 +4239,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126075165</v>
+        <v>126075421</v>
       </c>
       <c r="B37" t="n">
-        <v>19793</v>
+        <v>106188</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4250,16 +4250,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>241122</v>
+        <v>221903</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Axveronika</t>
+        </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Orellia scorzonerae</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Robineau-Desvoidy, 1830)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4269,10 +4274,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>723375</v>
+        <v>723321</v>
       </c>
       <c r="R37" t="n">
-        <v>6413131</v>
+        <v>6412897</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4307,11 +4312,6 @@
           <t>2024-05-16</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>På knoppar av värdväxten svinrot.</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -4320,21 +4320,6 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>svinrot</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Scorzonera humilis</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Scorzonera humilis</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -4355,10 +4340,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126075421</v>
+        <v>126075165</v>
       </c>
       <c r="B38" t="n">
-        <v>106175</v>
+        <v>19793</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4366,21 +4351,16 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221903</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Axveronika</t>
-        </is>
+        <v>241122</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Orellia scorzonerae</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Robineau-Desvoidy, 1830)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4390,10 +4370,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>723321</v>
+        <v>723375</v>
       </c>
       <c r="R38" t="n">
-        <v>6412897</v>
+        <v>6413131</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4428,6 +4408,11 @@
           <t>2024-05-16</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>På knoppar av värdväxten svinrot.</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -4436,6 +4421,21 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>svinrot</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -4459,7 +4459,7 @@
         <v>126075028</v>
       </c>
       <c r="B39" t="n">
-        <v>109160</v>
+        <v>109173</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4560,7 +4560,7 @@
         <v>126075039</v>
       </c>
       <c r="B40" t="n">
-        <v>109160</v>
+        <v>109173</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4661,7 +4661,7 @@
         <v>126075042</v>
       </c>
       <c r="B41" t="n">
-        <v>109160</v>
+        <v>109173</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4762,7 +4762,7 @@
         <v>126075030</v>
       </c>
       <c r="B42" t="n">
-        <v>109160</v>
+        <v>109173</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4860,10 +4860,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126075269</v>
+        <v>126075044</v>
       </c>
       <c r="B43" t="n">
-        <v>107218</v>
+        <v>109173</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4871,21 +4871,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220079</v>
+        <v>220299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4895,10 +4895,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>723282</v>
+        <v>723367</v>
       </c>
       <c r="R43" t="n">
-        <v>6413048</v>
+        <v>6413134</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4961,10 +4961,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126075044</v>
+        <v>126075184</v>
       </c>
       <c r="B44" t="n">
-        <v>109160</v>
+        <v>103803</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4972,23 +4972,19 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220299</v>
+        <v>224416</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Ljus solvända</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -4996,10 +4992,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>723367</v>
+        <v>723240</v>
       </c>
       <c r="R44" t="n">
-        <v>6413134</v>
+        <v>6413005</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5062,10 +5058,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126075184</v>
+        <v>126075269</v>
       </c>
       <c r="B45" t="n">
-        <v>103790</v>
+        <v>107231</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5073,19 +5069,23 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>224416</v>
+        <v>220079</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ljus solvända</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. nummularium</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr"/>
+          <t>Cirsium acaule</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5093,10 +5093,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>723240</v>
+        <v>723282</v>
       </c>
       <c r="R45" t="n">
-        <v>6413005</v>
+        <v>6413048</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5159,10 +5159,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126075412</v>
+        <v>126075045</v>
       </c>
       <c r="B46" t="n">
-        <v>106175</v>
+        <v>109173</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5170,16 +5170,16 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>221903</v>
+        <v>220299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -5194,10 +5194,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>723243</v>
+        <v>723352</v>
       </c>
       <c r="R46" t="n">
-        <v>6413018</v>
+        <v>6413153</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5263,7 +5263,7 @@
         <v>126075182</v>
       </c>
       <c r="B47" t="n">
-        <v>103790</v>
+        <v>103803</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5357,10 +5357,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126075045</v>
+        <v>126075412</v>
       </c>
       <c r="B48" t="n">
-        <v>109160</v>
+        <v>106188</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5368,16 +5368,16 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220299</v>
+        <v>221903</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -5392,10 +5392,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>723352</v>
+        <v>723243</v>
       </c>
       <c r="R48" t="n">
-        <v>6413153</v>
+        <v>6413018</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5461,7 +5461,7 @@
         <v>126075096</v>
       </c>
       <c r="B49" t="n">
-        <v>98373</v>
+        <v>98377</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5567,7 +5567,7 @@
         <v>126075047</v>
       </c>
       <c r="B50" t="n">
-        <v>109160</v>
+        <v>109173</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5668,7 +5668,7 @@
         <v>126075029</v>
       </c>
       <c r="B51" t="n">
-        <v>109160</v>
+        <v>109173</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>

--- a/artfynd/A 15629-2024 artfynd.xlsx
+++ b/artfynd/A 15629-2024 artfynd.xlsx
@@ -1609,27 +1609,27 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126075351</v>
+        <v>126075295</v>
       </c>
       <c r="B11" t="n">
-        <v>106642</v>
+        <v>105296</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221849</v>
+        <v>221141</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1644,10 +1644,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>723310</v>
+        <v>723293</v>
       </c>
       <c r="R11" t="n">
-        <v>6412729</v>
+        <v>6412916</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1710,27 +1710,27 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126075295</v>
+        <v>126075351</v>
       </c>
       <c r="B12" t="n">
-        <v>105296</v>
+        <v>106642</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221141</v>
+        <v>221849</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1745,10 +1745,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>723293</v>
+        <v>723310</v>
       </c>
       <c r="R12" t="n">
-        <v>6412916</v>
+        <v>6412729</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2114,59 +2114,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126075072</v>
+        <v>126075228</v>
       </c>
       <c r="B16" t="n">
-        <v>57653</v>
+        <v>75011</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>6426</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Hemhagen, Nors, Gtl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>723335</v>
+        <v>723347</v>
       </c>
       <c r="R16" t="n">
-        <v>6413183</v>
+        <v>6413067</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2199,11 +2185,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-05-16</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Lockläte i lämplig biotop, senvuxna tallar med spår av spår av spillkråka, enstaka äldre potentiella boträd i skogen.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2234,45 +2215,59 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126075228</v>
+        <v>126075072</v>
       </c>
       <c r="B17" t="n">
-        <v>75011</v>
+        <v>57653</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6426</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Hemhagen, Nors, Gtl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>723347</v>
+        <v>723335</v>
       </c>
       <c r="R17" t="n">
-        <v>6413067</v>
+        <v>6413183</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2305,6 +2300,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Lockläte i lämplig biotop, senvuxna tallar med spår av spår av spillkråka, enstaka äldre potentiella boträd i skogen.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2335,10 +2335,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126075192</v>
+        <v>126075041</v>
       </c>
       <c r="B18" t="n">
-        <v>103803</v>
+        <v>109173</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2346,19 +2346,23 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>224416</v>
+        <v>220299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ljus solvända</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. nummularium</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2366,10 +2370,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>723305</v>
+        <v>723339</v>
       </c>
       <c r="R18" t="n">
-        <v>6412896</v>
+        <v>6413055</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2432,10 +2436,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126075041</v>
+        <v>126075420</v>
       </c>
       <c r="B19" t="n">
-        <v>109173</v>
+        <v>106188</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2443,16 +2447,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220299</v>
+        <v>221903</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2467,10 +2471,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>723339</v>
+        <v>723302</v>
       </c>
       <c r="R19" t="n">
-        <v>6413055</v>
+        <v>6412899</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2533,10 +2537,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126075420</v>
+        <v>126075192</v>
       </c>
       <c r="B20" t="n">
-        <v>106188</v>
+        <v>103803</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2544,23 +2548,19 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221903</v>
+        <v>224416</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Ljus solvända</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2568,10 +2568,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>723302</v>
+        <v>723305</v>
       </c>
       <c r="R20" t="n">
-        <v>6412899</v>
+        <v>6412896</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -5260,10 +5260,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126075182</v>
+        <v>126075412</v>
       </c>
       <c r="B47" t="n">
-        <v>103803</v>
+        <v>106188</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5271,19 +5271,23 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>224416</v>
+        <v>221903</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ljus solvända</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. nummularium</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr"/>
+          <t>Veronica spicata</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5291,10 +5295,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>723272</v>
+        <v>723243</v>
       </c>
       <c r="R47" t="n">
-        <v>6413033</v>
+        <v>6413018</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5357,10 +5361,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126075412</v>
+        <v>126075182</v>
       </c>
       <c r="B48" t="n">
-        <v>106188</v>
+        <v>103803</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5368,23 +5372,19 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221903</v>
+        <v>224416</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Ljus solvända</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -5392,10 +5392,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>723243</v>
+        <v>723272</v>
       </c>
       <c r="R48" t="n">
-        <v>6413018</v>
+        <v>6413033</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5458,27 +5458,27 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126075096</v>
+        <v>126075047</v>
       </c>
       <c r="B49" t="n">
-        <v>98377</v>
+        <v>109173</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>219864</v>
+        <v>220299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -5487,21 +5487,16 @@
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Hemhagen, Nors, Gtl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>723293</v>
+        <v>723335</v>
       </c>
       <c r="R49" t="n">
-        <v>6412906</v>
+        <v>6413175</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5564,7 +5559,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126075047</v>
+        <v>126075029</v>
       </c>
       <c r="B50" t="n">
         <v>109173</v>
@@ -5599,10 +5594,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>723335</v>
+        <v>723216</v>
       </c>
       <c r="R50" t="n">
-        <v>6413175</v>
+        <v>6412940</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5665,27 +5660,27 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126075029</v>
+        <v>126075096</v>
       </c>
       <c r="B51" t="n">
-        <v>109173</v>
+        <v>98377</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220299</v>
+        <v>219864</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -5694,16 +5689,21 @@
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Hemhagen, Nors, Gtl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>723216</v>
+        <v>723293</v>
       </c>
       <c r="R51" t="n">
-        <v>6412940</v>
+        <v>6412906</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>

--- a/artfynd/A 15629-2024 artfynd.xlsx
+++ b/artfynd/A 15629-2024 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>126075195</v>
       </c>
       <c r="B3" t="n">
-        <v>103803</v>
+        <v>103806</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,27 +892,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126075032</v>
+        <v>126075089</v>
       </c>
       <c r="B4" t="n">
-        <v>109173</v>
+        <v>98380</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220299</v>
+        <v>219864</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -921,16 +921,21 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Hemhagen, Nors, Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>723222</v>
+        <v>723237</v>
       </c>
       <c r="R4" t="n">
-        <v>6412868</v>
+        <v>6413005</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +998,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126075055</v>
+        <v>126075032</v>
       </c>
       <c r="B5" t="n">
-        <v>109173</v>
+        <v>109176</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1028,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>723291</v>
+        <v>723222</v>
       </c>
       <c r="R5" t="n">
-        <v>6413160</v>
+        <v>6412868</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1058,12 +1063,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1094,27 +1099,27 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126075089</v>
+        <v>126075055</v>
       </c>
       <c r="B6" t="n">
-        <v>98377</v>
+        <v>109176</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219864</v>
+        <v>220299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1123,21 +1128,16 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hemhagen, Nors, Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>723237</v>
+        <v>723291</v>
       </c>
       <c r="R6" t="n">
-        <v>6413005</v>
+        <v>6413160</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1164,12 +1164,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1203,7 +1203,7 @@
         <v>126075167</v>
       </c>
       <c r="B7" t="n">
-        <v>98371</v>
+        <v>98374</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1301,27 +1301,27 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126075038</v>
+        <v>126075294</v>
       </c>
       <c r="B8" t="n">
-        <v>109173</v>
+        <v>105299</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220299</v>
+        <v>221141</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1336,10 +1336,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>723299</v>
+        <v>723318</v>
       </c>
       <c r="R8" t="n">
-        <v>6413005</v>
+        <v>6412902</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1402,27 +1402,27 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126075294</v>
+        <v>126075038</v>
       </c>
       <c r="B9" t="n">
-        <v>105296</v>
+        <v>109176</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221141</v>
+        <v>220299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1437,10 +1437,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>723318</v>
+        <v>723299</v>
       </c>
       <c r="R9" t="n">
-        <v>6412902</v>
+        <v>6413005</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1506,7 +1506,7 @@
         <v>126075088</v>
       </c>
       <c r="B10" t="n">
-        <v>98377</v>
+        <v>98380</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
         <v>126075295</v>
       </c>
       <c r="B11" t="n">
-        <v>105296</v>
+        <v>105299</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
         <v>126075351</v>
       </c>
       <c r="B12" t="n">
-        <v>106642</v>
+        <v>106645</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         <v>126075247</v>
       </c>
       <c r="B13" t="n">
-        <v>96409</v>
+        <v>96412</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>126075046</v>
       </c>
       <c r="B14" t="n">
-        <v>109173</v>
+        <v>109176</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
         <v>126075422</v>
       </c>
       <c r="B15" t="n">
-        <v>106188</v>
+        <v>106191</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2114,45 +2114,59 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126075228</v>
+        <v>126075072</v>
       </c>
       <c r="B16" t="n">
-        <v>75011</v>
+        <v>57653</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6426</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Hemhagen, Nors, Gtl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>723347</v>
+        <v>723335</v>
       </c>
       <c r="R16" t="n">
-        <v>6413067</v>
+        <v>6413183</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2185,6 +2199,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Lockläte i lämplig biotop, senvuxna tallar med spår av spår av spillkråka, enstaka äldre potentiella boträd i skogen.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2215,59 +2234,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126075072</v>
+        <v>126075228</v>
       </c>
       <c r="B17" t="n">
-        <v>57653</v>
+        <v>75011</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>6426</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Hemhagen, Nors, Gtl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>723335</v>
+        <v>723347</v>
       </c>
       <c r="R17" t="n">
-        <v>6413183</v>
+        <v>6413067</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2300,11 +2305,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-05-16</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Lockläte i lämplig biotop, senvuxna tallar med spår av spår av spillkråka, enstaka äldre potentiella boträd i skogen.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2338,7 +2338,7 @@
         <v>126075041</v>
       </c>
       <c r="B18" t="n">
-        <v>109173</v>
+        <v>109176</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2439,7 +2439,7 @@
         <v>126075420</v>
       </c>
       <c r="B19" t="n">
-        <v>106188</v>
+        <v>106191</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2540,7 +2540,7 @@
         <v>126075192</v>
       </c>
       <c r="B20" t="n">
-        <v>103803</v>
+        <v>103806</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2637,7 +2637,7 @@
         <v>126075050</v>
       </c>
       <c r="B21" t="n">
-        <v>109173</v>
+        <v>109176</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         <v>126075043</v>
       </c>
       <c r="B22" t="n">
-        <v>109173</v>
+        <v>109176</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2839,7 +2839,7 @@
         <v>126075053</v>
       </c>
       <c r="B23" t="n">
-        <v>109173</v>
+        <v>109176</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2940,7 +2940,7 @@
         <v>126075040</v>
       </c>
       <c r="B24" t="n">
-        <v>109173</v>
+        <v>109176</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3041,7 +3041,7 @@
         <v>126075330</v>
       </c>
       <c r="B25" t="n">
-        <v>95952</v>
+        <v>95955</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3139,27 +3139,27 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126075357</v>
+        <v>126075095</v>
       </c>
       <c r="B26" t="n">
-        <v>106642</v>
+        <v>98380</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221849</v>
+        <v>219864</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3168,16 +3168,21 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Hemhagen, Nors, Gtl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>723324</v>
+        <v>723328</v>
       </c>
       <c r="R26" t="n">
-        <v>6412899</v>
+        <v>6412904</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3240,10 +3245,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126075052</v>
+        <v>126075049</v>
       </c>
       <c r="B27" t="n">
-        <v>109173</v>
+        <v>109176</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3275,10 +3280,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>723338</v>
+        <v>723331</v>
       </c>
       <c r="R27" t="n">
-        <v>6413224</v>
+        <v>6413195</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3341,10 +3346,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126075049</v>
+        <v>126075052</v>
       </c>
       <c r="B28" t="n">
-        <v>109173</v>
+        <v>109176</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3376,10 +3381,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>723331</v>
+        <v>723338</v>
       </c>
       <c r="R28" t="n">
-        <v>6413195</v>
+        <v>6413224</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3442,10 +3447,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126075193</v>
+        <v>126075357</v>
       </c>
       <c r="B29" t="n">
-        <v>103803</v>
+        <v>106645</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3453,19 +3458,23 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>224416</v>
+        <v>221849</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ljus solvända</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. nummularium</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3473,10 +3482,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>723321</v>
+        <v>723324</v>
       </c>
       <c r="R29" t="n">
-        <v>6412898</v>
+        <v>6412899</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3539,50 +3548,41 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126075095</v>
+        <v>126075193</v>
       </c>
       <c r="B30" t="n">
-        <v>98377</v>
+        <v>103806</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>219864</v>
+        <v>224416</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Ljus solvända</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Hemhagen, Nors, Gtl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>723328</v>
+        <v>723321</v>
       </c>
       <c r="R30" t="n">
-        <v>6412904</v>
+        <v>6412898</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3648,7 +3648,7 @@
         <v>126075054</v>
       </c>
       <c r="B31" t="n">
-        <v>109173</v>
+        <v>109176</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3749,7 +3749,7 @@
         <v>126075188</v>
       </c>
       <c r="B32" t="n">
-        <v>103803</v>
+        <v>103806</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3846,7 +3846,7 @@
         <v>126075189</v>
       </c>
       <c r="B33" t="n">
-        <v>103803</v>
+        <v>103806</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3943,7 +3943,7 @@
         <v>126075185</v>
       </c>
       <c r="B34" t="n">
-        <v>103803</v>
+        <v>103806</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4040,7 +4040,7 @@
         <v>126075031</v>
       </c>
       <c r="B35" t="n">
-        <v>109173</v>
+        <v>109176</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4141,7 +4141,7 @@
         <v>126075328</v>
       </c>
       <c r="B36" t="n">
-        <v>100531</v>
+        <v>100534</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4242,7 +4242,7 @@
         <v>126075421</v>
       </c>
       <c r="B37" t="n">
-        <v>106188</v>
+        <v>106191</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4459,7 +4459,7 @@
         <v>126075028</v>
       </c>
       <c r="B39" t="n">
-        <v>109173</v>
+        <v>109176</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4560,7 +4560,7 @@
         <v>126075039</v>
       </c>
       <c r="B40" t="n">
-        <v>109173</v>
+        <v>109176</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4661,7 +4661,7 @@
         <v>126075042</v>
       </c>
       <c r="B41" t="n">
-        <v>109173</v>
+        <v>109176</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4762,7 +4762,7 @@
         <v>126075030</v>
       </c>
       <c r="B42" t="n">
-        <v>109173</v>
+        <v>109176</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4860,10 +4860,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126075044</v>
+        <v>126075269</v>
       </c>
       <c r="B43" t="n">
-        <v>109173</v>
+        <v>107234</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4871,21 +4871,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220299</v>
+        <v>220079</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4895,10 +4895,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>723367</v>
+        <v>723282</v>
       </c>
       <c r="R43" t="n">
-        <v>6413134</v>
+        <v>6413048</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4961,10 +4961,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126075184</v>
+        <v>126075044</v>
       </c>
       <c r="B44" t="n">
-        <v>103803</v>
+        <v>109176</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4972,19 +4972,23 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>224416</v>
+        <v>220299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ljus solvända</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. nummularium</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr"/>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -4992,10 +4996,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>723240</v>
+        <v>723367</v>
       </c>
       <c r="R44" t="n">
-        <v>6413005</v>
+        <v>6413134</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5058,10 +5062,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126075269</v>
+        <v>126075184</v>
       </c>
       <c r="B45" t="n">
-        <v>107231</v>
+        <v>103806</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5069,23 +5073,19 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220079</v>
+        <v>224416</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Ljus solvända</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5093,10 +5093,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>723282</v>
+        <v>723240</v>
       </c>
       <c r="R45" t="n">
-        <v>6413048</v>
+        <v>6413005</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5162,7 +5162,7 @@
         <v>126075045</v>
       </c>
       <c r="B46" t="n">
-        <v>109173</v>
+        <v>109176</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5263,7 +5263,7 @@
         <v>126075412</v>
       </c>
       <c r="B47" t="n">
-        <v>106188</v>
+        <v>106191</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5364,7 +5364,7 @@
         <v>126075182</v>
       </c>
       <c r="B48" t="n">
-        <v>103803</v>
+        <v>103806</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5461,7 +5461,7 @@
         <v>126075047</v>
       </c>
       <c r="B49" t="n">
-        <v>109173</v>
+        <v>109176</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5562,7 +5562,7 @@
         <v>126075029</v>
       </c>
       <c r="B50" t="n">
-        <v>109173</v>
+        <v>109176</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5663,7 +5663,7 @@
         <v>126075096</v>
       </c>
       <c r="B51" t="n">
-        <v>98377</v>
+        <v>98380</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>

--- a/artfynd/A 15629-2024 artfynd.xlsx
+++ b/artfynd/A 15629-2024 artfynd.xlsx
@@ -2335,10 +2335,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126075041</v>
+        <v>126075192</v>
       </c>
       <c r="B18" t="n">
-        <v>109176</v>
+        <v>103806</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2346,23 +2346,19 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220299</v>
+        <v>224416</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Ljus solvända</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2370,10 +2366,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>723339</v>
+        <v>723305</v>
       </c>
       <c r="R18" t="n">
-        <v>6413055</v>
+        <v>6412896</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2436,10 +2432,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126075420</v>
+        <v>126075041</v>
       </c>
       <c r="B19" t="n">
-        <v>106191</v>
+        <v>109176</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2447,16 +2443,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221903</v>
+        <v>220299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2471,10 +2467,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>723302</v>
+        <v>723339</v>
       </c>
       <c r="R19" t="n">
-        <v>6412899</v>
+        <v>6413055</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2537,10 +2533,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126075192</v>
+        <v>126075420</v>
       </c>
       <c r="B20" t="n">
-        <v>103806</v>
+        <v>106191</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2548,19 +2544,23 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>224416</v>
+        <v>221903</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ljus solvända</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. nummularium</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr"/>
+          <t>Veronica spicata</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2568,10 +2568,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>723305</v>
+        <v>723302</v>
       </c>
       <c r="R20" t="n">
-        <v>6412896</v>
+        <v>6412899</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -5458,27 +5458,27 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126075047</v>
+        <v>126075096</v>
       </c>
       <c r="B49" t="n">
-        <v>109176</v>
+        <v>98380</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220299</v>
+        <v>219864</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -5487,16 +5487,21 @@
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Hemhagen, Nors, Gtl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>723335</v>
+        <v>723293</v>
       </c>
       <c r="R49" t="n">
-        <v>6413175</v>
+        <v>6412906</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5559,7 +5564,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126075029</v>
+        <v>126075047</v>
       </c>
       <c r="B50" t="n">
         <v>109176</v>
@@ -5594,10 +5599,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>723216</v>
+        <v>723335</v>
       </c>
       <c r="R50" t="n">
-        <v>6412940</v>
+        <v>6413175</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5660,27 +5665,27 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126075096</v>
+        <v>126075029</v>
       </c>
       <c r="B51" t="n">
-        <v>98380</v>
+        <v>109176</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>219864</v>
+        <v>220299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -5689,21 +5694,16 @@
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Hemhagen, Nors, Gtl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>723293</v>
+        <v>723216</v>
       </c>
       <c r="R51" t="n">
-        <v>6412906</v>
+        <v>6412940</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>

--- a/artfynd/A 15629-2024 artfynd.xlsx
+++ b/artfynd/A 15629-2024 artfynd.xlsx
@@ -998,32 +998,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126075032</v>
+        <v>126075167</v>
       </c>
       <c r="B5" t="n">
-        <v>109176</v>
+        <v>98374</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220299</v>
+        <v>219862</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>723222</v>
+        <v>723327</v>
       </c>
       <c r="R5" t="n">
-        <v>6412868</v>
+        <v>6413202</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,7 +1099,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126075055</v>
+        <v>126075032</v>
       </c>
       <c r="B6" t="n">
         <v>109176</v>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>723291</v>
+        <v>723222</v>
       </c>
       <c r="R6" t="n">
-        <v>6413160</v>
+        <v>6412868</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1164,12 +1164,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,32 +1200,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126075167</v>
+        <v>126075055</v>
       </c>
       <c r="B7" t="n">
-        <v>98374</v>
+        <v>109176</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219862</v>
+        <v>220299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>723327</v>
+        <v>723291</v>
       </c>
       <c r="R7" t="n">
-        <v>6413202</v>
+        <v>6413160</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1265,12 +1265,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1301,10 +1301,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126075294</v>
+        <v>126075088</v>
       </c>
       <c r="B8" t="n">
-        <v>105299</v>
+        <v>98380</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1312,16 +1312,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221141</v>
+        <v>219864</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1330,16 +1330,21 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hemhagen, Nors, Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>723318</v>
+        <v>723278</v>
       </c>
       <c r="R8" t="n">
-        <v>6412902</v>
+        <v>6413037</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1402,27 +1407,27 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126075038</v>
+        <v>126075294</v>
       </c>
       <c r="B9" t="n">
-        <v>109176</v>
+        <v>105299</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220299</v>
+        <v>221141</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1437,10 +1442,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>723299</v>
+        <v>723318</v>
       </c>
       <c r="R9" t="n">
-        <v>6413005</v>
+        <v>6412902</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1503,27 +1508,27 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126075088</v>
+        <v>126075038</v>
       </c>
       <c r="B10" t="n">
-        <v>98380</v>
+        <v>109176</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219864</v>
+        <v>220299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1532,21 +1537,16 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hemhagen, Nors, Gtl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>723278</v>
+        <v>723299</v>
       </c>
       <c r="R10" t="n">
-        <v>6413037</v>
+        <v>6413005</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1912,10 +1912,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126075046</v>
+        <v>126075422</v>
       </c>
       <c r="B14" t="n">
-        <v>109176</v>
+        <v>106191</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1923,16 +1923,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220299</v>
+        <v>221903</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1947,10 +1947,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>723345</v>
+        <v>723297</v>
       </c>
       <c r="R14" t="n">
-        <v>6413172</v>
+        <v>6412905</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2013,10 +2013,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126075422</v>
+        <v>126075046</v>
       </c>
       <c r="B15" t="n">
-        <v>106191</v>
+        <v>109176</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2024,16 +2024,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221903</v>
+        <v>220299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2048,10 +2048,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>723297</v>
+        <v>723345</v>
       </c>
       <c r="R15" t="n">
-        <v>6412905</v>
+        <v>6413172</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2114,59 +2114,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126075072</v>
+        <v>126075228</v>
       </c>
       <c r="B16" t="n">
-        <v>57653</v>
+        <v>75011</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>6426</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Hemhagen, Nors, Gtl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>723335</v>
+        <v>723347</v>
       </c>
       <c r="R16" t="n">
-        <v>6413183</v>
+        <v>6413067</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2199,11 +2185,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-05-16</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Lockläte i lämplig biotop, senvuxna tallar med spår av spår av spillkråka, enstaka äldre potentiella boträd i skogen.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2234,45 +2215,59 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126075228</v>
+        <v>126075072</v>
       </c>
       <c r="B17" t="n">
-        <v>75011</v>
+        <v>57653</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6426</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Hemhagen, Nors, Gtl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>723347</v>
+        <v>723335</v>
       </c>
       <c r="R17" t="n">
-        <v>6413067</v>
+        <v>6413183</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2305,6 +2300,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Lockläte i lämplig biotop, senvuxna tallar med spår av spår av spillkråka, enstaka äldre potentiella boträd i skogen.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2335,10 +2335,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126075192</v>
+        <v>126075420</v>
       </c>
       <c r="B18" t="n">
-        <v>103806</v>
+        <v>106191</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2346,19 +2346,23 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>224416</v>
+        <v>221903</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ljus solvända</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. nummularium</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
+          <t>Veronica spicata</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2366,10 +2370,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>723305</v>
+        <v>723302</v>
       </c>
       <c r="R18" t="n">
-        <v>6412896</v>
+        <v>6412899</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2533,10 +2537,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126075420</v>
+        <v>126075192</v>
       </c>
       <c r="B20" t="n">
-        <v>106191</v>
+        <v>103806</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2544,23 +2548,19 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221903</v>
+        <v>224416</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Ljus solvända</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2568,10 +2568,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>723302</v>
+        <v>723305</v>
       </c>
       <c r="R20" t="n">
-        <v>6412899</v>
+        <v>6412896</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3245,10 +3245,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126075049</v>
+        <v>126075193</v>
       </c>
       <c r="B27" t="n">
-        <v>109176</v>
+        <v>103806</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3256,23 +3256,19 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220299</v>
+        <v>224416</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Ljus solvända</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3280,10 +3276,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>723331</v>
+        <v>723321</v>
       </c>
       <c r="R27" t="n">
-        <v>6413195</v>
+        <v>6412898</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3447,10 +3443,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126075357</v>
+        <v>126075049</v>
       </c>
       <c r="B29" t="n">
-        <v>106645</v>
+        <v>109176</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3458,16 +3454,16 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221849</v>
+        <v>220299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3482,10 +3478,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>723324</v>
+        <v>723331</v>
       </c>
       <c r="R29" t="n">
-        <v>6412899</v>
+        <v>6413195</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3548,10 +3544,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126075193</v>
+        <v>126075357</v>
       </c>
       <c r="B30" t="n">
-        <v>103806</v>
+        <v>106645</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3559,19 +3555,23 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>224416</v>
+        <v>221849</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ljus solvända</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. nummularium</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr"/>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3579,10 +3579,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>723321</v>
+        <v>723324</v>
       </c>
       <c r="R30" t="n">
-        <v>6412898</v>
+        <v>6412899</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3645,10 +3645,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126075054</v>
+        <v>126075188</v>
       </c>
       <c r="B31" t="n">
-        <v>109176</v>
+        <v>103806</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3656,23 +3656,19 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220299</v>
+        <v>224416</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Ljus solvända</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3680,10 +3676,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>723389</v>
+        <v>723322</v>
       </c>
       <c r="R31" t="n">
-        <v>6413195</v>
+        <v>6412738</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3746,7 +3742,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126075188</v>
+        <v>126075189</v>
       </c>
       <c r="B32" t="n">
         <v>103806</v>
@@ -3777,10 +3773,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>723322</v>
+        <v>723328</v>
       </c>
       <c r="R32" t="n">
-        <v>6412738</v>
+        <v>6412741</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3843,7 +3839,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126075189</v>
+        <v>126075185</v>
       </c>
       <c r="B33" t="n">
         <v>103806</v>
@@ -3874,10 +3870,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>723328</v>
+        <v>723250</v>
       </c>
       <c r="R33" t="n">
-        <v>6412741</v>
+        <v>6413023</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3940,10 +3936,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126075185</v>
+        <v>126075054</v>
       </c>
       <c r="B34" t="n">
-        <v>103806</v>
+        <v>109176</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3951,19 +3947,23 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>224416</v>
+        <v>220299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ljus solvända</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. nummularium</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr"/>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -3971,10 +3971,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>723250</v>
+        <v>723389</v>
       </c>
       <c r="R34" t="n">
-        <v>6413023</v>
+        <v>6413195</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4037,32 +4037,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126075031</v>
+        <v>126075328</v>
       </c>
       <c r="B35" t="n">
-        <v>109176</v>
+        <v>100534</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220299</v>
+        <v>222498</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4072,10 +4072,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>723216</v>
+        <v>723335</v>
       </c>
       <c r="R35" t="n">
-        <v>6412876</v>
+        <v>6413175</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4138,32 +4138,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126075328</v>
+        <v>126075031</v>
       </c>
       <c r="B36" t="n">
-        <v>100534</v>
+        <v>109176</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>222498</v>
+        <v>220299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4173,10 +4173,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>723335</v>
+        <v>723216</v>
       </c>
       <c r="R36" t="n">
-        <v>6413175</v>
+        <v>6412876</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4860,10 +4860,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126075269</v>
+        <v>126075044</v>
       </c>
       <c r="B43" t="n">
-        <v>107234</v>
+        <v>109176</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4871,21 +4871,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220079</v>
+        <v>220299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4895,10 +4895,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>723282</v>
+        <v>723367</v>
       </c>
       <c r="R43" t="n">
-        <v>6413048</v>
+        <v>6413134</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4961,10 +4961,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126075044</v>
+        <v>126075269</v>
       </c>
       <c r="B44" t="n">
-        <v>109176</v>
+        <v>107234</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4972,21 +4972,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220299</v>
+        <v>220079</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4996,10 +4996,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>723367</v>
+        <v>723282</v>
       </c>
       <c r="R44" t="n">
-        <v>6413134</v>
+        <v>6413048</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>

--- a/artfynd/A 15629-2024 artfynd.xlsx
+++ b/artfynd/A 15629-2024 artfynd.xlsx
@@ -1609,27 +1609,27 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126075295</v>
+        <v>126075351</v>
       </c>
       <c r="B11" t="n">
-        <v>105299</v>
+        <v>106645</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221141</v>
+        <v>221849</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1644,10 +1644,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>723293</v>
+        <v>723310</v>
       </c>
       <c r="R11" t="n">
-        <v>6412916</v>
+        <v>6412729</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1710,27 +1710,27 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126075351</v>
+        <v>126075295</v>
       </c>
       <c r="B12" t="n">
-        <v>106645</v>
+        <v>105299</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221849</v>
+        <v>221141</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1745,10 +1745,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>723310</v>
+        <v>723293</v>
       </c>
       <c r="R12" t="n">
-        <v>6412729</v>
+        <v>6412916</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2335,10 +2335,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126075420</v>
+        <v>126075041</v>
       </c>
       <c r="B18" t="n">
-        <v>106191</v>
+        <v>109176</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2346,16 +2346,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221903</v>
+        <v>220299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2370,10 +2370,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>723302</v>
+        <v>723339</v>
       </c>
       <c r="R18" t="n">
-        <v>6412899</v>
+        <v>6413055</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2436,10 +2436,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126075041</v>
+        <v>126075420</v>
       </c>
       <c r="B19" t="n">
-        <v>109176</v>
+        <v>106191</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2447,16 +2447,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220299</v>
+        <v>221903</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2471,10 +2471,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>723339</v>
+        <v>723302</v>
       </c>
       <c r="R19" t="n">
-        <v>6413055</v>
+        <v>6412899</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3139,50 +3139,41 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126075095</v>
+        <v>126075193</v>
       </c>
       <c r="B26" t="n">
-        <v>98380</v>
+        <v>103806</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>219864</v>
+        <v>224416</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Ljus solvända</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Hemhagen, Nors, Gtl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>723328</v>
+        <v>723321</v>
       </c>
       <c r="R26" t="n">
-        <v>6412904</v>
+        <v>6412898</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3245,41 +3236,50 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126075193</v>
+        <v>126075095</v>
       </c>
       <c r="B27" t="n">
-        <v>103806</v>
+        <v>98380</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>224416</v>
+        <v>219864</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ljus solvända</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. nummularium</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr"/>
+          <t>Orchis mascula</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Hemhagen, Nors, Gtl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>723321</v>
+        <v>723328</v>
       </c>
       <c r="R27" t="n">
-        <v>6412898</v>
+        <v>6412904</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3645,10 +3645,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126075188</v>
+        <v>126075054</v>
       </c>
       <c r="B31" t="n">
-        <v>103806</v>
+        <v>109176</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3656,19 +3656,23 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>224416</v>
+        <v>220299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ljus solvända</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. nummularium</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr"/>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3676,10 +3680,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>723322</v>
+        <v>723389</v>
       </c>
       <c r="R31" t="n">
-        <v>6412738</v>
+        <v>6413195</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3742,7 +3746,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126075189</v>
+        <v>126075188</v>
       </c>
       <c r="B32" t="n">
         <v>103806</v>
@@ -3773,10 +3777,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>723328</v>
+        <v>723322</v>
       </c>
       <c r="R32" t="n">
-        <v>6412741</v>
+        <v>6412738</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3839,7 +3843,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126075185</v>
+        <v>126075189</v>
       </c>
       <c r="B33" t="n">
         <v>103806</v>
@@ -3870,10 +3874,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>723250</v>
+        <v>723328</v>
       </c>
       <c r="R33" t="n">
-        <v>6413023</v>
+        <v>6412741</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3936,10 +3940,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126075054</v>
+        <v>126075185</v>
       </c>
       <c r="B34" t="n">
-        <v>109176</v>
+        <v>103806</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3947,23 +3951,19 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220299</v>
+        <v>224416</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Ljus solvända</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -3971,10 +3971,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>723389</v>
+        <v>723250</v>
       </c>
       <c r="R34" t="n">
-        <v>6413195</v>
+        <v>6413023</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>

--- a/artfynd/A 15629-2024 artfynd.xlsx
+++ b/artfynd/A 15629-2024 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>126075195</v>
       </c>
       <c r="B3" t="n">
-        <v>103806</v>
+        <v>103815</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,27 +892,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126075089</v>
+        <v>126075032</v>
       </c>
       <c r="B4" t="n">
-        <v>98380</v>
+        <v>109185</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219864</v>
+        <v>220299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -921,21 +921,16 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Hemhagen, Nors, Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>723237</v>
+        <v>723222</v>
       </c>
       <c r="R4" t="n">
-        <v>6413005</v>
+        <v>6412868</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -998,32 +993,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126075167</v>
+        <v>126075055</v>
       </c>
       <c r="B5" t="n">
-        <v>98374</v>
+        <v>109185</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219862</v>
+        <v>220299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1028,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>723327</v>
+        <v>723291</v>
       </c>
       <c r="R5" t="n">
-        <v>6413202</v>
+        <v>6413160</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,12 +1058,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1099,27 +1094,27 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126075032</v>
+        <v>126075089</v>
       </c>
       <c r="B6" t="n">
-        <v>109176</v>
+        <v>98389</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220299</v>
+        <v>219864</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1128,16 +1123,21 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hemhagen, Nors, Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>723222</v>
+        <v>723237</v>
       </c>
       <c r="R6" t="n">
-        <v>6412868</v>
+        <v>6413005</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1200,32 +1200,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126075055</v>
+        <v>126075167</v>
       </c>
       <c r="B7" t="n">
-        <v>109176</v>
+        <v>98383</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220299</v>
+        <v>219862</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>723291</v>
+        <v>723327</v>
       </c>
       <c r="R7" t="n">
-        <v>6413160</v>
+        <v>6413202</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1265,12 +1265,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1301,10 +1301,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126075088</v>
+        <v>126075294</v>
       </c>
       <c r="B8" t="n">
-        <v>98380</v>
+        <v>105308</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1312,16 +1312,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219864</v>
+        <v>221141</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1330,21 +1330,16 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hemhagen, Nors, Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>723278</v>
+        <v>723318</v>
       </c>
       <c r="R8" t="n">
-        <v>6413037</v>
+        <v>6412902</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1407,27 +1402,27 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126075294</v>
+        <v>126075038</v>
       </c>
       <c r="B9" t="n">
-        <v>105299</v>
+        <v>109185</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221141</v>
+        <v>220299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1442,10 +1437,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>723318</v>
+        <v>723299</v>
       </c>
       <c r="R9" t="n">
-        <v>6412902</v>
+        <v>6413005</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1508,27 +1503,27 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126075038</v>
+        <v>126075088</v>
       </c>
       <c r="B10" t="n">
-        <v>109176</v>
+        <v>98389</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220299</v>
+        <v>219864</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1537,16 +1532,21 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hemhagen, Nors, Gtl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>723299</v>
+        <v>723278</v>
       </c>
       <c r="R10" t="n">
-        <v>6413005</v>
+        <v>6413037</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1609,27 +1609,27 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126075351</v>
+        <v>126075295</v>
       </c>
       <c r="B11" t="n">
-        <v>106645</v>
+        <v>105308</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221849</v>
+        <v>221141</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1644,10 +1644,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>723310</v>
+        <v>723293</v>
       </c>
       <c r="R11" t="n">
-        <v>6412729</v>
+        <v>6412916</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1710,27 +1710,27 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126075295</v>
+        <v>126075351</v>
       </c>
       <c r="B12" t="n">
-        <v>105299</v>
+        <v>106654</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221141</v>
+        <v>221849</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1745,10 +1745,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>723293</v>
+        <v>723310</v>
       </c>
       <c r="R12" t="n">
-        <v>6412916</v>
+        <v>6412729</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1814,7 +1814,7 @@
         <v>126075247</v>
       </c>
       <c r="B13" t="n">
-        <v>96412</v>
+        <v>96421</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1912,10 +1912,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126075422</v>
+        <v>126075046</v>
       </c>
       <c r="B14" t="n">
-        <v>106191</v>
+        <v>109185</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1923,16 +1923,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221903</v>
+        <v>220299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1947,10 +1947,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>723297</v>
+        <v>723345</v>
       </c>
       <c r="R14" t="n">
-        <v>6412905</v>
+        <v>6413172</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2013,10 +2013,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126075046</v>
+        <v>126075422</v>
       </c>
       <c r="B15" t="n">
-        <v>109176</v>
+        <v>106200</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2024,16 +2024,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220299</v>
+        <v>221903</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2048,10 +2048,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>723345</v>
+        <v>723297</v>
       </c>
       <c r="R15" t="n">
-        <v>6413172</v>
+        <v>6412905</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2114,45 +2114,59 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126075228</v>
+        <v>126075072</v>
       </c>
       <c r="B16" t="n">
-        <v>75011</v>
+        <v>57654</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6426</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Hemhagen, Nors, Gtl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>723347</v>
+        <v>723335</v>
       </c>
       <c r="R16" t="n">
-        <v>6413067</v>
+        <v>6413183</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2185,6 +2199,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Lockläte i lämplig biotop, senvuxna tallar med spår av spår av spillkråka, enstaka äldre potentiella boträd i skogen.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2215,59 +2234,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126075072</v>
+        <v>126075228</v>
       </c>
       <c r="B17" t="n">
-        <v>57653</v>
+        <v>75014</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>6426</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Hemhagen, Nors, Gtl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>723335</v>
+        <v>723347</v>
       </c>
       <c r="R17" t="n">
-        <v>6413183</v>
+        <v>6413067</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2300,11 +2305,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-05-16</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Lockläte i lämplig biotop, senvuxna tallar med spår av spår av spillkråka, enstaka äldre potentiella boträd i skogen.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2335,10 +2335,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126075041</v>
+        <v>126075192</v>
       </c>
       <c r="B18" t="n">
-        <v>109176</v>
+        <v>103815</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2346,23 +2346,19 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220299</v>
+        <v>224416</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Ljus solvända</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2370,10 +2366,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>723339</v>
+        <v>723305</v>
       </c>
       <c r="R18" t="n">
-        <v>6413055</v>
+        <v>6412896</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2439,7 +2435,7 @@
         <v>126075420</v>
       </c>
       <c r="B19" t="n">
-        <v>106191</v>
+        <v>106200</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2537,10 +2533,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126075192</v>
+        <v>126075041</v>
       </c>
       <c r="B20" t="n">
-        <v>103806</v>
+        <v>109185</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2548,19 +2544,23 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>224416</v>
+        <v>220299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ljus solvända</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. nummularium</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr"/>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2568,10 +2568,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>723305</v>
+        <v>723339</v>
       </c>
       <c r="R20" t="n">
-        <v>6412896</v>
+        <v>6413055</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2637,7 +2637,7 @@
         <v>126075050</v>
       </c>
       <c r="B21" t="n">
-        <v>109176</v>
+        <v>109185</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         <v>126075043</v>
       </c>
       <c r="B22" t="n">
-        <v>109176</v>
+        <v>109185</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2839,7 +2839,7 @@
         <v>126075053</v>
       </c>
       <c r="B23" t="n">
-        <v>109176</v>
+        <v>109185</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2940,7 +2940,7 @@
         <v>126075040</v>
       </c>
       <c r="B24" t="n">
-        <v>109176</v>
+        <v>109185</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3038,34 +3038,30 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126075330</v>
+        <v>126075193</v>
       </c>
       <c r="B25" t="n">
-        <v>95955</v>
+        <v>103815</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2180</v>
+        <v>224416</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Ljus solvända</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3073,10 +3069,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>723341</v>
+        <v>723321</v>
       </c>
       <c r="R25" t="n">
-        <v>6413230</v>
+        <v>6412898</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3139,10 +3135,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126075193</v>
+        <v>126075052</v>
       </c>
       <c r="B26" t="n">
-        <v>103806</v>
+        <v>109185</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3150,19 +3146,23 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>224416</v>
+        <v>220299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ljus solvända</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. nummularium</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr"/>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3170,10 +3170,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>723321</v>
+        <v>723338</v>
       </c>
       <c r="R26" t="n">
-        <v>6412898</v>
+        <v>6413224</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3236,27 +3236,27 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126075095</v>
+        <v>126075049</v>
       </c>
       <c r="B27" t="n">
-        <v>98380</v>
+        <v>109185</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>219864</v>
+        <v>220299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3265,21 +3265,16 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Hemhagen, Nors, Gtl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>723328</v>
+        <v>723331</v>
       </c>
       <c r="R27" t="n">
-        <v>6412904</v>
+        <v>6413195</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3342,10 +3337,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126075052</v>
+        <v>126075357</v>
       </c>
       <c r="B28" t="n">
-        <v>109176</v>
+        <v>106654</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3353,16 +3348,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220299</v>
+        <v>221849</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3377,10 +3372,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>723338</v>
+        <v>723324</v>
       </c>
       <c r="R28" t="n">
-        <v>6413224</v>
+        <v>6412899</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3443,32 +3438,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126075049</v>
+        <v>126075330</v>
       </c>
       <c r="B29" t="n">
-        <v>109176</v>
+        <v>95964</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220299</v>
+        <v>2180</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3478,10 +3473,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>723331</v>
+        <v>723341</v>
       </c>
       <c r="R29" t="n">
-        <v>6413195</v>
+        <v>6413230</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3544,27 +3539,27 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126075357</v>
+        <v>126075095</v>
       </c>
       <c r="B30" t="n">
-        <v>106645</v>
+        <v>98389</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221849</v>
+        <v>219864</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3573,16 +3568,21 @@
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Hemhagen, Nors, Gtl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>723324</v>
+        <v>723328</v>
       </c>
       <c r="R30" t="n">
-        <v>6412899</v>
+        <v>6412904</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3648,7 +3648,7 @@
         <v>126075054</v>
       </c>
       <c r="B31" t="n">
-        <v>109176</v>
+        <v>109185</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3749,7 +3749,7 @@
         <v>126075188</v>
       </c>
       <c r="B32" t="n">
-        <v>103806</v>
+        <v>103815</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3846,7 +3846,7 @@
         <v>126075189</v>
       </c>
       <c r="B33" t="n">
-        <v>103806</v>
+        <v>103815</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3943,7 +3943,7 @@
         <v>126075185</v>
       </c>
       <c r="B34" t="n">
-        <v>103806</v>
+        <v>103815</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4037,32 +4037,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126075328</v>
+        <v>126075031</v>
       </c>
       <c r="B35" t="n">
-        <v>100534</v>
+        <v>109185</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>222498</v>
+        <v>220299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4072,10 +4072,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>723335</v>
+        <v>723216</v>
       </c>
       <c r="R35" t="n">
-        <v>6413175</v>
+        <v>6412876</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4138,32 +4138,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126075031</v>
+        <v>126075328</v>
       </c>
       <c r="B36" t="n">
-        <v>109176</v>
+        <v>100543</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220299</v>
+        <v>222498</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4173,10 +4173,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>723216</v>
+        <v>723335</v>
       </c>
       <c r="R36" t="n">
-        <v>6412876</v>
+        <v>6413175</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4239,10 +4239,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126075421</v>
+        <v>126075165</v>
       </c>
       <c r="B37" t="n">
-        <v>106191</v>
+        <v>19793</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4250,21 +4250,16 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221903</v>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Axveronika</t>
-        </is>
+        <v>241122</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Orellia scorzonerae</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Robineau-Desvoidy, 1830)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4274,10 +4269,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>723321</v>
+        <v>723375</v>
       </c>
       <c r="R37" t="n">
-        <v>6412897</v>
+        <v>6413131</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4312,6 +4307,11 @@
           <t>2024-05-16</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>På knoppar av värdväxten svinrot.</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -4320,6 +4320,21 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>svinrot</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -4340,10 +4355,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126075165</v>
+        <v>126075421</v>
       </c>
       <c r="B38" t="n">
-        <v>19793</v>
+        <v>106200</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4351,16 +4366,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>241122</v>
+        <v>221903</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Axveronika</t>
+        </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Orellia scorzonerae</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Robineau-Desvoidy, 1830)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4370,10 +4390,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>723375</v>
+        <v>723321</v>
       </c>
       <c r="R38" t="n">
-        <v>6413131</v>
+        <v>6412897</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4408,11 +4428,6 @@
           <t>2024-05-16</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>På knoppar av värdväxten svinrot.</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -4421,21 +4436,6 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>svinrot</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Scorzonera humilis</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Scorzonera humilis</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -4459,7 +4459,7 @@
         <v>126075028</v>
       </c>
       <c r="B39" t="n">
-        <v>109176</v>
+        <v>109185</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4560,7 +4560,7 @@
         <v>126075039</v>
       </c>
       <c r="B40" t="n">
-        <v>109176</v>
+        <v>109185</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4661,7 +4661,7 @@
         <v>126075042</v>
       </c>
       <c r="B41" t="n">
-        <v>109176</v>
+        <v>109185</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4762,7 +4762,7 @@
         <v>126075030</v>
       </c>
       <c r="B42" t="n">
-        <v>109176</v>
+        <v>109185</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4860,10 +4860,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126075044</v>
+        <v>126075269</v>
       </c>
       <c r="B43" t="n">
-        <v>109176</v>
+        <v>107243</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4871,21 +4871,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220299</v>
+        <v>220079</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4895,10 +4895,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>723367</v>
+        <v>723282</v>
       </c>
       <c r="R43" t="n">
-        <v>6413134</v>
+        <v>6413048</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4961,10 +4961,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126075269</v>
+        <v>126075044</v>
       </c>
       <c r="B44" t="n">
-        <v>107234</v>
+        <v>109185</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4972,21 +4972,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220079</v>
+        <v>220299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4996,10 +4996,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>723282</v>
+        <v>723367</v>
       </c>
       <c r="R44" t="n">
-        <v>6413048</v>
+        <v>6413134</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5065,7 +5065,7 @@
         <v>126075184</v>
       </c>
       <c r="B45" t="n">
-        <v>103806</v>
+        <v>103815</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5159,10 +5159,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126075045</v>
+        <v>126075412</v>
       </c>
       <c r="B46" t="n">
-        <v>109176</v>
+        <v>106200</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5170,16 +5170,16 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220299</v>
+        <v>221903</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -5194,10 +5194,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>723352</v>
+        <v>723243</v>
       </c>
       <c r="R46" t="n">
-        <v>6413153</v>
+        <v>6413018</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5260,10 +5260,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126075412</v>
+        <v>126075182</v>
       </c>
       <c r="B47" t="n">
-        <v>106191</v>
+        <v>103815</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5271,23 +5271,19 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221903</v>
+        <v>224416</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Ljus solvända</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5295,10 +5291,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>723243</v>
+        <v>723272</v>
       </c>
       <c r="R47" t="n">
-        <v>6413018</v>
+        <v>6413033</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5361,10 +5357,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126075182</v>
+        <v>126075045</v>
       </c>
       <c r="B48" t="n">
-        <v>103806</v>
+        <v>109185</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5372,19 +5368,23 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>224416</v>
+        <v>220299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ljus solvända</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. nummularium</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr"/>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -5392,10 +5392,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>723272</v>
+        <v>723352</v>
       </c>
       <c r="R48" t="n">
-        <v>6413033</v>
+        <v>6413153</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5458,27 +5458,27 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126075096</v>
+        <v>126075047</v>
       </c>
       <c r="B49" t="n">
-        <v>98380</v>
+        <v>109185</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>219864</v>
+        <v>220299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -5487,21 +5487,16 @@
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Hemhagen, Nors, Gtl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>723293</v>
+        <v>723335</v>
       </c>
       <c r="R49" t="n">
-        <v>6412906</v>
+        <v>6413175</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5564,10 +5559,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126075047</v>
+        <v>126075029</v>
       </c>
       <c r="B50" t="n">
-        <v>109176</v>
+        <v>109185</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5599,10 +5594,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>723335</v>
+        <v>723216</v>
       </c>
       <c r="R50" t="n">
-        <v>6413175</v>
+        <v>6412940</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5665,27 +5660,27 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126075029</v>
+        <v>126075096</v>
       </c>
       <c r="B51" t="n">
-        <v>109176</v>
+        <v>98389</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220299</v>
+        <v>219864</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -5694,16 +5689,21 @@
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Hemhagen, Nors, Gtl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>723216</v>
+        <v>723293</v>
       </c>
       <c r="R51" t="n">
-        <v>6412940</v>
+        <v>6412906</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>

--- a/artfynd/A 15629-2024 artfynd.xlsx
+++ b/artfynd/A 15629-2024 artfynd.xlsx
@@ -2335,10 +2335,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126075192</v>
+        <v>126075041</v>
       </c>
       <c r="B18" t="n">
-        <v>103815</v>
+        <v>109185</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2346,19 +2346,23 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>224416</v>
+        <v>220299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ljus solvända</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. nummularium</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2366,10 +2370,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>723305</v>
+        <v>723339</v>
       </c>
       <c r="R18" t="n">
-        <v>6412896</v>
+        <v>6413055</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2432,10 +2436,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126075420</v>
+        <v>126075192</v>
       </c>
       <c r="B19" t="n">
-        <v>106200</v>
+        <v>103815</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2443,23 +2447,19 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221903</v>
+        <v>224416</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Ljus solvända</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2467,10 +2467,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>723302</v>
+        <v>723305</v>
       </c>
       <c r="R19" t="n">
-        <v>6412899</v>
+        <v>6412896</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2533,10 +2533,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126075041</v>
+        <v>126075420</v>
       </c>
       <c r="B20" t="n">
-        <v>109185</v>
+        <v>106200</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2544,16 +2544,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220299</v>
+        <v>221903</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2568,10 +2568,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>723339</v>
+        <v>723302</v>
       </c>
       <c r="R20" t="n">
-        <v>6413055</v>
+        <v>6412899</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2735,7 +2735,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126075043</v>
+        <v>126075040</v>
       </c>
       <c r="B22" t="n">
         <v>109185</v>
@@ -2770,10 +2770,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>723368</v>
+        <v>723311</v>
       </c>
       <c r="R22" t="n">
-        <v>6413087</v>
+        <v>6413017</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2836,7 +2836,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126075053</v>
+        <v>126075043</v>
       </c>
       <c r="B23" t="n">
         <v>109185</v>
@@ -2871,10 +2871,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>723356</v>
+        <v>723368</v>
       </c>
       <c r="R23" t="n">
-        <v>6413200</v>
+        <v>6413087</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2937,7 +2937,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126075040</v>
+        <v>126075053</v>
       </c>
       <c r="B24" t="n">
         <v>109185</v>
@@ -2972,10 +2972,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>723311</v>
+        <v>723356</v>
       </c>
       <c r="R24" t="n">
-        <v>6413017</v>
+        <v>6413200</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>

--- a/artfynd/A 15629-2024 artfynd.xlsx
+++ b/artfynd/A 15629-2024 artfynd.xlsx
@@ -1402,27 +1402,27 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126075038</v>
+        <v>126075088</v>
       </c>
       <c r="B9" t="n">
-        <v>109185</v>
+        <v>98389</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220299</v>
+        <v>219864</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1431,16 +1431,21 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hemhagen, Nors, Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>723299</v>
+        <v>723278</v>
       </c>
       <c r="R9" t="n">
-        <v>6413005</v>
+        <v>6413037</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1503,27 +1508,27 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126075088</v>
+        <v>126075038</v>
       </c>
       <c r="B10" t="n">
-        <v>98389</v>
+        <v>109185</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219864</v>
+        <v>220299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1532,21 +1537,16 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hemhagen, Nors, Gtl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>723278</v>
+        <v>723299</v>
       </c>
       <c r="R10" t="n">
-        <v>6413037</v>
+        <v>6413005</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -2114,59 +2114,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126075072</v>
+        <v>126075228</v>
       </c>
       <c r="B16" t="n">
-        <v>57654</v>
+        <v>75014</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>6426</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Hemhagen, Nors, Gtl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>723335</v>
+        <v>723347</v>
       </c>
       <c r="R16" t="n">
-        <v>6413183</v>
+        <v>6413067</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2199,11 +2185,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-05-16</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Lockläte i lämplig biotop, senvuxna tallar med spår av spår av spillkråka, enstaka äldre potentiella boträd i skogen.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2234,45 +2215,59 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126075228</v>
+        <v>126075072</v>
       </c>
       <c r="B17" t="n">
-        <v>75014</v>
+        <v>57654</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6426</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Hemhagen, Nors, Gtl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>723347</v>
+        <v>723335</v>
       </c>
       <c r="R17" t="n">
-        <v>6413067</v>
+        <v>6413183</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2305,6 +2300,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Lockläte i lämplig biotop, senvuxna tallar med spår av spår av spillkråka, enstaka äldre potentiella boträd i skogen.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2335,10 +2335,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126075041</v>
+        <v>126075420</v>
       </c>
       <c r="B18" t="n">
-        <v>109185</v>
+        <v>106200</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2346,16 +2346,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220299</v>
+        <v>221903</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2370,10 +2370,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>723339</v>
+        <v>723302</v>
       </c>
       <c r="R18" t="n">
-        <v>6413055</v>
+        <v>6412899</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2533,10 +2533,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126075420</v>
+        <v>126075041</v>
       </c>
       <c r="B20" t="n">
-        <v>106200</v>
+        <v>109185</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2544,16 +2544,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221903</v>
+        <v>220299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2568,10 +2568,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>723302</v>
+        <v>723339</v>
       </c>
       <c r="R20" t="n">
-        <v>6412899</v>
+        <v>6413055</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2735,7 +2735,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126075040</v>
+        <v>126075043</v>
       </c>
       <c r="B22" t="n">
         <v>109185</v>
@@ -2770,10 +2770,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>723311</v>
+        <v>723368</v>
       </c>
       <c r="R22" t="n">
-        <v>6413017</v>
+        <v>6413087</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2836,7 +2836,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126075043</v>
+        <v>126075053</v>
       </c>
       <c r="B23" t="n">
         <v>109185</v>
@@ -2871,10 +2871,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>723368</v>
+        <v>723356</v>
       </c>
       <c r="R23" t="n">
-        <v>6413087</v>
+        <v>6413200</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2937,7 +2937,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126075053</v>
+        <v>126075040</v>
       </c>
       <c r="B24" t="n">
         <v>109185</v>
@@ -2972,10 +2972,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>723356</v>
+        <v>723311</v>
       </c>
       <c r="R24" t="n">
-        <v>6413200</v>
+        <v>6413017</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3337,27 +3337,27 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126075357</v>
+        <v>126075095</v>
       </c>
       <c r="B28" t="n">
-        <v>106654</v>
+        <v>98389</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221849</v>
+        <v>219864</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3366,16 +3366,21 @@
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Hemhagen, Nors, Gtl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>723324</v>
+        <v>723328</v>
       </c>
       <c r="R28" t="n">
-        <v>6412899</v>
+        <v>6412904</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3438,32 +3443,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126075330</v>
+        <v>126075357</v>
       </c>
       <c r="B29" t="n">
-        <v>95964</v>
+        <v>106654</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2180</v>
+        <v>221849</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3473,10 +3478,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>723341</v>
+        <v>723324</v>
       </c>
       <c r="R29" t="n">
-        <v>6413230</v>
+        <v>6412899</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3539,10 +3544,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126075095</v>
+        <v>126075330</v>
       </c>
       <c r="B30" t="n">
-        <v>98389</v>
+        <v>95964</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3550,39 +3555,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>219864</v>
+        <v>2180</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Hemhagen, Nors, Gtl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>723328</v>
+        <v>723341</v>
       </c>
       <c r="R30" t="n">
-        <v>6412904</v>
+        <v>6413230</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3645,10 +3645,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126075054</v>
+        <v>126075188</v>
       </c>
       <c r="B31" t="n">
-        <v>109185</v>
+        <v>103815</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3656,23 +3656,19 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220299</v>
+        <v>224416</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Ljus solvända</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3680,10 +3676,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>723389</v>
+        <v>723322</v>
       </c>
       <c r="R31" t="n">
-        <v>6413195</v>
+        <v>6412738</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3746,7 +3742,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126075188</v>
+        <v>126075189</v>
       </c>
       <c r="B32" t="n">
         <v>103815</v>
@@ -3777,10 +3773,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>723322</v>
+        <v>723328</v>
       </c>
       <c r="R32" t="n">
-        <v>6412738</v>
+        <v>6412741</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3843,7 +3839,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126075189</v>
+        <v>126075185</v>
       </c>
       <c r="B33" t="n">
         <v>103815</v>
@@ -3874,10 +3870,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>723328</v>
+        <v>723250</v>
       </c>
       <c r="R33" t="n">
-        <v>6412741</v>
+        <v>6413023</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3940,10 +3936,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126075185</v>
+        <v>126075054</v>
       </c>
       <c r="B34" t="n">
-        <v>103815</v>
+        <v>109185</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3951,19 +3947,23 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>224416</v>
+        <v>220299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ljus solvända</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. nummularium</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr"/>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -3971,10 +3971,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>723250</v>
+        <v>723389</v>
       </c>
       <c r="R34" t="n">
-        <v>6413023</v>
+        <v>6413195</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4239,10 +4239,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126075165</v>
+        <v>126075421</v>
       </c>
       <c r="B37" t="n">
-        <v>19793</v>
+        <v>106200</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4250,16 +4250,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>241122</v>
+        <v>221903</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Axveronika</t>
+        </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Orellia scorzonerae</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Robineau-Desvoidy, 1830)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4269,10 +4274,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>723375</v>
+        <v>723321</v>
       </c>
       <c r="R37" t="n">
-        <v>6413131</v>
+        <v>6412897</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4307,11 +4312,6 @@
           <t>2024-05-16</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>På knoppar av värdväxten svinrot.</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -4320,21 +4320,6 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>svinrot</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Scorzonera humilis</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Scorzonera humilis</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -4355,10 +4340,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126075421</v>
+        <v>126075165</v>
       </c>
       <c r="B38" t="n">
-        <v>106200</v>
+        <v>19793</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4366,21 +4351,16 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221903</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Axveronika</t>
-        </is>
+        <v>241122</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Orellia scorzonerae</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Robineau-Desvoidy, 1830)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4390,10 +4370,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>723321</v>
+        <v>723375</v>
       </c>
       <c r="R38" t="n">
-        <v>6412897</v>
+        <v>6413131</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4428,6 +4408,11 @@
           <t>2024-05-16</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>På knoppar av värdväxten svinrot.</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -4436,6 +4421,21 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>svinrot</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -4860,10 +4860,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126075269</v>
+        <v>126075044</v>
       </c>
       <c r="B43" t="n">
-        <v>107243</v>
+        <v>109185</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4871,21 +4871,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220079</v>
+        <v>220299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4895,10 +4895,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>723282</v>
+        <v>723367</v>
       </c>
       <c r="R43" t="n">
-        <v>6413048</v>
+        <v>6413134</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4961,10 +4961,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126075044</v>
+        <v>126075269</v>
       </c>
       <c r="B44" t="n">
-        <v>109185</v>
+        <v>107243</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4972,21 +4972,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220299</v>
+        <v>220079</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4996,10 +4996,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>723367</v>
+        <v>723282</v>
       </c>
       <c r="R44" t="n">
-        <v>6413134</v>
+        <v>6413048</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5159,10 +5159,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126075412</v>
+        <v>126075045</v>
       </c>
       <c r="B46" t="n">
-        <v>106200</v>
+        <v>109185</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5170,16 +5170,16 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>221903</v>
+        <v>220299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -5194,10 +5194,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>723243</v>
+        <v>723352</v>
       </c>
       <c r="R46" t="n">
-        <v>6413018</v>
+        <v>6413153</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5260,10 +5260,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126075182</v>
+        <v>126075412</v>
       </c>
       <c r="B47" t="n">
-        <v>103815</v>
+        <v>106200</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5271,19 +5271,23 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>224416</v>
+        <v>221903</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ljus solvända</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. nummularium</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr"/>
+          <t>Veronica spicata</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5291,10 +5295,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>723272</v>
+        <v>723243</v>
       </c>
       <c r="R47" t="n">
-        <v>6413033</v>
+        <v>6413018</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5357,10 +5361,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126075045</v>
+        <v>126075182</v>
       </c>
       <c r="B48" t="n">
-        <v>109185</v>
+        <v>103815</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5368,23 +5372,19 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220299</v>
+        <v>224416</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Ljus solvända</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -5392,10 +5392,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>723352</v>
+        <v>723272</v>
       </c>
       <c r="R48" t="n">
-        <v>6413153</v>
+        <v>6413033</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5458,27 +5458,27 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126075047</v>
+        <v>126075096</v>
       </c>
       <c r="B49" t="n">
-        <v>109185</v>
+        <v>98389</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220299</v>
+        <v>219864</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -5487,16 +5487,21 @@
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Hemhagen, Nors, Gtl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>723335</v>
+        <v>723293</v>
       </c>
       <c r="R49" t="n">
-        <v>6413175</v>
+        <v>6412906</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5559,7 +5564,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126075029</v>
+        <v>126075047</v>
       </c>
       <c r="B50" t="n">
         <v>109185</v>
@@ -5594,10 +5599,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>723216</v>
+        <v>723335</v>
       </c>
       <c r="R50" t="n">
-        <v>6412940</v>
+        <v>6413175</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5660,27 +5665,27 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126075096</v>
+        <v>126075029</v>
       </c>
       <c r="B51" t="n">
-        <v>98389</v>
+        <v>109185</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>219864</v>
+        <v>220299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -5689,21 +5694,16 @@
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Hemhagen, Nors, Gtl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>723293</v>
+        <v>723216</v>
       </c>
       <c r="R51" t="n">
-        <v>6412906</v>
+        <v>6412940</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>

--- a/artfynd/A 15629-2024 artfynd.xlsx
+++ b/artfynd/A 15629-2024 artfynd.xlsx
@@ -2436,10 +2436,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126075192</v>
+        <v>126075041</v>
       </c>
       <c r="B19" t="n">
-        <v>103815</v>
+        <v>109185</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2447,19 +2447,23 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>224416</v>
+        <v>220299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ljus solvända</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. nummularium</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2467,10 +2471,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>723305</v>
+        <v>723339</v>
       </c>
       <c r="R19" t="n">
-        <v>6412896</v>
+        <v>6413055</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2533,10 +2537,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126075041</v>
+        <v>126075192</v>
       </c>
       <c r="B20" t="n">
-        <v>109185</v>
+        <v>103815</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2544,23 +2548,19 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220299</v>
+        <v>224416</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Ljus solvända</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2568,10 +2568,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>723339</v>
+        <v>723305</v>
       </c>
       <c r="R20" t="n">
-        <v>6413055</v>
+        <v>6412896</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>

--- a/artfynd/A 15629-2024 artfynd.xlsx
+++ b/artfynd/A 15629-2024 artfynd.xlsx
@@ -2436,10 +2436,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126075041</v>
+        <v>126075192</v>
       </c>
       <c r="B19" t="n">
-        <v>109185</v>
+        <v>103815</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2447,23 +2447,19 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220299</v>
+        <v>224416</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Ljus solvända</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2471,10 +2467,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>723339</v>
+        <v>723305</v>
       </c>
       <c r="R19" t="n">
-        <v>6413055</v>
+        <v>6412896</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2537,10 +2533,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126075192</v>
+        <v>126075041</v>
       </c>
       <c r="B20" t="n">
-        <v>103815</v>
+        <v>109185</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2548,19 +2544,23 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>224416</v>
+        <v>220299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ljus solvända</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. nummularium</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr"/>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2568,10 +2568,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>723305</v>
+        <v>723339</v>
       </c>
       <c r="R20" t="n">
-        <v>6412896</v>
+        <v>6413055</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2735,7 +2735,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126075043</v>
+        <v>126075053</v>
       </c>
       <c r="B22" t="n">
         <v>109185</v>
@@ -2770,10 +2770,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>723368</v>
+        <v>723356</v>
       </c>
       <c r="R22" t="n">
-        <v>6413087</v>
+        <v>6413200</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2836,7 +2836,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126075053</v>
+        <v>126075040</v>
       </c>
       <c r="B23" t="n">
         <v>109185</v>
@@ -2871,10 +2871,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>723356</v>
+        <v>723311</v>
       </c>
       <c r="R23" t="n">
-        <v>6413200</v>
+        <v>6413017</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2937,7 +2937,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126075040</v>
+        <v>126075043</v>
       </c>
       <c r="B24" t="n">
         <v>109185</v>
@@ -2972,10 +2972,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>723311</v>
+        <v>723368</v>
       </c>
       <c r="R24" t="n">
-        <v>6413017</v>
+        <v>6413087</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>

--- a/artfynd/A 15629-2024 artfynd.xlsx
+++ b/artfynd/A 15629-2024 artfynd.xlsx
@@ -892,27 +892,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126075032</v>
+        <v>126075089</v>
       </c>
       <c r="B4" t="n">
-        <v>109185</v>
+        <v>98389</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220299</v>
+        <v>219864</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -921,16 +921,21 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Hemhagen, Nors, Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>723222</v>
+        <v>723237</v>
       </c>
       <c r="R4" t="n">
-        <v>6412868</v>
+        <v>6413005</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,32 +998,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126075055</v>
+        <v>126075167</v>
       </c>
       <c r="B5" t="n">
-        <v>109185</v>
+        <v>98383</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220299</v>
+        <v>219862</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1028,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>723291</v>
+        <v>723327</v>
       </c>
       <c r="R5" t="n">
-        <v>6413160</v>
+        <v>6413202</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1058,12 +1063,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1094,27 +1099,27 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126075089</v>
+        <v>126075032</v>
       </c>
       <c r="B6" t="n">
-        <v>98389</v>
+        <v>109185</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219864</v>
+        <v>220299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1123,21 +1128,16 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hemhagen, Nors, Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>723237</v>
+        <v>723222</v>
       </c>
       <c r="R6" t="n">
-        <v>6413005</v>
+        <v>6412868</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1200,32 +1200,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126075167</v>
+        <v>126075055</v>
       </c>
       <c r="B7" t="n">
-        <v>98383</v>
+        <v>109185</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219862</v>
+        <v>220299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>723327</v>
+        <v>723291</v>
       </c>
       <c r="R7" t="n">
-        <v>6413202</v>
+        <v>6413160</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1265,12 +1265,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -2735,7 +2735,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126075053</v>
+        <v>126075043</v>
       </c>
       <c r="B22" t="n">
         <v>109185</v>
@@ -2770,10 +2770,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>723356</v>
+        <v>723368</v>
       </c>
       <c r="R22" t="n">
-        <v>6413200</v>
+        <v>6413087</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2836,7 +2836,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126075040</v>
+        <v>126075053</v>
       </c>
       <c r="B23" t="n">
         <v>109185</v>
@@ -2871,10 +2871,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>723311</v>
+        <v>723356</v>
       </c>
       <c r="R23" t="n">
-        <v>6413017</v>
+        <v>6413200</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2937,7 +2937,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126075043</v>
+        <v>126075040</v>
       </c>
       <c r="B24" t="n">
         <v>109185</v>
@@ -2972,10 +2972,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>723368</v>
+        <v>723311</v>
       </c>
       <c r="R24" t="n">
-        <v>6413087</v>
+        <v>6413017</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3645,10 +3645,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126075188</v>
+        <v>126075054</v>
       </c>
       <c r="B31" t="n">
-        <v>103815</v>
+        <v>109185</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3656,19 +3656,23 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>224416</v>
+        <v>220299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ljus solvända</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. nummularium</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr"/>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3676,10 +3680,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>723322</v>
+        <v>723389</v>
       </c>
       <c r="R31" t="n">
-        <v>6412738</v>
+        <v>6413195</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3742,7 +3746,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126075189</v>
+        <v>126075188</v>
       </c>
       <c r="B32" t="n">
         <v>103815</v>
@@ -3773,10 +3777,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>723328</v>
+        <v>723322</v>
       </c>
       <c r="R32" t="n">
-        <v>6412741</v>
+        <v>6412738</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3839,7 +3843,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126075185</v>
+        <v>126075189</v>
       </c>
       <c r="B33" t="n">
         <v>103815</v>
@@ -3870,10 +3874,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>723250</v>
+        <v>723328</v>
       </c>
       <c r="R33" t="n">
-        <v>6413023</v>
+        <v>6412741</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3936,10 +3940,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126075054</v>
+        <v>126075185</v>
       </c>
       <c r="B34" t="n">
-        <v>109185</v>
+        <v>103815</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3947,23 +3951,19 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220299</v>
+        <v>224416</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Ljus solvända</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -3971,10 +3971,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>723389</v>
+        <v>723250</v>
       </c>
       <c r="R34" t="n">
-        <v>6413195</v>
+        <v>6413023</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>

--- a/artfynd/A 15629-2024 artfynd.xlsx
+++ b/artfynd/A 15629-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY51"/>
+  <dimension ref="A1:AY101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>114813676</v>
+        <v>126075241</v>
       </c>
       <c r="B2" t="n">
-        <v>42985</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97165</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,48 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>101509</v>
+        <v>588</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Apollofjäril</t>
+          <t>Kalkkoppmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Parnassius apollo</t>
+          <t>Entosthodon muhlenbergii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Turner) Fife</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lärbro, Gtl</t>
+          <t>Hemhagen, Nors, Gtl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>723302</v>
+        <v>723268</v>
       </c>
       <c r="R2" t="n">
-        <v>6412894</v>
+        <v>6413065</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-07-13</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-07-13</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,26 +760,26 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Patrick Gant</t>
+          <t>Frida Nettelbladt</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Dennis Nyström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>Artskyddsutredning vid Lärbro 2021 (JAG0090)</t>
+          <t>FNT0020 Lärbro Nors NVI 2024</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126075195</v>
+        <v>126075242</v>
       </c>
       <c r="B3" t="n">
-        <v>103815</v>
+        <v>97165</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -806,19 +787,23 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>224416</v>
+        <v>588</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ljus solvända</t>
+          <t>Kalkkoppmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. nummularium</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>Entosthodon muhlenbergii</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Turner) Fife</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -826,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>723294</v>
+        <v>723241</v>
       </c>
       <c r="R3" t="n">
-        <v>6412905</v>
+        <v>6413024</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -892,50 +877,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126075089</v>
+        <v>126075243</v>
       </c>
       <c r="B4" t="n">
-        <v>98389</v>
+        <v>97165</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219864</v>
+        <v>588</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Kalkkoppmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Entosthodon muhlenbergii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Turner) Fife</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Hemhagen, Nors, Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>723237</v>
+        <v>723216</v>
       </c>
       <c r="R4" t="n">
-        <v>6413005</v>
+        <v>6413021</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -998,32 +978,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126075167</v>
+        <v>126075244</v>
       </c>
       <c r="B5" t="n">
-        <v>98383</v>
+        <v>97165</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219862</v>
+        <v>588</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Kalkkoppmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Entosthodon muhlenbergii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Turner) Fife</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>723327</v>
+        <v>723304</v>
       </c>
       <c r="R5" t="n">
-        <v>6413202</v>
+        <v>6412711</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126075032</v>
+        <v>126075245</v>
       </c>
       <c r="B6" t="n">
-        <v>109185</v>
+        <v>97165</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1110,21 +1090,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220299</v>
+        <v>588</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Kalkkoppmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Entosthodon muhlenbergii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Turner) Fife</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1134,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>723222</v>
+        <v>723314</v>
       </c>
       <c r="R6" t="n">
-        <v>6412868</v>
+        <v>6412718</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1200,10 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126075055</v>
+        <v>126075247</v>
       </c>
       <c r="B7" t="n">
-        <v>109185</v>
+        <v>97165</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1211,21 +1191,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220299</v>
+        <v>588</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Kalkkoppmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Entosthodon muhlenbergii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Turner) Fife</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>723291</v>
+        <v>723305</v>
       </c>
       <c r="R7" t="n">
-        <v>6413160</v>
+        <v>6412901</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1265,12 +1245,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1301,32 +1281,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126075294</v>
+        <v>126075253</v>
       </c>
       <c r="B8" t="n">
-        <v>105308</v>
+        <v>97165</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221141</v>
+        <v>588</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Kalkkoppmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Entosthodon muhlenbergii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Turner) Fife</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1336,10 +1316,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>723318</v>
+        <v>723351</v>
       </c>
       <c r="R8" t="n">
-        <v>6412902</v>
+        <v>6413257</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1402,50 +1382,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126075088</v>
+        <v>126075254</v>
       </c>
       <c r="B9" t="n">
-        <v>98389</v>
+        <v>97165</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219864</v>
+        <v>588</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Kalkkoppmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Entosthodon muhlenbergii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Turner) Fife</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hemhagen, Nors, Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>723278</v>
+        <v>723335</v>
       </c>
       <c r="R9" t="n">
-        <v>6413037</v>
+        <v>6413242</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1508,10 +1483,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126075038</v>
+        <v>126075255</v>
       </c>
       <c r="B10" t="n">
-        <v>109185</v>
+        <v>97165</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1519,21 +1494,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220299</v>
+        <v>588</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Kalkkoppmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Entosthodon muhlenbergii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Turner) Fife</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1543,10 +1518,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>723299</v>
+        <v>723344</v>
       </c>
       <c r="R10" t="n">
-        <v>6413005</v>
+        <v>6413239</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1609,32 +1584,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126075295</v>
+        <v>126075258</v>
       </c>
       <c r="B11" t="n">
-        <v>105308</v>
+        <v>97165</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221141</v>
+        <v>588</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Kalkkoppmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Entosthodon muhlenbergii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Turner) Fife</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1644,10 +1619,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>723293</v>
+        <v>723289</v>
       </c>
       <c r="R11" t="n">
-        <v>6412916</v>
+        <v>6413084</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1674,12 +1649,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1710,32 +1685,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126075351</v>
+        <v>126075330</v>
       </c>
       <c r="B12" t="n">
-        <v>106654</v>
+        <v>96708</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221849</v>
+        <v>2180</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1745,10 +1720,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>723310</v>
+        <v>723341</v>
       </c>
       <c r="R12" t="n">
-        <v>6412729</v>
+        <v>6413230</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1811,10 +1786,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126075247</v>
+        <v>126075228</v>
       </c>
       <c r="B13" t="n">
-        <v>96421</v>
+        <v>75428</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1822,21 +1797,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>588</v>
+        <v>6426</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kalkkoppmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Entosthodon muhlenbergii</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Turner) Fife</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1846,10 +1821,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>723305</v>
+        <v>723347</v>
       </c>
       <c r="R13" t="n">
-        <v>6412901</v>
+        <v>6413067</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1912,32 +1887,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126075046</v>
+        <v>126075071</v>
       </c>
       <c r="B14" t="n">
-        <v>109185</v>
+        <v>57950</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220299</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1947,10 +1922,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>723345</v>
+        <v>723236</v>
       </c>
       <c r="R14" t="n">
-        <v>6413172</v>
+        <v>6412858</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2013,45 +1988,59 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126075422</v>
+        <v>126075072</v>
       </c>
       <c r="B15" t="n">
-        <v>106200</v>
+        <v>57950</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221903</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Hemhagen, Nors, Gtl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>723297</v>
+        <v>723335</v>
       </c>
       <c r="R15" t="n">
-        <v>6412905</v>
+        <v>6413183</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2084,6 +2073,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Lockläte i lämplig biotop, senvuxna tallar med spår av spår av spillkråka, enstaka äldre potentiella boträd i skogen.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2114,45 +2108,64 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126075228</v>
+        <v>114813484</v>
       </c>
       <c r="B16" t="n">
-        <v>75014</v>
+        <v>43518</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6426</v>
+        <v>101509</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Apollofjäril</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Parnassius apollo</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Hemhagen, Nors, Gtl</t>
+          <t>Lärbro, Gtl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>723347</v>
+        <v>723272</v>
       </c>
       <c r="R16" t="n">
-        <v>6413067</v>
+        <v>6412720</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2179,12 +2192,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2021-07-15</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2021-07-15</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2199,26 +2212,26 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Frida Nettelbladt</t>
+          <t>Patrick Gant</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Dennis Nyström</t>
+          <t>Oskar Kindvall</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>FNT0020 Lärbro Nors NVI 2024</t>
+          <t>Artskyddsutredning vid Lärbro 2021 (JAG0090)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126075072</v>
+        <v>114813676</v>
       </c>
       <c r="B17" t="n">
-        <v>57654</v>
+        <v>43518</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2226,16 +2239,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>101509</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Apollofjäril</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Parnassius apollo</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2248,26 +2261,26 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Hemhagen, Nors, Gtl</t>
+          <t>Lärbro, Gtl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>723335</v>
+        <v>723302</v>
       </c>
       <c r="R17" t="n">
-        <v>6413183</v>
+        <v>6412894</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2294,17 +2307,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2021-07-13</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Lockläte i lämplig biotop, senvuxna tallar med spår av spår av spillkråka, enstaka äldre potentiella boträd i skogen.</t>
+          <t>2021-07-13</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2319,26 +2327,26 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Frida Nettelbladt</t>
+          <t>Patrick Gant</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Dennis Nyström</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>FNT0020 Lärbro Nors NVI 2024</t>
+          <t>Artskyddsutredning vid Lärbro 2021 (JAG0090)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126075420</v>
+        <v>114814801</v>
       </c>
       <c r="B18" t="n">
-        <v>106200</v>
+        <v>43518</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2346,34 +2354,48 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221903</v>
+        <v>101509</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Apollofjäril</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Parnassius apollo</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Hemhagen, Nors, Gtl</t>
+          <t>Lärbro, Gtl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>723302</v>
+        <v>723385</v>
       </c>
       <c r="R18" t="n">
-        <v>6412899</v>
+        <v>6412926</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2400,12 +2422,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2021-06-29</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2021-06-29</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2420,26 +2442,26 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Frida Nettelbladt</t>
+          <t>Patrick Gant</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Dennis Nyström</t>
+          <t>Bafraw Karimi</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>FNT0020 Lärbro Nors NVI 2024</t>
+          <t>Artskyddsutredning vid Lärbro 2021 (JAG0090)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126075192</v>
+        <v>114814802</v>
       </c>
       <c r="B19" t="n">
-        <v>103815</v>
+        <v>43518</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2447,30 +2469,48 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>224416</v>
+        <v>101509</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ljus solvända</t>
+          <t>Apollofjäril</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. nummularium</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
+          <t>Parnassius apollo</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Hemhagen, Nors, Gtl</t>
+          <t>Lärbro, Gtl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>723305</v>
+        <v>723399</v>
       </c>
       <c r="R19" t="n">
-        <v>6412896</v>
+        <v>6412912</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2497,12 +2537,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2021-06-29</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2021-06-29</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2517,26 +2557,26 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Frida Nettelbladt</t>
+          <t>Patrick Gant</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Dennis Nyström</t>
+          <t>Bafraw Karimi</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>FNT0020 Lärbro Nors NVI 2024</t>
+          <t>Artskyddsutredning vid Lärbro 2021 (JAG0090)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126075041</v>
+        <v>126075452</v>
       </c>
       <c r="B20" t="n">
-        <v>109185</v>
+        <v>43518</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2544,21 +2584,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220299</v>
+        <v>101509</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Apollofjäril</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Parnassius apollo</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2568,10 +2608,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>723339</v>
+        <v>723238</v>
       </c>
       <c r="R20" t="n">
-        <v>6413055</v>
+        <v>6413030</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2634,10 +2674,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126075050</v>
+        <v>126075455</v>
       </c>
       <c r="B21" t="n">
-        <v>109185</v>
+        <v>43518</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2645,21 +2685,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220299</v>
+        <v>101509</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Apollofjäril</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Parnassius apollo</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2669,10 +2709,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>723315</v>
+        <v>723342</v>
       </c>
       <c r="R21" t="n">
-        <v>6413206</v>
+        <v>6413255</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2735,32 +2775,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126075043</v>
+        <v>126075073</v>
       </c>
       <c r="B22" t="n">
-        <v>109185</v>
+        <v>40516</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220299</v>
+        <v>102406</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Solvändesäckmal</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Coleophora ochrea</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Haworth, 1828)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2770,10 +2810,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>723368</v>
+        <v>723245</v>
       </c>
       <c r="R22" t="n">
-        <v>6413087</v>
+        <v>6413024</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2836,32 +2876,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126075053</v>
+        <v>126075074</v>
       </c>
       <c r="B23" t="n">
-        <v>109185</v>
+        <v>40516</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220299</v>
+        <v>102406</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Solvändesäckmal</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Coleophora ochrea</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Haworth, 1828)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2871,10 +2911,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>723356</v>
+        <v>723267</v>
       </c>
       <c r="R23" t="n">
-        <v>6413200</v>
+        <v>6412737</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2937,32 +2977,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126075040</v>
+        <v>126075167</v>
       </c>
       <c r="B24" t="n">
-        <v>109185</v>
+        <v>99141</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220299</v>
+        <v>219862</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2972,10 +3012,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>723311</v>
+        <v>723327</v>
       </c>
       <c r="R24" t="n">
-        <v>6413017</v>
+        <v>6413202</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3038,41 +3078,50 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126075193</v>
+        <v>126075088</v>
       </c>
       <c r="B25" t="n">
-        <v>103815</v>
+        <v>99147</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>224416</v>
+        <v>219864</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ljus solvända</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. nummularium</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr"/>
+          <t>Orchis mascula</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Hemhagen, Nors, Gtl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>723321</v>
+        <v>723278</v>
       </c>
       <c r="R25" t="n">
-        <v>6412898</v>
+        <v>6413037</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3135,27 +3184,27 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126075052</v>
+        <v>126075089</v>
       </c>
       <c r="B26" t="n">
-        <v>109185</v>
+        <v>99147</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220299</v>
+        <v>219864</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3164,16 +3213,21 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Hemhagen, Nors, Gtl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>723338</v>
+        <v>723237</v>
       </c>
       <c r="R26" t="n">
-        <v>6413224</v>
+        <v>6413005</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3236,27 +3290,27 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126075049</v>
+        <v>126075094</v>
       </c>
       <c r="B27" t="n">
-        <v>109185</v>
+        <v>99147</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220299</v>
+        <v>219864</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3265,16 +3319,21 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Hemhagen, Nors, Gtl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>723331</v>
+        <v>723322</v>
       </c>
       <c r="R27" t="n">
-        <v>6413195</v>
+        <v>6412725</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3340,7 +3399,7 @@
         <v>126075095</v>
       </c>
       <c r="B28" t="n">
-        <v>98389</v>
+        <v>99147</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3443,27 +3502,27 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126075357</v>
+        <v>126075096</v>
       </c>
       <c r="B29" t="n">
-        <v>106654</v>
+        <v>99147</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221849</v>
+        <v>219864</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3472,16 +3531,21 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Hemhagen, Nors, Gtl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>723324</v>
+        <v>723293</v>
       </c>
       <c r="R29" t="n">
-        <v>6412899</v>
+        <v>6412906</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3544,10 +3608,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126075330</v>
+        <v>126075099</v>
       </c>
       <c r="B30" t="n">
-        <v>95964</v>
+        <v>99147</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3555,34 +3619,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2180</v>
+        <v>219864</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Hemhagen, Nors, Gtl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>723341</v>
+        <v>723427</v>
       </c>
       <c r="R30" t="n">
-        <v>6413230</v>
+        <v>6413250</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3645,27 +3714,27 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126075054</v>
+        <v>126075103</v>
       </c>
       <c r="B31" t="n">
-        <v>109185</v>
+        <v>99147</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220299</v>
+        <v>219864</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3674,16 +3743,21 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Hemhagen, Nors, Gtl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>723389</v>
+        <v>723322</v>
       </c>
       <c r="R31" t="n">
-        <v>6413195</v>
+        <v>6413117</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3710,12 +3784,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3746,41 +3820,50 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126075188</v>
+        <v>126075105</v>
       </c>
       <c r="B32" t="n">
-        <v>103815</v>
+        <v>99147</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>224416</v>
+        <v>219864</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ljus solvända</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. nummularium</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr"/>
+          <t>Orchis mascula</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Hemhagen, Nors, Gtl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>723322</v>
+        <v>723325</v>
       </c>
       <c r="R32" t="n">
-        <v>6412738</v>
+        <v>6413232</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3807,12 +3890,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3843,10 +3926,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126075189</v>
+        <v>126075269</v>
       </c>
       <c r="B33" t="n">
-        <v>103815</v>
+        <v>108116</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3854,19 +3937,23 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>224416</v>
+        <v>220079</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ljus solvända</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. nummularium</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr"/>
+          <t>Cirsium acaule</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -3874,10 +3961,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>723328</v>
+        <v>723282</v>
       </c>
       <c r="R33" t="n">
-        <v>6412741</v>
+        <v>6413048</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3940,10 +4027,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126075185</v>
+        <v>126075028</v>
       </c>
       <c r="B34" t="n">
-        <v>103815</v>
+        <v>110078</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3951,19 +4038,23 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>224416</v>
+        <v>220299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ljus solvända</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. nummularium</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr"/>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -3971,10 +4062,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>723250</v>
+        <v>723208</v>
       </c>
       <c r="R34" t="n">
-        <v>6413023</v>
+        <v>6412969</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4037,10 +4128,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126075031</v>
+        <v>126075029</v>
       </c>
       <c r="B35" t="n">
-        <v>109185</v>
+        <v>110078</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4075,7 +4166,7 @@
         <v>723216</v>
       </c>
       <c r="R35" t="n">
-        <v>6412876</v>
+        <v>6412940</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4138,32 +4229,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126075328</v>
+        <v>126075030</v>
       </c>
       <c r="B36" t="n">
-        <v>100543</v>
+        <v>110078</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>222498</v>
+        <v>220299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4173,10 +4264,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>723335</v>
+        <v>723211</v>
       </c>
       <c r="R36" t="n">
-        <v>6413175</v>
+        <v>6412911</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4239,10 +4330,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126075421</v>
+        <v>126075031</v>
       </c>
       <c r="B37" t="n">
-        <v>106200</v>
+        <v>110078</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4250,16 +4341,16 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221903</v>
+        <v>220299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -4274,10 +4365,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>723321</v>
+        <v>723216</v>
       </c>
       <c r="R37" t="n">
-        <v>6412897</v>
+        <v>6412876</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4340,10 +4431,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126075165</v>
+        <v>126075032</v>
       </c>
       <c r="B38" t="n">
-        <v>19793</v>
+        <v>110078</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4351,16 +4442,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>241122</v>
+        <v>220299</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Orellia scorzonerae</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Robineau-Desvoidy, 1830)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4370,10 +4466,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>723375</v>
+        <v>723222</v>
       </c>
       <c r="R38" t="n">
-        <v>6413131</v>
+        <v>6412868</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4408,11 +4504,6 @@
           <t>2024-05-16</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>På knoppar av värdväxten svinrot.</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -4421,21 +4512,6 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>svinrot</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Scorzonera humilis</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Scorzonera humilis</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -4456,10 +4532,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126075028</v>
+        <v>126075037</v>
       </c>
       <c r="B39" t="n">
-        <v>109185</v>
+        <v>110078</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4491,10 +4567,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>723208</v>
+        <v>723279</v>
       </c>
       <c r="R39" t="n">
-        <v>6412969</v>
+        <v>6412857</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4557,10 +4633,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126075039</v>
+        <v>126075038</v>
       </c>
       <c r="B40" t="n">
-        <v>109185</v>
+        <v>110078</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4592,10 +4668,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>723331</v>
+        <v>723299</v>
       </c>
       <c r="R40" t="n">
-        <v>6413009</v>
+        <v>6413005</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4658,10 +4734,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126075042</v>
+        <v>126075039</v>
       </c>
       <c r="B41" t="n">
-        <v>109185</v>
+        <v>110078</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4693,10 +4769,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>723354</v>
+        <v>723331</v>
       </c>
       <c r="R41" t="n">
-        <v>6413071</v>
+        <v>6413009</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4759,10 +4835,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126075030</v>
+        <v>126075040</v>
       </c>
       <c r="B42" t="n">
-        <v>109185</v>
+        <v>110078</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4794,10 +4870,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>723211</v>
+        <v>723311</v>
       </c>
       <c r="R42" t="n">
-        <v>6412911</v>
+        <v>6413017</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4860,10 +4936,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126075044</v>
+        <v>126075041</v>
       </c>
       <c r="B43" t="n">
-        <v>109185</v>
+        <v>110078</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4895,10 +4971,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>723367</v>
+        <v>723339</v>
       </c>
       <c r="R43" t="n">
-        <v>6413134</v>
+        <v>6413055</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4961,10 +5037,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126075184</v>
+        <v>126075042</v>
       </c>
       <c r="B44" t="n">
-        <v>103815</v>
+        <v>110078</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4972,19 +5048,23 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>224416</v>
+        <v>220299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ljus solvända</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. nummularium</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr"/>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -4992,10 +5072,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>723240</v>
+        <v>723354</v>
       </c>
       <c r="R44" t="n">
-        <v>6413005</v>
+        <v>6413071</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5058,10 +5138,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126075269</v>
+        <v>126075043</v>
       </c>
       <c r="B45" t="n">
-        <v>107243</v>
+        <v>110078</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5069,21 +5149,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220079</v>
+        <v>220299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5093,10 +5173,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>723282</v>
+        <v>723368</v>
       </c>
       <c r="R45" t="n">
-        <v>6413048</v>
+        <v>6413087</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5159,10 +5239,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126075045</v>
+        <v>126075044</v>
       </c>
       <c r="B46" t="n">
-        <v>109185</v>
+        <v>110078</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5194,10 +5274,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>723352</v>
+        <v>723367</v>
       </c>
       <c r="R46" t="n">
-        <v>6413153</v>
+        <v>6413134</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5260,10 +5340,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126075412</v>
+        <v>126075045</v>
       </c>
       <c r="B47" t="n">
-        <v>106200</v>
+        <v>110078</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5271,16 +5351,16 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221903</v>
+        <v>220299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -5295,10 +5375,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>723243</v>
+        <v>723352</v>
       </c>
       <c r="R47" t="n">
-        <v>6413018</v>
+        <v>6413153</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5361,10 +5441,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126075182</v>
+        <v>126075046</v>
       </c>
       <c r="B48" t="n">
-        <v>103815</v>
+        <v>110078</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5372,19 +5452,23 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>224416</v>
+        <v>220299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ljus solvända</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. nummularium</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr"/>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -5392,10 +5476,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>723272</v>
+        <v>723345</v>
       </c>
       <c r="R48" t="n">
-        <v>6413033</v>
+        <v>6413172</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5461,7 +5545,7 @@
         <v>126075047</v>
       </c>
       <c r="B49" t="n">
-        <v>109185</v>
+        <v>110078</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5559,10 +5643,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126075029</v>
+        <v>126075049</v>
       </c>
       <c r="B50" t="n">
-        <v>109185</v>
+        <v>110078</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5594,10 +5678,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>723216</v>
+        <v>723331</v>
       </c>
       <c r="R50" t="n">
-        <v>6412940</v>
+        <v>6413195</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5660,27 +5744,27 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126075096</v>
+        <v>126075050</v>
       </c>
       <c r="B51" t="n">
-        <v>98389</v>
+        <v>110078</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>219864</v>
+        <v>220299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -5689,21 +5773,16 @@
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Hemhagen, Nors, Gtl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>723293</v>
+        <v>723315</v>
       </c>
       <c r="R51" t="n">
-        <v>6412906</v>
+        <v>6413206</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5759,6 +5838,5019 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr">
+        <is>
+          <t>FNT0020 Lärbro Nors NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>126075051</v>
+      </c>
+      <c r="B52" t="n">
+        <v>110078</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Hemhagen, Nors, Gtl</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>723310</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6413217</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Lärbro</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr">
+        <is>
+          <t>FNT0020 Lärbro Nors NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>126075052</v>
+      </c>
+      <c r="B53" t="n">
+        <v>110078</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Hemhagen, Nors, Gtl</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>723338</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6413224</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Lärbro</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr">
+        <is>
+          <t>FNT0020 Lärbro Nors NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>126075053</v>
+      </c>
+      <c r="B54" t="n">
+        <v>110078</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Hemhagen, Nors, Gtl</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>723356</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6413200</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Lärbro</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr">
+        <is>
+          <t>FNT0020 Lärbro Nors NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>126075054</v>
+      </c>
+      <c r="B55" t="n">
+        <v>110078</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Hemhagen, Nors, Gtl</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>723389</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6413195</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Lärbro</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr">
+        <is>
+          <t>FNT0020 Lärbro Nors NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>126075055</v>
+      </c>
+      <c r="B56" t="n">
+        <v>110078</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Hemhagen, Nors, Gtl</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>723291</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6413160</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Lärbro</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2024-05-15</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2024-05-15</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr">
+        <is>
+          <t>FNT0020 Lärbro Nors NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>126075294</v>
+      </c>
+      <c r="B57" t="n">
+        <v>106156</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Hemhagen, Nors, Gtl</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>723318</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6412902</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Lärbro</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr">
+        <is>
+          <t>FNT0020 Lärbro Nors NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>126075295</v>
+      </c>
+      <c r="B58" t="n">
+        <v>106156</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Hemhagen, Nors, Gtl</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>723293</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6412916</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Lärbro</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr">
+        <is>
+          <t>FNT0020 Lärbro Nors NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>126075344</v>
+      </c>
+      <c r="B59" t="n">
+        <v>107517</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Hemhagen, Nors, Gtl</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>723213</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6413017</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Lärbro</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr">
+        <is>
+          <t>FNT0020 Lärbro Nors NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>126075350</v>
+      </c>
+      <c r="B60" t="n">
+        <v>107517</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Hemhagen, Nors, Gtl</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>723288</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6412710</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Lärbro</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr">
+        <is>
+          <t>FNT0020 Lärbro Nors NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>126075351</v>
+      </c>
+      <c r="B61" t="n">
+        <v>107517</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Hemhagen, Nors, Gtl</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>723310</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6412729</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Lärbro</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr">
+        <is>
+          <t>FNT0020 Lärbro Nors NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>126075352</v>
+      </c>
+      <c r="B62" t="n">
+        <v>107517</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Hemhagen, Nors, Gtl</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>723318</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6412725</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Lärbro</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr">
+        <is>
+          <t>FNT0020 Lärbro Nors NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>126075353</v>
+      </c>
+      <c r="B63" t="n">
+        <v>107517</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Hemhagen, Nors, Gtl</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>723312</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6412713</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Lärbro</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr">
+        <is>
+          <t>FNT0020 Lärbro Nors NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>126075354</v>
+      </c>
+      <c r="B64" t="n">
+        <v>107517</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Hemhagen, Nors, Gtl</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>723278</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6412706</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Lärbro</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr">
+        <is>
+          <t>FNT0020 Lärbro Nors NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>126075355</v>
+      </c>
+      <c r="B65" t="n">
+        <v>107517</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Hemhagen, Nors, Gtl</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>723270</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6412709</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Lärbro</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr">
+        <is>
+          <t>FNT0020 Lärbro Nors NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>126075357</v>
+      </c>
+      <c r="B66" t="n">
+        <v>107517</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Hemhagen, Nors, Gtl</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>723324</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6412899</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Lärbro</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr">
+        <is>
+          <t>FNT0020 Lärbro Nors NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>126075369</v>
+      </c>
+      <c r="B67" t="n">
+        <v>107517</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Hemhagen, Nors, Gtl</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>723424</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6413262</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Lärbro</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr">
+        <is>
+          <t>FNT0020 Lärbro Nors NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>126075370</v>
+      </c>
+      <c r="B68" t="n">
+        <v>107517</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Hemhagen, Nors, Gtl</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>723421</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6413277</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Lärbro</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr">
+        <is>
+          <t>FNT0020 Lärbro Nors NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>126075378</v>
+      </c>
+      <c r="B69" t="n">
+        <v>107517</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Hemhagen, Nors, Gtl</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>723262</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6413194</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Lärbro</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2024-05-15</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2024-05-15</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr">
+        <is>
+          <t>FNT0020 Lärbro Nors NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>126075379</v>
+      </c>
+      <c r="B70" t="n">
+        <v>107517</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Hemhagen, Nors, Gtl</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>723324</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6413112</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Lärbro</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2024-05-15</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2024-05-15</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr">
+        <is>
+          <t>FNT0020 Lärbro Nors NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>126075380</v>
+      </c>
+      <c r="B71" t="n">
+        <v>107517</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Hemhagen, Nors, Gtl</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>723304</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6413098</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Lärbro</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2024-05-15</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2024-05-15</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr">
+        <is>
+          <t>FNT0020 Lärbro Nors NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>126075410</v>
+      </c>
+      <c r="B72" t="n">
+        <v>107061</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>221903</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Axveronika</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Veronica spicata</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Hemhagen, Nors, Gtl</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>723265</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6413065</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Lärbro</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr">
+        <is>
+          <t>FNT0020 Lärbro Nors NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>126075412</v>
+      </c>
+      <c r="B73" t="n">
+        <v>107061</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>221903</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Axveronika</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Veronica spicata</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Hemhagen, Nors, Gtl</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>723243</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6413018</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Lärbro</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr">
+        <is>
+          <t>FNT0020 Lärbro Nors NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>126075413</v>
+      </c>
+      <c r="B74" t="n">
+        <v>107061</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>221903</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Axveronika</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Veronica spicata</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Hemhagen, Nors, Gtl</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>723215</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6413024</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Lärbro</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr">
+        <is>
+          <t>FNT0020 Lärbro Nors NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>126075416</v>
+      </c>
+      <c r="B75" t="n">
+        <v>107061</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>221903</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Axveronika</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Veronica spicata</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Hemhagen, Nors, Gtl</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>723296</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6412723</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Lärbro</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr">
+        <is>
+          <t>FNT0020 Lärbro Nors NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>126075417</v>
+      </c>
+      <c r="B76" t="n">
+        <v>107061</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>221903</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Axveronika</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Veronica spicata</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Hemhagen, Nors, Gtl</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>723315</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6412731</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Lärbro</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr">
+        <is>
+          <t>FNT0020 Lärbro Nors NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>126075419</v>
+      </c>
+      <c r="B77" t="n">
+        <v>107061</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>221903</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Axveronika</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Veronica spicata</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Hemhagen, Nors, Gtl</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>723266</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6412738</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Lärbro</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr">
+        <is>
+          <t>FNT0020 Lärbro Nors NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>126075420</v>
+      </c>
+      <c r="B78" t="n">
+        <v>107061</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>221903</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Axveronika</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Veronica spicata</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Hemhagen, Nors, Gtl</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>723302</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6412899</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Lärbro</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr">
+        <is>
+          <t>FNT0020 Lärbro Nors NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>126075421</v>
+      </c>
+      <c r="B79" t="n">
+        <v>107061</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>221903</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Axveronika</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Veronica spicata</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Hemhagen, Nors, Gtl</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>723321</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6412897</v>
+      </c>
+      <c r="S79" t="n">
+        <v>10</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Lärbro</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr">
+        <is>
+          <t>FNT0020 Lärbro Nors NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>126075422</v>
+      </c>
+      <c r="B80" t="n">
+        <v>107061</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>221903</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Axveronika</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Veronica spicata</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Hemhagen, Nors, Gtl</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>723297</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6412905</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Lärbro</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr">
+        <is>
+          <t>FNT0020 Lärbro Nors NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>126075427</v>
+      </c>
+      <c r="B81" t="n">
+        <v>107061</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>221903</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Axveronika</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Veronica spicata</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Hemhagen, Nors, Gtl</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>723356</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6413265</v>
+      </c>
+      <c r="S81" t="n">
+        <v>10</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Lärbro</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr">
+        <is>
+          <t>FNT0020 Lärbro Nors NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>126075431</v>
+      </c>
+      <c r="B82" t="n">
+        <v>107061</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>221903</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Axveronika</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Veronica spicata</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Hemhagen, Nors, Gtl</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>723290</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6413083</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Lärbro</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2024-05-15</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2024-05-15</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr">
+        <is>
+          <t>FNT0020 Lärbro Nors NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>126075432</v>
+      </c>
+      <c r="B83" t="n">
+        <v>107061</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>221903</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Axveronika</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Veronica spicata</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Hemhagen, Nors, Gtl</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>723305</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6413092</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Lärbro</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2024-05-15</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2024-05-15</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr">
+        <is>
+          <t>FNT0020 Lärbro Nors NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>126075328</v>
+      </c>
+      <c r="B84" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Hemhagen, Nors, Gtl</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>723335</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6413175</v>
+      </c>
+      <c r="S84" t="n">
+        <v>10</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Lärbro</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr">
+        <is>
+          <t>FNT0020 Lärbro Nors NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>126075329</v>
+      </c>
+      <c r="B85" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Hemhagen, Nors, Gtl</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>723425</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6413264</v>
+      </c>
+      <c r="S85" t="n">
+        <v>10</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Lärbro</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr">
+        <is>
+          <t>FNT0020 Lärbro Nors NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>126075276</v>
+      </c>
+      <c r="B86" t="n">
+        <v>108205</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>223700</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Hällklofibbla</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Crepis tectorum var. glabrescens</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Neuman</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Hemhagen, Nors, Gtl</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>723336</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6413243</v>
+      </c>
+      <c r="S86" t="n">
+        <v>10</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Lärbro</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr">
+        <is>
+          <t>FNT0020 Lärbro Nors NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>126075182</v>
+      </c>
+      <c r="B87" t="n">
+        <v>104641</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>224416</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Ljus solvända</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Hemhagen, Nors, Gtl</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>723272</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6413033</v>
+      </c>
+      <c r="S87" t="n">
+        <v>10</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Lärbro</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr">
+        <is>
+          <t>FNT0020 Lärbro Nors NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>126075183</v>
+      </c>
+      <c r="B88" t="n">
+        <v>104641</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>224416</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Ljus solvända</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Hemhagen, Nors, Gtl</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>723236</v>
+      </c>
+      <c r="R88" t="n">
+        <v>6413020</v>
+      </c>
+      <c r="S88" t="n">
+        <v>10</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Lärbro</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr">
+        <is>
+          <t>FNT0020 Lärbro Nors NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>126075184</v>
+      </c>
+      <c r="B89" t="n">
+        <v>104641</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>224416</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Ljus solvända</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Hemhagen, Nors, Gtl</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>723240</v>
+      </c>
+      <c r="R89" t="n">
+        <v>6413005</v>
+      </c>
+      <c r="S89" t="n">
+        <v>10</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Lärbro</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr">
+        <is>
+          <t>FNT0020 Lärbro Nors NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>126075185</v>
+      </c>
+      <c r="B90" t="n">
+        <v>104641</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>224416</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Ljus solvända</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Hemhagen, Nors, Gtl</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>723250</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6413023</v>
+      </c>
+      <c r="S90" t="n">
+        <v>10</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Lärbro</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr">
+        <is>
+          <t>FNT0020 Lärbro Nors NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>126075186</v>
+      </c>
+      <c r="B91" t="n">
+        <v>104641</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>224416</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Ljus solvända</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Hemhagen, Nors, Gtl</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>723211</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6413013</v>
+      </c>
+      <c r="S91" t="n">
+        <v>10</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Lärbro</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr">
+        <is>
+          <t>FNT0020 Lärbro Nors NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>126075188</v>
+      </c>
+      <c r="B92" t="n">
+        <v>104641</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>224416</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Ljus solvända</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Hemhagen, Nors, Gtl</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>723322</v>
+      </c>
+      <c r="R92" t="n">
+        <v>6412738</v>
+      </c>
+      <c r="S92" t="n">
+        <v>10</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Lärbro</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr">
+        <is>
+          <t>FNT0020 Lärbro Nors NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>126075189</v>
+      </c>
+      <c r="B93" t="n">
+        <v>104641</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>224416</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Ljus solvända</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Hemhagen, Nors, Gtl</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>723328</v>
+      </c>
+      <c r="R93" t="n">
+        <v>6412741</v>
+      </c>
+      <c r="S93" t="n">
+        <v>10</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Lärbro</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr">
+        <is>
+          <t>FNT0020 Lärbro Nors NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>126075190</v>
+      </c>
+      <c r="B94" t="n">
+        <v>104641</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>224416</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Ljus solvända</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Hemhagen, Nors, Gtl</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>723319</v>
+      </c>
+      <c r="R94" t="n">
+        <v>6412723</v>
+      </c>
+      <c r="S94" t="n">
+        <v>10</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Lärbro</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr">
+        <is>
+          <t>FNT0020 Lärbro Nors NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>126075191</v>
+      </c>
+      <c r="B95" t="n">
+        <v>104641</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>224416</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Ljus solvända</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Hemhagen, Nors, Gtl</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>723269</v>
+      </c>
+      <c r="R95" t="n">
+        <v>6412739</v>
+      </c>
+      <c r="S95" t="n">
+        <v>10</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Lärbro</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr">
+        <is>
+          <t>FNT0020 Lärbro Nors NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>126075192</v>
+      </c>
+      <c r="B96" t="n">
+        <v>104641</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>224416</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Ljus solvända</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Hemhagen, Nors, Gtl</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>723305</v>
+      </c>
+      <c r="R96" t="n">
+        <v>6412896</v>
+      </c>
+      <c r="S96" t="n">
+        <v>10</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Lärbro</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr">
+        <is>
+          <t>FNT0020 Lärbro Nors NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>126075193</v>
+      </c>
+      <c r="B97" t="n">
+        <v>104641</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>224416</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Ljus solvända</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr"/>
+      <c r="I97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Hemhagen, Nors, Gtl</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>723321</v>
+      </c>
+      <c r="R97" t="n">
+        <v>6412898</v>
+      </c>
+      <c r="S97" t="n">
+        <v>10</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Lärbro</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr">
+        <is>
+          <t>FNT0020 Lärbro Nors NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>126075195</v>
+      </c>
+      <c r="B98" t="n">
+        <v>104641</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>224416</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Ljus solvända</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Hemhagen, Nors, Gtl</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>723294</v>
+      </c>
+      <c r="R98" t="n">
+        <v>6412905</v>
+      </c>
+      <c r="S98" t="n">
+        <v>10</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Lärbro</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr">
+        <is>
+          <t>FNT0020 Lärbro Nors NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>126075200</v>
+      </c>
+      <c r="B99" t="n">
+        <v>104641</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>224416</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Ljus solvända</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Hemhagen, Nors, Gtl</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>723346</v>
+      </c>
+      <c r="R99" t="n">
+        <v>6413244</v>
+      </c>
+      <c r="S99" t="n">
+        <v>10</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Lärbro</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr">
+        <is>
+          <t>FNT0020 Lärbro Nors NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>126075271</v>
+      </c>
+      <c r="B100" t="n">
+        <v>67930</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>232915</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Jordhår</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Nostoc flagelliforme</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Harvey ex Molinari-Novoa, Calvo-Pérez &amp; Guiry</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Hemhagen, Nors, Gtl</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>723332</v>
+      </c>
+      <c r="R100" t="n">
+        <v>6413254</v>
+      </c>
+      <c r="S100" t="n">
+        <v>10</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Lärbro</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>2024-05-15</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>2024-05-15</t>
+        </is>
+      </c>
+      <c r="AD100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr">
+        <is>
+          <t>FNT0020 Lärbro Nors NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>126075165</v>
+      </c>
+      <c r="B101" t="n">
+        <v>19917</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>241122</v>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Orellia scorzonerae</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>(Robineau-Desvoidy, 1830)</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Hemhagen, Nors, Gtl</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>723375</v>
+      </c>
+      <c r="R101" t="n">
+        <v>6413131</v>
+      </c>
+      <c r="S101" t="n">
+        <v>10</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Lärbro</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>På knoppar av värdväxten svinrot.</t>
+        </is>
+      </c>
+      <c r="AD101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ101" t="inlineStr">
+        <is>
+          <t>svinrot</t>
+        </is>
+      </c>
+      <c r="AK101" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="AO101" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr">
         <is>
           <t>FNT0020 Lärbro Nors NVI 2024</t>
         </is>

--- a/artfynd/A 15629-2024 artfynd.xlsx
+++ b/artfynd/A 15629-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY101"/>
+  <dimension ref="A1:AZ101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>FNT0020 Lärbro Nors NVI 2024</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126075241</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>FNT0020 Lärbro Nors NVI 2024</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126075242</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>FNT0020 Lärbro Nors NVI 2024</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126075243</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t>FNT0020 Lärbro Nors NVI 2024</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126075244</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
           <t>FNT0020 Lärbro Nors NVI 2024</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126075245</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
           <t>FNT0020 Lärbro Nors NVI 2024</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126075247</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,6 +1414,11 @@
           <t>FNT0020 Lärbro Nors NVI 2024</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126075253</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1480,6 +1520,11 @@
           <t>FNT0020 Lärbro Nors NVI 2024</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126075254</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1581,6 +1626,11 @@
           <t>FNT0020 Lärbro Nors NVI 2024</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126075255</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1682,6 +1732,11 @@
           <t>FNT0020 Lärbro Nors NVI 2024</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126075258</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1783,6 +1838,11 @@
           <t>FNT0020 Lärbro Nors NVI 2024</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126075330</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1884,6 +1944,11 @@
           <t>FNT0020 Lärbro Nors NVI 2024</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126075228</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1985,6 +2050,11 @@
           <t>FNT0020 Lärbro Nors NVI 2024</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126075071</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2105,6 +2175,11 @@
           <t>FNT0020 Lärbro Nors NVI 2024</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126075072</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2225,6 +2300,11 @@
           <t>Artskyddsutredning vid Lärbro 2021 (JAG0090)</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114813484</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2340,6 +2420,11 @@
           <t>Artskyddsutredning vid Lärbro 2021 (JAG0090)</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114813676</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2455,6 +2540,11 @@
           <t>Artskyddsutredning vid Lärbro 2021 (JAG0090)</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114814801</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2570,6 +2660,11 @@
           <t>Artskyddsutredning vid Lärbro 2021 (JAG0090)</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114814802</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2671,6 +2766,11 @@
           <t>FNT0020 Lärbro Nors NVI 2024</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126075452</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2772,6 +2872,11 @@
           <t>FNT0020 Lärbro Nors NVI 2024</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126075455</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2873,6 +2978,11 @@
           <t>FNT0020 Lärbro Nors NVI 2024</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126075073</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2974,6 +3084,11 @@
           <t>FNT0020 Lärbro Nors NVI 2024</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126075074</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3075,6 +3190,11 @@
           <t>FNT0020 Lärbro Nors NVI 2024</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126075167</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3181,6 +3301,11 @@
           <t>FNT0020 Lärbro Nors NVI 2024</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126075088</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3287,6 +3412,11 @@
           <t>FNT0020 Lärbro Nors NVI 2024</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126075089</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3393,6 +3523,11 @@
           <t>FNT0020 Lärbro Nors NVI 2024</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126075094</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3499,6 +3634,11 @@
           <t>FNT0020 Lärbro Nors NVI 2024</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126075095</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3605,6 +3745,11 @@
           <t>FNT0020 Lärbro Nors NVI 2024</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126075096</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3711,6 +3856,11 @@
           <t>FNT0020 Lärbro Nors NVI 2024</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126075099</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3817,6 +3967,11 @@
           <t>FNT0020 Lärbro Nors NVI 2024</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126075103</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3923,6 +4078,11 @@
           <t>FNT0020 Lärbro Nors NVI 2024</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126075105</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4024,6 +4184,11 @@
           <t>FNT0020 Lärbro Nors NVI 2024</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126075269</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4125,6 +4290,11 @@
           <t>FNT0020 Lärbro Nors NVI 2024</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126075028</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4226,6 +4396,11 @@
           <t>FNT0020 Lärbro Nors NVI 2024</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126075029</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4327,6 +4502,11 @@
           <t>FNT0020 Lärbro Nors NVI 2024</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126075030</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4428,6 +4608,11 @@
           <t>FNT0020 Lärbro Nors NVI 2024</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126075031</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4529,6 +4714,11 @@
           <t>FNT0020 Lärbro Nors NVI 2024</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126075032</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4630,6 +4820,11 @@
           <t>FNT0020 Lärbro Nors NVI 2024</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126075037</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4731,6 +4926,11 @@
           <t>FNT0020 Lärbro Nors NVI 2024</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126075038</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4832,6 +5032,11 @@
           <t>FNT0020 Lärbro Nors NVI 2024</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126075039</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4933,6 +5138,11 @@
           <t>FNT0020 Lärbro Nors NVI 2024</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126075040</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5034,6 +5244,11 @@
           <t>FNT0020 Lärbro Nors NVI 2024</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126075041</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5135,6 +5350,11 @@
           <t>FNT0020 Lärbro Nors NVI 2024</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126075042</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5236,6 +5456,11 @@
           <t>FNT0020 Lärbro Nors NVI 2024</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126075043</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5337,6 +5562,11 @@
           <t>FNT0020 Lärbro Nors NVI 2024</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126075044</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5438,6 +5668,11 @@
           <t>FNT0020 Lärbro Nors NVI 2024</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126075045</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5539,6 +5774,11 @@
           <t>FNT0020 Lärbro Nors NVI 2024</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126075046</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5640,6 +5880,11 @@
           <t>FNT0020 Lärbro Nors NVI 2024</t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126075047</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5741,6 +5986,11 @@
           <t>FNT0020 Lärbro Nors NVI 2024</t>
         </is>
       </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126075049</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5842,6 +6092,11 @@
           <t>FNT0020 Lärbro Nors NVI 2024</t>
         </is>
       </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126075050</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5943,6 +6198,11 @@
           <t>FNT0020 Lärbro Nors NVI 2024</t>
         </is>
       </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126075051</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6044,6 +6304,11 @@
           <t>FNT0020 Lärbro Nors NVI 2024</t>
         </is>
       </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126075052</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6145,6 +6410,11 @@
           <t>FNT0020 Lärbro Nors NVI 2024</t>
         </is>
       </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126075053</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6246,6 +6516,11 @@
           <t>FNT0020 Lärbro Nors NVI 2024</t>
         </is>
       </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126075054</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6347,6 +6622,11 @@
           <t>FNT0020 Lärbro Nors NVI 2024</t>
         </is>
       </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126075055</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6448,6 +6728,11 @@
           <t>FNT0020 Lärbro Nors NVI 2024</t>
         </is>
       </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126075294</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6549,6 +6834,11 @@
           <t>FNT0020 Lärbro Nors NVI 2024</t>
         </is>
       </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126075295</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6650,6 +6940,11 @@
           <t>FNT0020 Lärbro Nors NVI 2024</t>
         </is>
       </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126075344</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6751,6 +7046,11 @@
           <t>FNT0020 Lärbro Nors NVI 2024</t>
         </is>
       </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126075350</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6852,6 +7152,11 @@
           <t>FNT0020 Lärbro Nors NVI 2024</t>
         </is>
       </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126075351</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6953,6 +7258,11 @@
           <t>FNT0020 Lärbro Nors NVI 2024</t>
         </is>
       </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126075352</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7054,6 +7364,11 @@
           <t>FNT0020 Lärbro Nors NVI 2024</t>
         </is>
       </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126075353</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7155,6 +7470,11 @@
           <t>FNT0020 Lärbro Nors NVI 2024</t>
         </is>
       </c>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126075354</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7256,6 +7576,11 @@
           <t>FNT0020 Lärbro Nors NVI 2024</t>
         </is>
       </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126075355</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7357,6 +7682,11 @@
           <t>FNT0020 Lärbro Nors NVI 2024</t>
         </is>
       </c>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126075357</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7458,6 +7788,11 @@
           <t>FNT0020 Lärbro Nors NVI 2024</t>
         </is>
       </c>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126075369</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7559,6 +7894,11 @@
           <t>FNT0020 Lärbro Nors NVI 2024</t>
         </is>
       </c>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126075370</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7660,6 +8000,11 @@
           <t>FNT0020 Lärbro Nors NVI 2024</t>
         </is>
       </c>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126075378</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7761,6 +8106,11 @@
           <t>FNT0020 Lärbro Nors NVI 2024</t>
         </is>
       </c>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126075379</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7862,6 +8212,11 @@
           <t>FNT0020 Lärbro Nors NVI 2024</t>
         </is>
       </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126075380</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7963,6 +8318,11 @@
           <t>FNT0020 Lärbro Nors NVI 2024</t>
         </is>
       </c>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126075410</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8064,6 +8424,11 @@
           <t>FNT0020 Lärbro Nors NVI 2024</t>
         </is>
       </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126075412</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8165,6 +8530,11 @@
           <t>FNT0020 Lärbro Nors NVI 2024</t>
         </is>
       </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126075413</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8266,6 +8636,11 @@
           <t>FNT0020 Lärbro Nors NVI 2024</t>
         </is>
       </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126075416</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8367,6 +8742,11 @@
           <t>FNT0020 Lärbro Nors NVI 2024</t>
         </is>
       </c>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126075417</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8468,6 +8848,11 @@
           <t>FNT0020 Lärbro Nors NVI 2024</t>
         </is>
       </c>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126075419</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8569,6 +8954,11 @@
           <t>FNT0020 Lärbro Nors NVI 2024</t>
         </is>
       </c>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126075420</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8670,6 +9060,11 @@
           <t>FNT0020 Lärbro Nors NVI 2024</t>
         </is>
       </c>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126075421</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8771,6 +9166,11 @@
           <t>FNT0020 Lärbro Nors NVI 2024</t>
         </is>
       </c>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126075422</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8872,6 +9272,11 @@
           <t>FNT0020 Lärbro Nors NVI 2024</t>
         </is>
       </c>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126075427</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8973,6 +9378,11 @@
           <t>FNT0020 Lärbro Nors NVI 2024</t>
         </is>
       </c>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126075431</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9074,6 +9484,11 @@
           <t>FNT0020 Lärbro Nors NVI 2024</t>
         </is>
       </c>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126075432</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9175,6 +9590,11 @@
           <t>FNT0020 Lärbro Nors NVI 2024</t>
         </is>
       </c>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126075328</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9276,6 +9696,11 @@
           <t>FNT0020 Lärbro Nors NVI 2024</t>
         </is>
       </c>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126075329</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9377,6 +9802,11 @@
           <t>FNT0020 Lärbro Nors NVI 2024</t>
         </is>
       </c>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126075276</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9474,6 +9904,11 @@
           <t>FNT0020 Lärbro Nors NVI 2024</t>
         </is>
       </c>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126075182</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9571,6 +10006,11 @@
           <t>FNT0020 Lärbro Nors NVI 2024</t>
         </is>
       </c>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126075183</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9668,6 +10108,11 @@
           <t>FNT0020 Lärbro Nors NVI 2024</t>
         </is>
       </c>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126075184</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9765,6 +10210,11 @@
           <t>FNT0020 Lärbro Nors NVI 2024</t>
         </is>
       </c>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126075185</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9862,6 +10312,11 @@
           <t>FNT0020 Lärbro Nors NVI 2024</t>
         </is>
       </c>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126075186</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9959,6 +10414,11 @@
           <t>FNT0020 Lärbro Nors NVI 2024</t>
         </is>
       </c>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126075188</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10056,6 +10516,11 @@
           <t>FNT0020 Lärbro Nors NVI 2024</t>
         </is>
       </c>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126075189</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10153,6 +10618,11 @@
           <t>FNT0020 Lärbro Nors NVI 2024</t>
         </is>
       </c>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126075190</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10250,6 +10720,11 @@
           <t>FNT0020 Lärbro Nors NVI 2024</t>
         </is>
       </c>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126075191</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10347,6 +10822,11 @@
           <t>FNT0020 Lärbro Nors NVI 2024</t>
         </is>
       </c>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126075192</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10444,6 +10924,11 @@
           <t>FNT0020 Lärbro Nors NVI 2024</t>
         </is>
       </c>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126075193</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10541,6 +11026,11 @@
           <t>FNT0020 Lärbro Nors NVI 2024</t>
         </is>
       </c>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126075195</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10638,6 +11128,11 @@
           <t>FNT0020 Lärbro Nors NVI 2024</t>
         </is>
       </c>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126075200</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10739,6 +11234,11 @@
           <t>FNT0020 Lärbro Nors NVI 2024</t>
         </is>
       </c>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126075271</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -10855,8 +11355,115 @@
           <t>FNT0020 Lärbro Nors NVI 2024</t>
         </is>
       </c>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126075165</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>